--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G46">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G67">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G96">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G8">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N34">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G95">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G88">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G90">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G96">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G106">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G108">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G67">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G96">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G108">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G122">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G127">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,17 +5684,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5847,17 +5847,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,17 +7477,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,17 +7640,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,17 +8292,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,17 +8455,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G60">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G107">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G127">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q133">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
@@ -7816,55 +7816,55 @@
         <v>3.6</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14197,10 +14197,10 @@
         <v>0</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14360,10 +14360,10 @@
         <v>0</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14686,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q90">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -644,55 +644,55 @@
         <v>2.35</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>3.22</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -2111,34 +2111,34 @@
         <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
         <v>1.85</v>
@@ -2147,19 +2147,19 @@
         <v>1.91</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.85</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.93</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3741,34 +3741,34 @@
         <v>3.99</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA21">
         <v>1.79</v>
@@ -3777,19 +3777,19 @@
         <v>1.97</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.74</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>4.83</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
         <v>1.81</v>
@@ -4266,19 +4266,19 @@
         <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,34 +4393,34 @@
         <v>6.77</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
@@ -4429,19 +4429,19 @@
         <v>1.9</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
@@ -4755,19 +4755,19 @@
         <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,34 +4882,34 @@
         <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
         <v>1.88</v>
@@ -4918,19 +4918,19 @@
         <v>1.88</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>2.59</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>2.26</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>3.16</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>4.1</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,34 +5860,34 @@
         <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
         <v>1.81</v>
@@ -5896,19 +5896,19 @@
         <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>2.93</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
         <v>1.94</v>
@@ -6059,19 +6059,19 @@
         <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,34 +6186,34 @@
         <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
         <v>1.88</v>
@@ -6222,19 +6222,19 @@
         <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,34 +6349,34 @@
         <v>4.73</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA37">
         <v>1.83</v>
@@ -6385,19 +6385,19 @@
         <v>1.94</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,34 +6512,34 @@
         <v>2.73</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA38">
         <v>1.79</v>
@@ -6548,19 +6548,19 @@
         <v>1.97</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>3.19</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>2.14</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>3.03</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="O45">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="P45">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AB45">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="O46">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="P46">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="Q46">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="V46">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB46">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
       <c r="AD46">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE46">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
+        <v>1.58</v>
+      </c>
+      <c r="AG46">
+        <v>2.2</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.22</v>
+      </c>
+      <c r="AK46">
         <v>1.57</v>
-      </c>
-      <c r="AG46">
-        <v>2.26</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.23</v>
-      </c>
-      <c r="AK46">
-        <v>1.95</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,68 +7966,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
+        <v>2.92</v>
+      </c>
+      <c r="O47">
+        <v>3.1</v>
+      </c>
+      <c r="P47">
+        <v>2.48</v>
+      </c>
+      <c r="Q47">
+        <v>3.79</v>
+      </c>
+      <c r="R47">
+        <v>1.94</v>
+      </c>
+      <c r="S47">
+        <v>1.44</v>
+      </c>
+      <c r="T47">
+        <v>2.63</v>
+      </c>
+      <c r="U47">
+        <v>3.02</v>
+      </c>
+      <c r="V47">
+        <v>1.32</v>
+      </c>
+      <c r="W47">
+        <v>1.04</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.36</v>
+      </c>
+      <c r="Z47">
+        <v>2.92</v>
+      </c>
+      <c r="AA47">
         <v>2.28</v>
       </c>
-      <c r="O47">
-        <v>3.52</v>
-      </c>
-      <c r="P47">
-        <v>2.89</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
-      </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
-      </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.03</v>
+        <v>2.43</v>
       </c>
       <c r="O48">
         <v>3.72</v>
       </c>
       <c r="P48">
-        <v>1.81</v>
+        <v>2.53</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA48">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,68 +8292,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O49">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.43</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
         <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.53</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>2.62</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA55">
         <v>2.25</v>
@@ -9319,19 +9319,19 @@
         <v>1.55</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>4.55</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>2.84</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q113">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU134"/>
+  <dimension ref="A1:AU135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,55 +970,55 @@
         <v>1.67</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>2.22</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>3.62</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>3.26</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.99</v>
+        <v>2.74</v>
       </c>
       <c r="Q21">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE21">
         <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK21">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O22">
+        <v>3.62</v>
+      </c>
+      <c r="P22">
+        <v>3.04</v>
+      </c>
+      <c r="Q22">
+        <v>2.52</v>
+      </c>
+      <c r="R22">
+        <v>2.27</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
         <v>3.5</v>
       </c>
-      <c r="P22">
-        <v>2.74</v>
-      </c>
-      <c r="Q22">
-        <v>3.3</v>
-      </c>
-      <c r="R22">
-        <v>2.25</v>
-      </c>
-      <c r="S22">
-        <v>1.29</v>
-      </c>
-      <c r="T22">
-        <v>3.25</v>
-      </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
+        <v>1.55</v>
+      </c>
+      <c r="W22">
+        <v>1.14</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.16</v>
+      </c>
+      <c r="Z22">
+        <v>4.38</v>
+      </c>
+      <c r="AA22">
+        <v>1.81</v>
+      </c>
+      <c r="AB22">
+        <v>1.96</v>
+      </c>
+      <c r="AC22">
+        <v>2.49</v>
+      </c>
+      <c r="AD22">
+        <v>1.44</v>
+      </c>
+      <c r="AE22">
+        <v>1.13</v>
+      </c>
+      <c r="AF22">
         <v>1.53</v>
       </c>
-      <c r="W22">
-        <v>1.11</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.17</v>
-      </c>
-      <c r="Z22">
-        <v>4</v>
-      </c>
-      <c r="AA22">
-        <v>1.64</v>
-      </c>
-      <c r="AB22">
-        <v>2.08</v>
-      </c>
-      <c r="AC22">
-        <v>2.62</v>
-      </c>
-      <c r="AD22">
-        <v>1.38</v>
-      </c>
-      <c r="AE22">
-        <v>1.16</v>
-      </c>
-      <c r="AF22">
-        <v>1.56</v>
-      </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="P30">
-        <v>2.59</v>
+        <v>4.1</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AB30">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>3.42</v>
+        <v>2.27</v>
       </c>
       <c r="AD30">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="AE30">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG30">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P31">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="Q31">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AA31">
         <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AC31">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG31">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O32">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P32">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q32">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,69 +5684,69 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
+        <v>3.17</v>
+      </c>
+      <c r="R33">
+        <v>2.23</v>
+      </c>
+      <c r="S33">
+        <v>1.39</v>
+      </c>
+      <c r="T33">
+        <v>2.71</v>
+      </c>
+      <c r="U33">
+        <v>2.81</v>
+      </c>
+      <c r="V33">
+        <v>1.36</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.27</v>
+      </c>
+      <c r="Z33">
+        <v>3.42</v>
+      </c>
+      <c r="AA33">
+        <v>1.88</v>
+      </c>
+      <c r="AB33">
+        <v>1.88</v>
+      </c>
+      <c r="AC33">
+        <v>3.08</v>
+      </c>
+      <c r="AD33">
+        <v>1.28</v>
+      </c>
+      <c r="AE33">
+        <v>1.06</v>
+      </c>
+      <c r="AF33">
+        <v>1.75</v>
+      </c>
+      <c r="AG33">
         <v>2</v>
       </c>
-      <c r="R33">
-        <v>2.4</v>
-      </c>
-      <c r="S33">
-        <v>1.18</v>
-      </c>
-      <c r="T33">
-        <v>3.8</v>
-      </c>
-      <c r="U33">
-        <v>2.2</v>
-      </c>
-      <c r="V33">
-        <v>1.6</v>
-      </c>
-      <c r="W33">
-        <v>1.16</v>
-      </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.11</v>
-      </c>
-      <c r="Z33">
-        <v>4.85</v>
-      </c>
-      <c r="AA33">
-        <v>1.47</v>
-      </c>
-      <c r="AB33">
-        <v>2.35</v>
-      </c>
-      <c r="AC33">
-        <v>2.27</v>
-      </c>
-      <c r="AD33">
-        <v>1.61</v>
-      </c>
-      <c r="AE33">
-        <v>1.19</v>
-      </c>
-      <c r="AF33">
-        <v>1.52</v>
-      </c>
-      <c r="AG33">
-        <v>2.33</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,61 +5851,61 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
         <v>2.05</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
+        <v>2.17</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.61</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.19</v>
+      </c>
+      <c r="Z35">
+        <v>3.74</v>
+      </c>
+      <c r="AA35">
+        <v>1.73</v>
+      </c>
+      <c r="AB35">
+        <v>1.99</v>
+      </c>
+      <c r="AC35">
+        <v>2.7</v>
+      </c>
+      <c r="AD35">
+        <v>1.35</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
         <v>2.2</v>
       </c>
-      <c r="S35">
-        <v>1.38</v>
-      </c>
-      <c r="T35">
-        <v>2.91</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.08</v>
-      </c>
-      <c r="AA35">
-        <v>1.94</v>
-      </c>
-      <c r="AB35">
-        <v>1.83</v>
-      </c>
-      <c r="AC35">
-        <v>3.28</v>
-      </c>
-      <c r="AD35">
-        <v>1.25</v>
-      </c>
-      <c r="AE35">
-        <v>1.1</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>1.94</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
+        <v>2.91</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.36</v>
+      </c>
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
         <v>3.08</v>
       </c>
-      <c r="U37">
-        <v>2.48</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.08</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.26</v>
-      </c>
-      <c r="Z37">
-        <v>3.58</v>
-      </c>
       <c r="AA37">
+        <v>1.94</v>
+      </c>
+      <c r="AB37">
         <v>1.83</v>
       </c>
-      <c r="AB37">
-        <v>1.94</v>
-      </c>
       <c r="AC37">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.73</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,84 +7477,84 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="O44">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>3.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q44">
-        <v>2.7</v>
+        <v>3.79</v>
       </c>
       <c r="R44">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>3.02</v>
       </c>
       <c r="V44">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W44">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="AB44">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AC44">
-        <v>2.62</v>
+        <v>3.96</v>
       </c>
       <c r="AD44">
+        <v>1.17</v>
+      </c>
+      <c r="AE44">
+        <v>1.02</v>
+      </c>
+      <c r="AF44">
+        <v>1.85</v>
+      </c>
+      <c r="AG44">
+        <v>1.8</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.33</v>
+      </c>
+      <c r="AK44">
         <v>1.38</v>
-      </c>
-      <c r="AE44">
-        <v>1.11</v>
-      </c>
-      <c r="AF44">
-        <v>1.56</v>
-      </c>
-      <c r="AG44">
-        <v>2.24</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.26</v>
-      </c>
-      <c r="AK44">
-        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
-        <v>1.9</v>
+        <v>4.03</v>
       </c>
       <c r="O45">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="P45">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="Q45">
-        <v>2.3</v>
+        <v>4.36</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U45">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="V45">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AB45">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AC45">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
       <c r="AD45">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG45">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>2.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q46">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AA46">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,68 +7966,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="P47">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="Q47">
-        <v>3.79</v>
+        <v>2.3</v>
       </c>
       <c r="R47">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U47">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="V47">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
-        <v>1.61</v>
+        <v>2.23</v>
       </c>
       <c r="AC47">
-        <v>3.96</v>
+        <v>2.41</v>
       </c>
       <c r="AD47">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.09</v>
+        <v>3.03</v>
       </c>
       <c r="Q49">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z49">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AB49">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
         <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,32 +8455,32 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>2.28</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.89</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>2.88</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
         <v>1.44</v>
@@ -8489,50 +8489,50 @@
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
+        <v>1.21</v>
+      </c>
+      <c r="Z50">
+        <v>3.88</v>
+      </c>
+      <c r="AA50">
+        <v>1.73</v>
+      </c>
+      <c r="AB50">
+        <v>2.1</v>
+      </c>
+      <c r="AC50">
+        <v>2.74</v>
+      </c>
+      <c r="AD50">
+        <v>1.35</v>
+      </c>
+      <c r="AE50">
+        <v>1.1</v>
+      </c>
+      <c r="AF50">
+        <v>1.58</v>
+      </c>
+      <c r="AG50">
+        <v>2.2</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.81</v>
-      </c>
-      <c r="AB50">
-        <v>1.99</v>
-      </c>
-      <c r="AC50">
-        <v>2.83</v>
-      </c>
-      <c r="AD50">
-        <v>1.36</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.71</v>
-      </c>
-      <c r="AG50">
-        <v>2</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.25</v>
-      </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>3.33</v>
+        <v>1.75</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.8</v>
+        <v>1.11</v>
       </c>
       <c r="O53">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="P53">
-        <v>1.75</v>
+        <v>15.5</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AC53">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AD53">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="O54">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="P54">
-        <v>15.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G78">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-10-03 13:30:00</t>
+          <t>2026-10-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="O80">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="P80">
-        <v>2.84</v>
+        <v>3.67</v>
       </c>
       <c r="Q80">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB80">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC80">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-10-03 13:45:00</t>
+          <t>2026-10-03 13:30:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-03 14:00:00</t>
+          <t>2026-10-03 13:45:00</t>
         </is>
       </c>
     </row>
@@ -13791,27 +13791,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G83">
@@ -13834,68 +13834,68 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N83">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-03 15:00:00</t>
+          <t>2026-10-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O84">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q84">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R84">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U84">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="V84">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W84">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z84">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="AA84">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AB84">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC84">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD84">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,68 +14160,68 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N85">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O85">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>4.27</v>
+        <v>3.3</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z85">
+        <v>2.91</v>
+      </c>
+      <c r="AA85">
         <v>2.15</v>
       </c>
-      <c r="AA85">
-        <v>0</v>
-      </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O86">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P86">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>1.6</v>
       </c>
       <c r="Z86">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O87">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="P87">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
+        <v>2.25</v>
+      </c>
+      <c r="O88">
         <v>2.55</v>
       </c>
-      <c r="O88">
-        <v>2.7</v>
-      </c>
       <c r="P88">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14686,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z88">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,14 +14816,14 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O89">
+        <v>2.7</v>
+      </c>
+      <c r="P89">
         <v>2.95</v>
       </c>
-      <c r="P89">
-        <v>3.2</v>
-      </c>
       <c r="Q89">
         <v>0</v>
       </c>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Z89">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O90">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P90">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G94">
@@ -15634,61 +15634,61 @@
         <v>1.91</v>
       </c>
       <c r="O94">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P94">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
       </c>
       <c r="R94">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S94">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T94">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U94">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="V94">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="W94">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z94">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA94">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB94">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AC94">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AD94">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AE94">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF94">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG94">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
+        <v>1.91</v>
+      </c>
+      <c r="O95">
+        <v>3.7</v>
+      </c>
+      <c r="P95">
+        <v>3.1</v>
+      </c>
+      <c r="Q95">
+        <v>2.4</v>
+      </c>
+      <c r="R95">
+        <v>2.5</v>
+      </c>
+      <c r="S95">
+        <v>1.2</v>
+      </c>
+      <c r="T95">
+        <v>4</v>
+      </c>
+      <c r="U95">
+        <v>2.1</v>
+      </c>
+      <c r="V95">
+        <v>1.69</v>
+      </c>
+      <c r="W95">
+        <v>1.18</v>
+      </c>
+      <c r="X95">
+        <v>1.02</v>
+      </c>
+      <c r="Y95">
+        <v>1.11</v>
+      </c>
+      <c r="Z95">
+        <v>5.75</v>
+      </c>
+      <c r="AA95">
+        <v>1.39</v>
+      </c>
+      <c r="AB95">
+        <v>2.59</v>
+      </c>
+      <c r="AC95">
+        <v>2.06</v>
+      </c>
+      <c r="AD95">
+        <v>1.7</v>
+      </c>
+      <c r="AE95">
+        <v>1.25</v>
+      </c>
+      <c r="AF95">
+        <v>1.39</v>
+      </c>
+      <c r="AG95">
+        <v>2.77</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.2</v>
+      </c>
+      <c r="AK95">
         <v>1.8</v>
-      </c>
-      <c r="O95">
-        <v>3.8</v>
-      </c>
-      <c r="P95">
-        <v>3.3</v>
-      </c>
-      <c r="Q95">
-        <v>2.3</v>
-      </c>
-      <c r="R95">
-        <v>2.51</v>
-      </c>
-      <c r="S95">
-        <v>1.15</v>
-      </c>
-      <c r="T95">
-        <v>4.3</v>
-      </c>
-      <c r="U95">
-        <v>1.97</v>
-      </c>
-      <c r="V95">
-        <v>1.75</v>
-      </c>
-      <c r="W95">
-        <v>1.22</v>
-      </c>
-      <c r="X95">
-        <v>1.01</v>
-      </c>
-      <c r="Y95">
-        <v>1.07</v>
-      </c>
-      <c r="Z95">
-        <v>7</v>
-      </c>
-      <c r="AA95">
-        <v>1.32</v>
-      </c>
-      <c r="AB95">
-        <v>2.88</v>
-      </c>
-      <c r="AC95">
-        <v>1.89</v>
-      </c>
-      <c r="AD95">
-        <v>1.84</v>
-      </c>
-      <c r="AE95">
-        <v>1.32</v>
-      </c>
-      <c r="AF95">
-        <v>1.35</v>
-      </c>
-      <c r="AG95">
-        <v>2.9</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.18</v>
-      </c>
-      <c r="AK95">
-        <v>1.87</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,65 +15957,65 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.82</v>
+        <v>1.8</v>
       </c>
       <c r="O96">
         <v>3.8</v>
       </c>
       <c r="P96">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q96">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="R96">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S96">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T96">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U96">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V96">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA96">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB96">
+        <v>2.88</v>
+      </c>
+      <c r="AC96">
+        <v>1.89</v>
+      </c>
+      <c r="AD96">
+        <v>1.84</v>
+      </c>
+      <c r="AE96">
+        <v>1.32</v>
+      </c>
+      <c r="AF96">
+        <v>1.35</v>
+      </c>
+      <c r="AG96">
         <v>2.9</v>
       </c>
-      <c r="AC96">
-        <v>1.99</v>
-      </c>
-      <c r="AD96">
-        <v>1.75</v>
-      </c>
-      <c r="AE96">
-        <v>1.33</v>
-      </c>
-      <c r="AF96">
-        <v>1.33</v>
-      </c>
-      <c r="AG96">
-        <v>3</v>
-      </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AK96">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-03 15:30:00</t>
+          <t>2026-10-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G101">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-03 15:45:00</t>
+          <t>2026-10-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G109">
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-03 16:00:00</t>
+          <t>2026-10-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-03 17:00:00</t>
+          <t>2026-10-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G117">
@@ -19376,68 +19376,68 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N117">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S117">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T117">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U117">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V117">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB117">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD117">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE117">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK117">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-03 17:30:00</t>
+          <t>2026-10-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O118">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S118">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T118">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U118">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V118">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W118">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
         <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z118">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA118">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB118">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC118">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD118">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE118">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF118">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG118">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK118">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-03 18:30:00</t>
+          <t>2026-10-03 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G119">
@@ -19702,68 +19702,68 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-03 19:30:00</t>
+          <t>2026-10-03 19:00:00</t>
         </is>
       </c>
     </row>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G124">
@@ -20517,68 +20517,68 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N124">
-        <v>2.97</v>
+        <v>1.43</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="P124">
-        <v>2.22</v>
+        <v>5.65</v>
       </c>
       <c r="Q124">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S124">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T124">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U124">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W124">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA124">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AD124">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK124">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-03 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G125">
@@ -20680,68 +20680,68 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>4.13</v>
       </c>
       <c r="O126">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P126">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-10-03 20:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-03 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G130">
@@ -21615,27 +21615,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-10-03 21:45:00</t>
+          <t>2026-10-03 21:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="O132">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="P132">
-        <v>4.24</v>
+        <v>3.01</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-10-03 22:00:00</t>
+          <t>2026-10-03 21:45:00</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
       <c r="O133">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="P133">
-        <v>2.76</v>
+        <v>4.24</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-10-03 23:00:00</t>
+          <t>2026-10-03 22:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,156 +22104,319 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N134">
+        <v>2.21</v>
+      </c>
+      <c r="O134">
+        <v>3.44</v>
+      </c>
+      <c r="P134">
+        <v>2.76</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
+        <v>0</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>-1</v>
+      </c>
+      <c r="AN134">
+        <v>-1</v>
+      </c>
+      <c r="AO134">
+        <v>-1</v>
+      </c>
+      <c r="AP134">
+        <v>-1</v>
+      </c>
+      <c r="AQ134">
+        <v>0</v>
+      </c>
+      <c r="AR134">
+        <v>0</v>
+      </c>
+      <c r="AS134">
+        <v>0</v>
+      </c>
+      <c r="AT134">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>2026-10-03 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>-1</v>
+      </c>
+      <c r="AN135">
+        <v>-1</v>
+      </c>
+      <c r="AO135">
+        <v>-1</v>
+      </c>
+      <c r="AP135">
+        <v>-1</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
         <is>
           <t>2026-10-03 23:30:00</t>
         </is>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.98</v>
+        <v>1.79</v>
       </c>
       <c r="O5">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>2.22</v>
+        <v>3.62</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="S5">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>3.46</v>
       </c>
       <c r="U5">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>3.07</v>
+        <v>4.73</v>
       </c>
       <c r="AA5">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AC5">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.79</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.13</v>
       </c>
       <c r="P6">
-        <v>3.62</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="R6">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="V6">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>4.73</v>
+        <v>3.07</v>
       </c>
       <c r="AA6">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AG6">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.74</v>
+        <v>3.99</v>
       </c>
       <c r="Q21">
+        <v>2.23</v>
+      </c>
+      <c r="R21">
+        <v>2.46</v>
+      </c>
+      <c r="S21">
+        <v>1.25</v>
+      </c>
+      <c r="T21">
         <v>3.3</v>
       </c>
-      <c r="R21">
-        <v>2.25</v>
-      </c>
-      <c r="S21">
-        <v>1.29</v>
-      </c>
-      <c r="T21">
-        <v>3.25</v>
-      </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="AA21">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB21">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AC21">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
         <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>2.74</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O25">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P25">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R25">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U25">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC25">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="P26">
-        <v>1.66</v>
+        <v>6.77</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
         <v>2.68</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
+        <v>3.34</v>
+      </c>
+      <c r="AA26">
+        <v>1.85</v>
+      </c>
+      <c r="AB26">
+        <v>1.9</v>
+      </c>
+      <c r="AC26">
         <v>3.19</v>
       </c>
-      <c r="AA26">
-        <v>2.02</v>
-      </c>
-      <c r="AB26">
-        <v>1.77</v>
-      </c>
-      <c r="AC26">
-        <v>3.34</v>
-      </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK26">
-        <v>1.1</v>
+        <v>2.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,65 +4710,65 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>1.66</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.66</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.19</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB27">
+        <v>1.77</v>
+      </c>
+      <c r="AC27">
+        <v>3.34</v>
+      </c>
+      <c r="AD27">
+        <v>1.24</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
         <v>1.91</v>
       </c>
-      <c r="AC27">
-        <v>2.89</v>
-      </c>
-      <c r="AD27">
-        <v>1.38</v>
-      </c>
-      <c r="AE27">
-        <v>1.13</v>
-      </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>1.76</v>
       </c>
-      <c r="AG27">
-        <v>1.94</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q33">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,40 +5851,40 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U34">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
         <v>3.42</v>
@@ -5905,10 +5905,10 @@
         <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
         <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
+        <v>1.23</v>
+      </c>
+      <c r="Z37">
+        <v>3.42</v>
+      </c>
+      <c r="AA37">
+        <v>1.88</v>
+      </c>
+      <c r="AB37">
+        <v>1.88</v>
+      </c>
+      <c r="AC37">
+        <v>3.08</v>
+      </c>
+      <c r="AD37">
         <v>1.28</v>
       </c>
-      <c r="Z37">
-        <v>3.08</v>
-      </c>
-      <c r="AA37">
-        <v>1.94</v>
-      </c>
-      <c r="AB37">
-        <v>1.83</v>
-      </c>
-      <c r="AC37">
-        <v>3.28</v>
-      </c>
-      <c r="AD37">
-        <v>1.25</v>
-      </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.11</v>
+        <v>2.43</v>
       </c>
       <c r="O43">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P43">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="Q43">
+        <v>2.88</v>
+      </c>
+      <c r="R43">
+        <v>2.26</v>
+      </c>
+      <c r="S43">
+        <v>1.22</v>
+      </c>
+      <c r="T43">
         <v>3.9</v>
       </c>
-      <c r="R43">
+      <c r="U43">
+        <v>2.25</v>
+      </c>
+      <c r="V43">
+        <v>1.57</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1.02</v>
+      </c>
+      <c r="Y43">
+        <v>1.14</v>
+      </c>
+      <c r="Z43">
+        <v>4.7</v>
+      </c>
+      <c r="AA43">
+        <v>1.53</v>
+      </c>
+      <c r="AB43">
+        <v>2.21</v>
+      </c>
+      <c r="AC43">
         <v>2.4</v>
       </c>
-      <c r="S43">
-        <v>1.29</v>
-      </c>
-      <c r="T43">
-        <v>3.26</v>
-      </c>
-      <c r="U43">
-        <v>2.35</v>
-      </c>
-      <c r="V43">
-        <v>1.51</v>
-      </c>
-      <c r="W43">
-        <v>1.1</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.2</v>
-      </c>
-      <c r="Z43">
-        <v>3.7</v>
-      </c>
-      <c r="AA43">
-        <v>1.64</v>
-      </c>
-      <c r="AB43">
-        <v>2.14</v>
-      </c>
-      <c r="AC43">
-        <v>2.56</v>
-      </c>
       <c r="AD43">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="P44">
-        <v>2.48</v>
+        <v>3.03</v>
       </c>
       <c r="Q44">
-        <v>3.79</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z44">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA44">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AC44">
-        <v>3.96</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AE44">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>4.03</v>
+        <v>3.15</v>
       </c>
       <c r="O45">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P45">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="Q45">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U45">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W45">
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA45">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB45">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD45">
         <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="P46">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q46">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD46">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,84 +7966,84 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="O47">
-        <v>3.76</v>
+        <v>3.16</v>
       </c>
       <c r="P47">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="Q47">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V47">
+        <v>1.35</v>
+      </c>
+      <c r="W47">
+        <v>1.03</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>1.3</v>
+      </c>
+      <c r="Z47">
+        <v>3.44</v>
+      </c>
+      <c r="AA47">
+        <v>2</v>
+      </c>
+      <c r="AB47">
+        <v>1.83</v>
+      </c>
+      <c r="AC47">
+        <v>3.2</v>
+      </c>
+      <c r="AD47">
+        <v>1.3</v>
+      </c>
+      <c r="AE47">
+        <v>1.06</v>
+      </c>
+      <c r="AF47">
+        <v>1.73</v>
+      </c>
+      <c r="AG47">
+        <v>1.98</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.31</v>
+      </c>
+      <c r="AK47">
         <v>1.56</v>
-      </c>
-      <c r="W47">
-        <v>1.12</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.15</v>
-      </c>
-      <c r="Z47">
-        <v>4.2</v>
-      </c>
-      <c r="AA47">
-        <v>1.61</v>
-      </c>
-      <c r="AB47">
-        <v>2.23</v>
-      </c>
-      <c r="AC47">
-        <v>2.41</v>
-      </c>
-      <c r="AD47">
-        <v>1.45</v>
-      </c>
-      <c r="AE47">
-        <v>1.16</v>
-      </c>
-      <c r="AF47">
-        <v>1.57</v>
-      </c>
-      <c r="AG47">
-        <v>2.26</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.23</v>
-      </c>
-      <c r="AK47">
-        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.43</v>
+        <v>3.11</v>
       </c>
       <c r="O48">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P48">
-        <v>2.53</v>
+        <v>2.14</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="U48">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>3.7</v>
+      </c>
+      <c r="AA48">
+        <v>1.64</v>
+      </c>
+      <c r="AB48">
+        <v>2.14</v>
+      </c>
+      <c r="AC48">
+        <v>2.56</v>
+      </c>
+      <c r="AD48">
+        <v>1.4</v>
+      </c>
+      <c r="AE48">
         <v>1.14</v>
       </c>
-      <c r="Z48">
-        <v>4.7</v>
-      </c>
-      <c r="AA48">
-        <v>1.53</v>
-      </c>
-      <c r="AB48">
-        <v>2.21</v>
-      </c>
-      <c r="AC48">
-        <v>2.4</v>
-      </c>
-      <c r="AD48">
-        <v>1.53</v>
-      </c>
-      <c r="AE48">
-        <v>1.17</v>
-      </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,68 +8292,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
-        <v>2.16</v>
+        <v>4.03</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="P49">
-        <v>3.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>4.36</v>
       </c>
       <c r="R49">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AB49">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC49">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG49">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="O53">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>15.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q53">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="R53">
-        <v>3.74</v>
+        <v>2.55</v>
       </c>
       <c r="S53">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T53">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="U53">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V53">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="W53">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA53">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AB53">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC53">
+        <v>1.7</v>
+      </c>
+      <c r="AD53">
+        <v>1.99</v>
+      </c>
+      <c r="AE53">
         <v>1.44</v>
       </c>
-      <c r="AD53">
-        <v>2.42</v>
-      </c>
-      <c r="AE53">
-        <v>1.67</v>
-      </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AG53">
-        <v>2.32</v>
+        <v>3.24</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="O54">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="P54">
-        <v>3.33</v>
+        <v>15.5</v>
       </c>
       <c r="Q54">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="R54">
-        <v>2.55</v>
+        <v>3.74</v>
       </c>
       <c r="S54">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="T54">
+        <v>6.5</v>
+      </c>
+      <c r="U54">
+        <v>1.58</v>
+      </c>
+      <c r="V54">
+        <v>2.19</v>
+      </c>
+      <c r="W54">
+        <v>1.36</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.01</v>
+      </c>
+      <c r="Z54">
+        <v>10</v>
+      </c>
+      <c r="AA54">
+        <v>1.14</v>
+      </c>
+      <c r="AB54">
         <v>4.8</v>
       </c>
-      <c r="U54">
-        <v>1.78</v>
-      </c>
-      <c r="V54">
-        <v>2</v>
-      </c>
-      <c r="W54">
-        <v>1.25</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.05</v>
-      </c>
-      <c r="Z54">
-        <v>8</v>
-      </c>
-      <c r="AA54">
-        <v>1.28</v>
-      </c>
-      <c r="AB54">
-        <v>3.6</v>
-      </c>
       <c r="AC54">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AD54">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="AE54">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AF54">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>3.24</v>
+        <v>2.32</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK54">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22353,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC135">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P21">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q21">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R21">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
         <v>1.55</v>
@@ -3762,34 +3762,34 @@
         <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
         <v>4.38</v>
       </c>
       <c r="AA21">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
+        <v>1.17</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>1.64</v>
+      </c>
+      <c r="AB22">
+        <v>2.08</v>
+      </c>
+      <c r="AC22">
+        <v>2.62</v>
+      </c>
+      <c r="AD22">
+        <v>1.38</v>
+      </c>
+      <c r="AE22">
         <v>1.16</v>
       </c>
-      <c r="Z22">
-        <v>4.38</v>
-      </c>
-      <c r="AA22">
-        <v>1.81</v>
-      </c>
-      <c r="AB22">
-        <v>1.96</v>
-      </c>
-      <c r="AC22">
-        <v>2.49</v>
-      </c>
-      <c r="AD22">
-        <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
       <c r="AF22">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG22">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AK22">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>2.74</v>
+        <v>3.99</v>
       </c>
       <c r="Q24">
+        <v>2.23</v>
+      </c>
+      <c r="R24">
+        <v>2.46</v>
+      </c>
+      <c r="S24">
+        <v>1.25</v>
+      </c>
+      <c r="T24">
         <v>3.3</v>
       </c>
-      <c r="R24">
-        <v>2.25</v>
-      </c>
-      <c r="S24">
-        <v>1.29</v>
-      </c>
-      <c r="T24">
-        <v>3.25</v>
-      </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
         <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
         <v>2.25</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="O32">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P32">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q32">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R32">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q33">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R33">
+        <v>2.17</v>
+      </c>
+      <c r="S33">
+        <v>1.3</v>
+      </c>
+      <c r="T33">
+        <v>3.14</v>
+      </c>
+      <c r="U33">
+        <v>2.61</v>
+      </c>
+      <c r="V33">
+        <v>1.45</v>
+      </c>
+      <c r="W33">
+        <v>1.09</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.19</v>
+      </c>
+      <c r="Z33">
+        <v>3.74</v>
+      </c>
+      <c r="AA33">
+        <v>1.73</v>
+      </c>
+      <c r="AB33">
+        <v>1.99</v>
+      </c>
+      <c r="AC33">
+        <v>2.7</v>
+      </c>
+      <c r="AD33">
+        <v>1.35</v>
+      </c>
+      <c r="AE33">
+        <v>1.11</v>
+      </c>
+      <c r="AF33">
+        <v>1.6</v>
+      </c>
+      <c r="AG33">
         <v>2.2</v>
       </c>
-      <c r="S33">
-        <v>1.38</v>
-      </c>
-      <c r="T33">
-        <v>2.91</v>
-      </c>
-      <c r="U33">
-        <v>2.88</v>
-      </c>
-      <c r="V33">
-        <v>1.36</v>
-      </c>
-      <c r="W33">
-        <v>1.07</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.28</v>
-      </c>
-      <c r="Z33">
-        <v>3.08</v>
-      </c>
-      <c r="AA33">
-        <v>1.94</v>
-      </c>
-      <c r="AB33">
-        <v>1.83</v>
-      </c>
-      <c r="AC33">
-        <v>3.28</v>
-      </c>
-      <c r="AD33">
-        <v>1.25</v>
-      </c>
-      <c r="AE33">
-        <v>1.1</v>
-      </c>
-      <c r="AF33">
-        <v>1.75</v>
-      </c>
-      <c r="AG33">
-        <v>1.94</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z35">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA35">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK35">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>4.73</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
         <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
         <v>2.05</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,61 +6340,61 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>2.45</v>
+        <v>4.73</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
+        <v>1.29</v>
+      </c>
+      <c r="T37">
+        <v>3.08</v>
+      </c>
+      <c r="U37">
+        <v>2.48</v>
+      </c>
+      <c r="V37">
+        <v>1.46</v>
+      </c>
+      <c r="W37">
+        <v>1.08</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.26</v>
+      </c>
+      <c r="Z37">
+        <v>3.58</v>
+      </c>
+      <c r="AA37">
+        <v>1.83</v>
+      </c>
+      <c r="AB37">
+        <v>1.94</v>
+      </c>
+      <c r="AC37">
+        <v>3.11</v>
+      </c>
+      <c r="AD37">
         <v>1.31</v>
       </c>
-      <c r="T37">
-        <v>3.2</v>
-      </c>
-      <c r="U37">
-        <v>2.57</v>
-      </c>
-      <c r="V37">
-        <v>1.43</v>
-      </c>
-      <c r="W37">
-        <v>1.07</v>
-      </c>
-      <c r="X37">
-        <v>1</v>
-      </c>
-      <c r="Y37">
-        <v>1.23</v>
-      </c>
-      <c r="Z37">
-        <v>3.42</v>
-      </c>
-      <c r="AA37">
-        <v>1.88</v>
-      </c>
-      <c r="AB37">
-        <v>1.88</v>
-      </c>
-      <c r="AC37">
-        <v>3.08</v>
-      </c>
-      <c r="AD37">
-        <v>1.28</v>
-      </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
         <v>2.05</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z38">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="O45">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P45">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="Q45">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="V45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB45">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD45">
         <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG45">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
+        <v>1.25</v>
+      </c>
+      <c r="AK45">
         <v>1.22</v>
-      </c>
-      <c r="AK45">
-        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
+        <v>2.09</v>
+      </c>
+      <c r="Q46">
         <v>3.6</v>
-      </c>
-      <c r="Q46">
-        <v>2.3</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AB46">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,68 +7966,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="O47">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
       <c r="P47">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="Q47">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="R47">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U47">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V47">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
+        <v>1.12</v>
+      </c>
+      <c r="X47">
         <v>1.03</v>
       </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AC47">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.11</v>
+        <v>2.27</v>
       </c>
       <c r="O48">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="P48">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T48">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="U48">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA48">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AB48">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
+        <v>1.73</v>
+      </c>
+      <c r="AG48">
+        <v>1.98</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.31</v>
+      </c>
+      <c r="AK48">
         <v>1.56</v>
-      </c>
-      <c r="AG48">
-        <v>2.24</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.26</v>
-      </c>
-      <c r="AK48">
-        <v>1.29</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O49">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P49">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U49">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA49">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB49">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU135"/>
+  <dimension ref="A1:AU136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-03 11:00:00</t>
+          <t>2026-10-03 10:00:00</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O22">
+        <v>3.62</v>
+      </c>
+      <c r="P22">
+        <v>3.04</v>
+      </c>
+      <c r="Q22">
+        <v>2.52</v>
+      </c>
+      <c r="R22">
+        <v>2.27</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
         <v>3.5</v>
       </c>
-      <c r="P22">
-        <v>2.74</v>
-      </c>
-      <c r="Q22">
-        <v>3.3</v>
-      </c>
-      <c r="R22">
-        <v>2.25</v>
-      </c>
-      <c r="S22">
-        <v>1.29</v>
-      </c>
-      <c r="T22">
-        <v>3.25</v>
-      </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
+        <v>1.55</v>
+      </c>
+      <c r="W22">
+        <v>1.14</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.16</v>
+      </c>
+      <c r="Z22">
+        <v>4.38</v>
+      </c>
+      <c r="AA22">
+        <v>1.81</v>
+      </c>
+      <c r="AB22">
+        <v>1.96</v>
+      </c>
+      <c r="AC22">
+        <v>2.49</v>
+      </c>
+      <c r="AD22">
+        <v>1.44</v>
+      </c>
+      <c r="AE22">
+        <v>1.13</v>
+      </c>
+      <c r="AF22">
         <v>1.53</v>
       </c>
-      <c r="W22">
-        <v>1.11</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.17</v>
-      </c>
-      <c r="Z22">
-        <v>4</v>
-      </c>
-      <c r="AA22">
-        <v>1.64</v>
-      </c>
-      <c r="AB22">
-        <v>2.08</v>
-      </c>
-      <c r="AC22">
-        <v>2.62</v>
-      </c>
-      <c r="AD22">
-        <v>1.38</v>
-      </c>
-      <c r="AE22">
-        <v>1.16</v>
-      </c>
-      <c r="AF22">
-        <v>1.56</v>
-      </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>5.86</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>2.09</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
         <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AB25">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AC25">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AD25">
         <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="AG25">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AK25">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="O30">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AA30">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>2.27</v>
+        <v>3.42</v>
       </c>
       <c r="AD30">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="AE30">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,68 +5358,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="P31">
-        <v>2.73</v>
+        <v>4.1</v>
       </c>
       <c r="Q31">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T31">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z31">
-        <v>3.92</v>
+        <v>4.85</v>
       </c>
       <c r="AA31">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AB31">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,31 +5525,31 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O32">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P32">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="Q32">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U32">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
         <v>1.07</v>
@@ -5558,31 +5558,31 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="AA32">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB32">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AC32">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="O33">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="P33">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK33">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.81</v>
+      </c>
+      <c r="AB34">
+        <v>1.95</v>
+      </c>
+      <c r="AC34">
+        <v>2.66</v>
+      </c>
+      <c r="AD34">
+        <v>1.41</v>
+      </c>
+      <c r="AE34">
         <v>1.12</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.25</v>
-      </c>
-      <c r="Z34">
-        <v>3.82</v>
-      </c>
-      <c r="AA34">
-        <v>1.79</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.83</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>2.45</v>
+        <v>3.16</v>
       </c>
       <c r="Q35">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
+        <v>2.17</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.61</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.19</v>
+      </c>
+      <c r="Z35">
+        <v>3.74</v>
+      </c>
+      <c r="AA35">
+        <v>1.73</v>
+      </c>
+      <c r="AB35">
+        <v>1.99</v>
+      </c>
+      <c r="AC35">
+        <v>2.7</v>
+      </c>
+      <c r="AD35">
+        <v>1.35</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
         <v>2.2</v>
       </c>
-      <c r="S35">
-        <v>1.31</v>
-      </c>
-      <c r="T35">
-        <v>3.2</v>
-      </c>
-      <c r="U35">
-        <v>2.57</v>
-      </c>
-      <c r="V35">
-        <v>1.43</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1</v>
-      </c>
-      <c r="Y35">
-        <v>1.23</v>
-      </c>
-      <c r="Z35">
-        <v>3.42</v>
-      </c>
-      <c r="AA35">
-        <v>1.88</v>
-      </c>
-      <c r="AB35">
-        <v>1.88</v>
-      </c>
-      <c r="AC35">
-        <v>3.08</v>
-      </c>
-      <c r="AD35">
-        <v>1.28</v>
-      </c>
-      <c r="AE35">
-        <v>1.06</v>
-      </c>
-      <c r="AF35">
-        <v>1.67</v>
-      </c>
-      <c r="AG35">
-        <v>2.05</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>4.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
         <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="O43">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>3.79</v>
       </c>
       <c r="R43">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.36</v>
+      </c>
+      <c r="Z43">
+        <v>2.92</v>
+      </c>
+      <c r="AA43">
+        <v>2.28</v>
+      </c>
+      <c r="AB43">
+        <v>1.61</v>
+      </c>
+      <c r="AC43">
+        <v>3.96</v>
+      </c>
+      <c r="AD43">
+        <v>1.17</v>
+      </c>
+      <c r="AE43">
         <v>1.02</v>
       </c>
-      <c r="Y43">
-        <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>4.7</v>
-      </c>
-      <c r="AA43">
-        <v>1.53</v>
-      </c>
-      <c r="AB43">
-        <v>2.21</v>
-      </c>
-      <c r="AC43">
-        <v>2.4</v>
-      </c>
-      <c r="AD43">
-        <v>1.53</v>
-      </c>
-      <c r="AE43">
-        <v>1.17</v>
-      </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="O44">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="P44">
-        <v>3.03</v>
+        <v>2.53</v>
       </c>
       <c r="Q44">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AC44">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AD44">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE44">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>4.03</v>
+        <v>2.16</v>
       </c>
       <c r="O45">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="P45">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q45">
-        <v>4.36</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA45">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB45">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AC45">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,68 +7803,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P46">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="Q46">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB46">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD46">
         <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
+        <v>1.25</v>
+      </c>
+      <c r="AK46">
         <v>1.22</v>
-      </c>
-      <c r="AK46">
-        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="O47">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
+        <v>2.09</v>
+      </c>
+      <c r="Q47">
         <v>3.6</v>
-      </c>
-      <c r="Q47">
-        <v>2.3</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V47">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA47">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AB47">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AC47">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,68 +8129,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="O48">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
       <c r="P48">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V48">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="W48">
+        <v>1.12</v>
+      </c>
+      <c r="X48">
         <v>1.03</v>
       </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AC48">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE48">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,68 +8292,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
-        <v>3.11</v>
+        <v>2.28</v>
       </c>
       <c r="O49">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="P49">
-        <v>2.14</v>
+        <v>2.89</v>
       </c>
       <c r="Q49">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
+        <v>1.08</v>
+      </c>
+      <c r="X49">
+        <v>1.04</v>
+      </c>
+      <c r="Y49">
+        <v>1.21</v>
+      </c>
+      <c r="Z49">
+        <v>3.88</v>
+      </c>
+      <c r="AA49">
+        <v>1.73</v>
+      </c>
+      <c r="AB49">
+        <v>2.1</v>
+      </c>
+      <c r="AC49">
+        <v>2.74</v>
+      </c>
+      <c r="AD49">
+        <v>1.35</v>
+      </c>
+      <c r="AE49">
         <v>1.1</v>
       </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.2</v>
-      </c>
-      <c r="Z49">
-        <v>3.7</v>
-      </c>
-      <c r="AA49">
-        <v>1.64</v>
-      </c>
-      <c r="AB49">
-        <v>2.14</v>
-      </c>
-      <c r="AC49">
-        <v>2.56</v>
-      </c>
-      <c r="AD49">
-        <v>1.4</v>
-      </c>
-      <c r="AE49">
-        <v>1.14</v>
-      </c>
       <c r="AF49">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,68 +8455,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="O50">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="P50">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="Q50">
+        <v>2.96</v>
+      </c>
+      <c r="R50">
+        <v>2.02</v>
+      </c>
+      <c r="S50">
+        <v>1.39</v>
+      </c>
+      <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.88</v>
       </c>
-      <c r="R50">
-        <v>2.2</v>
-      </c>
-      <c r="S50">
-        <v>1.29</v>
-      </c>
-      <c r="T50">
-        <v>3.3</v>
-      </c>
-      <c r="U50">
-        <v>2.55</v>
-      </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="AA50">
+        <v>2</v>
+      </c>
+      <c r="AB50">
+        <v>1.83</v>
+      </c>
+      <c r="AC50">
+        <v>3.2</v>
+      </c>
+      <c r="AD50">
+        <v>1.3</v>
+      </c>
+      <c r="AE50">
+        <v>1.06</v>
+      </c>
+      <c r="AF50">
         <v>1.73</v>
       </c>
-      <c r="AB50">
-        <v>2.1</v>
-      </c>
-      <c r="AC50">
-        <v>2.74</v>
-      </c>
-      <c r="AD50">
-        <v>1.35</v>
-      </c>
-      <c r="AE50">
-        <v>1.1</v>
-      </c>
-      <c r="AF50">
-        <v>1.58</v>
-      </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P53">
-        <v>3.33</v>
+        <v>1.75</v>
       </c>
       <c r="Q53">
-        <v>2.15</v>
+        <v>3.98</v>
       </c>
       <c r="R53">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="S53">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="V53">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="W53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA53">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB53">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="AC53">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD53">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AE53">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AG53">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.92</v>
       </c>
       <c r="AK53">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="O54">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="P54">
-        <v>15.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q54">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="R54">
-        <v>3.74</v>
+        <v>2.55</v>
       </c>
       <c r="S54">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T54">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="U54">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V54">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="W54">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA54">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AB54">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC54">
+        <v>1.7</v>
+      </c>
+      <c r="AD54">
+        <v>1.99</v>
+      </c>
+      <c r="AE54">
         <v>1.44</v>
       </c>
-      <c r="AD54">
-        <v>2.42</v>
-      </c>
-      <c r="AE54">
-        <v>1.67</v>
-      </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AG54">
-        <v>2.32</v>
+        <v>3.24</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.62</v>
+        <v>1.11</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="P55">
-        <v>2.62</v>
+        <v>15.5</v>
       </c>
       <c r="Q55">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>3.74</v>
       </c>
       <c r="S55">
+        <v>1.08</v>
+      </c>
+      <c r="T55">
+        <v>6.5</v>
+      </c>
+      <c r="U55">
+        <v>1.58</v>
+      </c>
+      <c r="V55">
+        <v>2.19</v>
+      </c>
+      <c r="W55">
+        <v>1.36</v>
+      </c>
+      <c r="X55">
+        <v>1</v>
+      </c>
+      <c r="Y55">
+        <v>1.01</v>
+      </c>
+      <c r="Z55">
+        <v>10</v>
+      </c>
+      <c r="AA55">
+        <v>1.14</v>
+      </c>
+      <c r="AB55">
+        <v>4.8</v>
+      </c>
+      <c r="AC55">
         <v>1.44</v>
       </c>
-      <c r="T55">
-        <v>2.6</v>
-      </c>
-      <c r="U55">
-        <v>2.97</v>
-      </c>
-      <c r="V55">
-        <v>1.29</v>
-      </c>
-      <c r="W55">
-        <v>1.03</v>
-      </c>
-      <c r="X55">
-        <v>1.03</v>
-      </c>
-      <c r="Y55">
-        <v>1.36</v>
-      </c>
-      <c r="Z55">
-        <v>2.96</v>
-      </c>
-      <c r="AA55">
-        <v>2.25</v>
-      </c>
-      <c r="AB55">
-        <v>1.55</v>
-      </c>
-      <c r="AC55">
-        <v>3.92</v>
-      </c>
       <c r="AD55">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="AE55">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AF55">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="O56">
-        <v>3.67</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>4.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q56">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S56">
+        <v>1.44</v>
+      </c>
+      <c r="T56">
+        <v>2.6</v>
+      </c>
+      <c r="U56">
+        <v>2.97</v>
+      </c>
+      <c r="V56">
+        <v>1.29</v>
+      </c>
+      <c r="W56">
+        <v>1.03</v>
+      </c>
+      <c r="X56">
+        <v>1.03</v>
+      </c>
+      <c r="Y56">
         <v>1.36</v>
       </c>
-      <c r="T56">
-        <v>2.92</v>
-      </c>
-      <c r="U56">
-        <v>2.63</v>
-      </c>
-      <c r="V56">
-        <v>1.41</v>
-      </c>
-      <c r="W56">
-        <v>1.08</v>
-      </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56">
-        <v>1.3</v>
-      </c>
       <c r="Z56">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="AA56">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AC56">
-        <v>2.92</v>
+        <v>3.92</v>
       </c>
       <c r="AD56">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
         <v>1.83</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AK56">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-03 11:15:00</t>
+          <t>2026-10-03 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-03 11:30:00</t>
+          <t>2026-10-03 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P63">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q63">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="R63">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T63">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="U63">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V63">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>4.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA63">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AB63">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="AC63">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="AD63">
+        <v>1.63</v>
+      </c>
+      <c r="AE63">
+        <v>1.22</v>
+      </c>
+      <c r="AF63">
         <v>1.41</v>
       </c>
-      <c r="AE63">
-        <v>1.12</v>
-      </c>
-      <c r="AF63">
-        <v>1.55</v>
-      </c>
       <c r="AG63">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-03 11:30:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G67">
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,68 +11389,68 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-03 12:30:00</t>
+          <t>2026-10-03 12:00:00</t>
         </is>
       </c>
     </row>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,68 +11552,68 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-03 13:00:00</t>
+          <t>2026-10-03 12:30:00</t>
         </is>
       </c>
     </row>
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G79">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-10-03 13:30:00</t>
+          <t>2026-10-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="O81">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="P81">
-        <v>2.84</v>
+        <v>3.67</v>
       </c>
       <c r="Q81">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y81">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA81">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB81">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC81">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK81">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-03 13:45:00</t>
+          <t>2026-10-03 13:30:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-03 14:00:00</t>
+          <t>2026-10-03 13:45:00</t>
         </is>
       </c>
     </row>
@@ -13954,27 +13954,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G84">
@@ -13997,68 +13997,68 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N84">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-03 15:00:00</t>
+          <t>2026-10-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q85">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U85">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="V85">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="AA85">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AB85">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC85">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD85">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G86">
@@ -14323,68 +14323,68 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N86">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O86">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>4.27</v>
+        <v>3.3</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y86">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z86">
+        <v>2.91</v>
+      </c>
+      <c r="AA86">
         <v>2.15</v>
       </c>
-      <c r="AA86">
-        <v>0</v>
-      </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O87">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P87">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14526,7 +14526,7 @@
         <v>1.6</v>
       </c>
       <c r="Z87">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O88">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="P88">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14686,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z88">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
+        <v>2.25</v>
+      </c>
+      <c r="O89">
         <v>2.55</v>
       </c>
-      <c r="O89">
-        <v>2.7</v>
-      </c>
       <c r="P89">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,14 +14979,14 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O90">
+        <v>2.7</v>
+      </c>
+      <c r="P90">
         <v>2.95</v>
       </c>
-      <c r="P90">
-        <v>3.2</v>
-      </c>
       <c r="Q90">
         <v>0</v>
       </c>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Z90">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O91">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P91">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15175,10 +15175,10 @@
         <v>0</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S94">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T94">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U94">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD94">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK94">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G95">
@@ -15797,61 +15797,61 @@
         <v>1.91</v>
       </c>
       <c r="O95">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P95">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q95">
         <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S95">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U95">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="V95">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="W95">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z95">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA95">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB95">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AC95">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AD95">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF95">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG95">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
+        <v>1.91</v>
+      </c>
+      <c r="O96">
+        <v>3.7</v>
+      </c>
+      <c r="P96">
+        <v>3.1</v>
+      </c>
+      <c r="Q96">
+        <v>2.4</v>
+      </c>
+      <c r="R96">
+        <v>2.5</v>
+      </c>
+      <c r="S96">
+        <v>1.2</v>
+      </c>
+      <c r="T96">
+        <v>4</v>
+      </c>
+      <c r="U96">
+        <v>2.1</v>
+      </c>
+      <c r="V96">
+        <v>1.69</v>
+      </c>
+      <c r="W96">
+        <v>1.18</v>
+      </c>
+      <c r="X96">
+        <v>1.02</v>
+      </c>
+      <c r="Y96">
+        <v>1.11</v>
+      </c>
+      <c r="Z96">
+        <v>5.75</v>
+      </c>
+      <c r="AA96">
+        <v>1.39</v>
+      </c>
+      <c r="AB96">
+        <v>2.59</v>
+      </c>
+      <c r="AC96">
+        <v>2.06</v>
+      </c>
+      <c r="AD96">
+        <v>1.7</v>
+      </c>
+      <c r="AE96">
+        <v>1.25</v>
+      </c>
+      <c r="AF96">
+        <v>1.39</v>
+      </c>
+      <c r="AG96">
+        <v>2.77</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.2</v>
+      </c>
+      <c r="AK96">
         <v>1.8</v>
-      </c>
-      <c r="O96">
-        <v>3.8</v>
-      </c>
-      <c r="P96">
-        <v>3.3</v>
-      </c>
-      <c r="Q96">
-        <v>2.3</v>
-      </c>
-      <c r="R96">
-        <v>2.51</v>
-      </c>
-      <c r="S96">
-        <v>1.15</v>
-      </c>
-      <c r="T96">
-        <v>4.3</v>
-      </c>
-      <c r="U96">
-        <v>1.97</v>
-      </c>
-      <c r="V96">
-        <v>1.75</v>
-      </c>
-      <c r="W96">
-        <v>1.22</v>
-      </c>
-      <c r="X96">
-        <v>1.01</v>
-      </c>
-      <c r="Y96">
-        <v>1.07</v>
-      </c>
-      <c r="Z96">
-        <v>7</v>
-      </c>
-      <c r="AA96">
-        <v>1.32</v>
-      </c>
-      <c r="AB96">
-        <v>2.88</v>
-      </c>
-      <c r="AC96">
-        <v>1.89</v>
-      </c>
-      <c r="AD96">
-        <v>1.84</v>
-      </c>
-      <c r="AE96">
-        <v>1.32</v>
-      </c>
-      <c r="AF96">
-        <v>1.35</v>
-      </c>
-      <c r="AG96">
-        <v>2.9</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.18</v>
-      </c>
-      <c r="AK96">
-        <v>1.87</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,65 +16120,65 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.82</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
         <v>3.8</v>
       </c>
       <c r="P97">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q97">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="R97">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S97">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T97">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U97">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V97">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W97">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA97">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB97">
+        <v>2.88</v>
+      </c>
+      <c r="AC97">
+        <v>1.89</v>
+      </c>
+      <c r="AD97">
+        <v>1.84</v>
+      </c>
+      <c r="AE97">
+        <v>1.32</v>
+      </c>
+      <c r="AF97">
+        <v>1.35</v>
+      </c>
+      <c r="AG97">
         <v>2.9</v>
       </c>
-      <c r="AC97">
-        <v>1.99</v>
-      </c>
-      <c r="AD97">
-        <v>1.75</v>
-      </c>
-      <c r="AE97">
-        <v>1.33</v>
-      </c>
-      <c r="AF97">
-        <v>1.33</v>
-      </c>
-      <c r="AG97">
-        <v>3</v>
-      </c>
       <c r="AH97" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-03 15:30:00</t>
+          <t>2026-10-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G102">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-03 15:45:00</t>
+          <t>2026-10-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-03 16:00:00</t>
+          <t>2026-10-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-03 17:00:00</t>
+          <t>2026-10-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G118">
@@ -19539,68 +19539,68 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N118">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S118">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T118">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U118">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z118">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA118">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD118">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE118">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF118">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK118">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-03 17:30:00</t>
+          <t>2026-10-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O119">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P119">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="Q119">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S119">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T119">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U119">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V119">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X119">
         <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z119">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA119">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB119">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC119">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD119">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE119">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF119">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG119">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK119">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-03 18:30:00</t>
+          <t>2026-10-03 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G120">
@@ -19865,68 +19865,68 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="O121">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-10-03 19:30:00</t>
+          <t>2026-10-03 19:00:00</t>
         </is>
       </c>
     </row>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G125">
@@ -20680,68 +20680,68 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N125">
-        <v>2.97</v>
+        <v>1.43</v>
       </c>
       <c r="O125">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="P125">
-        <v>2.22</v>
+        <v>5.65</v>
       </c>
       <c r="Q125">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-03 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G126">
@@ -20843,68 +20843,68 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N126">
-        <v>4.13</v>
+        <v>2.97</v>
       </c>
       <c r="O126">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P126">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>4.13</v>
       </c>
       <c r="O127">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P127">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O128">
-        <v>3.78</v>
+        <v>3.46</v>
       </c>
       <c r="P128">
-        <v>5.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="O129">
-        <v>4.15</v>
+        <v>3.78</v>
       </c>
       <c r="P129">
-        <v>7.37</v>
+        <v>5.05</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-10-03 20:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21452,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.72</v>
+        <v>1.37</v>
       </c>
       <c r="O130">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="P130">
-        <v>2.34</v>
+        <v>7.37</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-03 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21778,27 +21778,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>2.97</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>1.43</v>
+      </c>
+      <c r="T132">
+        <v>2.72</v>
+      </c>
+      <c r="U132">
+        <v>3.19</v>
+      </c>
+      <c r="V132">
+        <v>1.33</v>
+      </c>
+      <c r="W132">
+        <v>1.03</v>
+      </c>
+      <c r="X132">
+        <v>1.03</v>
+      </c>
+      <c r="Y132">
+        <v>1.36</v>
+      </c>
+      <c r="Z132">
         <v>3.01</v>
       </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-10-03 21:45:00</t>
+          <t>2026-10-03 21:00:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="O133">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="P133">
-        <v>4.24</v>
+        <v>3.01</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-10-03 22:00:00</t>
+          <t>2026-10-03 21:45:00</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
       <c r="O134">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="P134">
-        <v>2.76</v>
+        <v>4.24</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-10-03 23:00:00</t>
+          <t>2026-10-03 22:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,156 +22267,319 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N135">
+        <v>2.21</v>
+      </c>
+      <c r="O135">
+        <v>3.44</v>
+      </c>
+      <c r="P135">
+        <v>2.76</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>-1</v>
+      </c>
+      <c r="AN135">
+        <v>-1</v>
+      </c>
+      <c r="AO135">
+        <v>-1</v>
+      </c>
+      <c r="AP135">
+        <v>-1</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>2026-10-03 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N135">
+      <c r="N136">
         <v>2.22</v>
       </c>
-      <c r="O135">
+      <c r="O136">
         <v>3.26</v>
       </c>
-      <c r="P135">
+      <c r="P136">
         <v>2.87</v>
       </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
         <v>2.03</v>
       </c>
-      <c r="AB135">
+      <c r="AB136">
         <v>1.78</v>
       </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>0</v>
+      </c>
+      <c r="AG136">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>0</v>
+      </c>
+      <c r="AM136">
+        <v>-1</v>
+      </c>
+      <c r="AN136">
+        <v>-1</v>
+      </c>
+      <c r="AO136">
+        <v>-1</v>
+      </c>
+      <c r="AP136">
+        <v>-1</v>
+      </c>
+      <c r="AQ136">
+        <v>0</v>
+      </c>
+      <c r="AR136">
+        <v>0</v>
+      </c>
+      <c r="AS136">
+        <v>0</v>
+      </c>
+      <c r="AT136">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
         <is>
           <t>2026-10-03 23:30:00</t>
         </is>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O22">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q22">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R22">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V22">
         <v>1.55</v>
@@ -3925,50 +3925,50 @@
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
         <v>4.38</v>
       </c>
       <c r="AA22">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB22">
+        <v>1.97</v>
+      </c>
+      <c r="AC22">
+        <v>2.38</v>
+      </c>
+      <c r="AD22">
+        <v>1.46</v>
+      </c>
+      <c r="AE22">
+        <v>1.16</v>
+      </c>
+      <c r="AF22">
+        <v>1.6</v>
+      </c>
+      <c r="AG22">
+        <v>2.25</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.16</v>
+      </c>
+      <c r="AK22">
         <v>1.96</v>
-      </c>
-      <c r="AC22">
-        <v>2.49</v>
-      </c>
-      <c r="AD22">
-        <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
-      <c r="AF22">
-        <v>1.53</v>
-      </c>
-      <c r="AG22">
-        <v>2.32</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.33</v>
-      </c>
-      <c r="AK22">
-        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>2.93</v>
+        <v>4.73</v>
       </c>
       <c r="Q36">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
+        <v>1.83</v>
+      </c>
+      <c r="AB36">
         <v>1.94</v>
       </c>
-      <c r="AB36">
-        <v>1.83</v>
-      </c>
       <c r="AC36">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
         <v>3.42</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
+        <v>3.08</v>
+      </c>
+      <c r="AA37">
+        <v>1.94</v>
+      </c>
+      <c r="AB37">
+        <v>1.83</v>
+      </c>
+      <c r="AC37">
+        <v>3.28</v>
+      </c>
+      <c r="AD37">
         <v>1.25</v>
       </c>
-      <c r="Z37">
-        <v>3.82</v>
-      </c>
-      <c r="AA37">
-        <v>1.79</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.83</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,68 +7803,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
-        <v>4.03</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="Q46">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA46">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB46">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
         <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="O47">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="P47">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q47">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="O48">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="Q48">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="V48">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
       <c r="AD48">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
+        <v>1.58</v>
+      </c>
+      <c r="AG48">
+        <v>2.2</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.22</v>
+      </c>
+      <c r="AK48">
         <v>1.57</v>
-      </c>
-      <c r="AG48">
-        <v>2.26</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.23</v>
-      </c>
-      <c r="AK48">
-        <v>1.95</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,68 +8292,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
-        <v>2.28</v>
+        <v>3.11</v>
       </c>
       <c r="O49">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="P49">
-        <v>2.89</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U49">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AA49">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AB49">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.27</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>3.19</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>2.96</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
+        <v>1.81</v>
+      </c>
+      <c r="AB50">
+        <v>1.99</v>
+      </c>
+      <c r="AC50">
+        <v>2.83</v>
+      </c>
+      <c r="AD50">
+        <v>1.36</v>
+      </c>
+      <c r="AE50">
+        <v>1.08</v>
+      </c>
+      <c r="AF50">
+        <v>1.71</v>
+      </c>
+      <c r="AG50">
         <v>2</v>
       </c>
-      <c r="AB50">
-        <v>1.83</v>
-      </c>
-      <c r="AC50">
-        <v>3.2</v>
-      </c>
-      <c r="AD50">
-        <v>1.3</v>
-      </c>
-      <c r="AE50">
-        <v>1.06</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>1.98</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>2.27</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
+        <v>1.73</v>
+      </c>
+      <c r="AG51">
+        <v>1.98</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.31</v>
+      </c>
+      <c r="AK51">
         <v>1.56</v>
-      </c>
-      <c r="AG51">
-        <v>2.24</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.26</v>
-      </c>
-      <c r="AK51">
-        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="O104">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P104">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q104">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="R104">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T104">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="U104">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W104">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="Z104">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA104">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB104">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AC104">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="AD104">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK104">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O105">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q105">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R105">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U105">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="AA105">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC105">
-        <v>3.67</v>
+        <v>3.04</v>
       </c>
       <c r="AD105">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG105">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="O106">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P106">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q106">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R106">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U106">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="V106">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
         <v>1.03</v>
       </c>
       <c r="Y106">
+        <v>1.16</v>
+      </c>
+      <c r="Z106">
+        <v>4.1</v>
+      </c>
+      <c r="AA106">
+        <v>1.65</v>
+      </c>
+      <c r="AB106">
+        <v>2.06</v>
+      </c>
+      <c r="AC106">
+        <v>2.56</v>
+      </c>
+      <c r="AD106">
         <v>1.4</v>
       </c>
-      <c r="Z106">
-        <v>2.7</v>
-      </c>
-      <c r="AA106">
-        <v>2.2</v>
-      </c>
-      <c r="AB106">
-        <v>1.58</v>
-      </c>
-      <c r="AC106">
-        <v>4.05</v>
-      </c>
-      <c r="AD106">
-        <v>1.17</v>
-      </c>
       <c r="AE106">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG106">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK106">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="O107">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P107">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q107">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S107">
+        <v>1.33</v>
+      </c>
+      <c r="T107">
+        <v>3</v>
+      </c>
+      <c r="U107">
+        <v>2.72</v>
+      </c>
+      <c r="V107">
+        <v>1.36</v>
+      </c>
+      <c r="W107">
+        <v>1.06</v>
+      </c>
+      <c r="X107">
+        <v>1.01</v>
+      </c>
+      <c r="Y107">
         <v>1.3</v>
       </c>
-      <c r="T107">
-        <v>2.95</v>
-      </c>
-      <c r="U107">
-        <v>2.55</v>
-      </c>
-      <c r="V107">
-        <v>1.44</v>
-      </c>
-      <c r="W107">
-        <v>1.07</v>
-      </c>
-      <c r="X107">
-        <v>1</v>
-      </c>
-      <c r="Y107">
-        <v>1.26</v>
-      </c>
       <c r="Z107">
-        <v>3.66</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
+        <v>1.86</v>
+      </c>
+      <c r="AB107">
         <v>1.81</v>
       </c>
-      <c r="AB107">
-        <v>1.86</v>
-      </c>
       <c r="AC107">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG107">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK107">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="O108">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P108">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q108">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R108">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T108">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U108">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V108">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W108">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z108">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB108">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AC108">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE108">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF108">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK108">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="O109">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P109">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q109">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="R109">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T109">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U109">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="V109">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z109">
+        <v>3.14</v>
+      </c>
+      <c r="AA109">
+        <v>2</v>
+      </c>
+      <c r="AB109">
+        <v>1.8</v>
+      </c>
+      <c r="AC109">
         <v>3.34</v>
       </c>
-      <c r="AA109">
+      <c r="AD109">
+        <v>1.24</v>
+      </c>
+      <c r="AE109">
+        <v>1.04</v>
+      </c>
+      <c r="AF109">
         <v>1.86</v>
       </c>
-      <c r="AB109">
-        <v>1.81</v>
-      </c>
-      <c r="AC109">
-        <v>3.3</v>
-      </c>
-      <c r="AD109">
-        <v>1.31</v>
-      </c>
-      <c r="AE109">
-        <v>1.1</v>
-      </c>
-      <c r="AF109">
-        <v>2</v>
-      </c>
       <c r="AG109">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,40 +18239,40 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
         <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
         <v>3.5</v>
@@ -18284,19 +18284,19 @@
         <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
         <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
         <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.34</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -19389,55 +19389,55 @@
         <v>1.78</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20204,55 +20204,55 @@
         <v>2.94</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20693,55 +20693,55 @@
         <v>5.65</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.13</v>
+        <v>2</v>
       </c>
       <c r="O127">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P127">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2</v>
+        <v>4.13</v>
       </c>
       <c r="O128">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P128">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,34 +21345,34 @@
         <v>5.05</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA129">
         <v>1.8</v>
@@ -21381,19 +21381,19 @@
         <v>2</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,55 +21508,55 @@
         <v>7.37</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21671,55 +21671,55 @@
         <v>2.34</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22160,55 +22160,55 @@
         <v>4.24</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>2.76</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22486,34 +22486,34 @@
         <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA136">
         <v>2.03</v>
@@ -22522,19 +22522,19 @@
         <v>1.78</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL136">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>6.77</v>
+        <v>1.66</v>
       </c>
       <c r="Q26">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U26">
         <v>2.68</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
+        <v>1.27</v>
+      </c>
+      <c r="Z26">
+        <v>3.19</v>
+      </c>
+      <c r="AA26">
+        <v>2.02</v>
+      </c>
+      <c r="AB26">
+        <v>1.77</v>
+      </c>
+      <c r="AC26">
+        <v>3.34</v>
+      </c>
+      <c r="AD26">
         <v>1.24</v>
       </c>
-      <c r="Z26">
-        <v>3.34</v>
-      </c>
-      <c r="AA26">
-        <v>1.85</v>
-      </c>
-      <c r="AB26">
-        <v>1.9</v>
-      </c>
-      <c r="AC26">
-        <v>3.19</v>
-      </c>
-      <c r="AD26">
-        <v>1.3</v>
-      </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>2.75</v>
+        <v>1.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>1.66</v>
+        <v>6.77</v>
       </c>
       <c r="Q27">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
         <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.85</v>
+      </c>
+      <c r="AB27">
+        <v>1.9</v>
+      </c>
+      <c r="AC27">
         <v>3.19</v>
       </c>
-      <c r="AA27">
-        <v>2.02</v>
-      </c>
-      <c r="AB27">
-        <v>1.77</v>
-      </c>
-      <c r="AC27">
-        <v>3.34</v>
-      </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>1.1</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
+        <v>2.91</v>
+      </c>
+      <c r="U36">
+        <v>2.88</v>
+      </c>
+      <c r="V36">
+        <v>1.36</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
         <v>3.08</v>
       </c>
-      <c r="U36">
-        <v>2.48</v>
-      </c>
-      <c r="V36">
-        <v>1.46</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.26</v>
-      </c>
-      <c r="Z36">
-        <v>3.58</v>
-      </c>
       <c r="AA36">
+        <v>1.94</v>
+      </c>
+      <c r="AB36">
         <v>1.83</v>
       </c>
-      <c r="AB36">
-        <v>1.94</v>
-      </c>
       <c r="AC36">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
         <v>3.42</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>2.27</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>3.19</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>2.96</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S50">
+        <v>1.39</v>
+      </c>
+      <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
+        <v>2.88</v>
+      </c>
+      <c r="V50">
+        <v>1.35</v>
+      </c>
+      <c r="W50">
+        <v>1.03</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
         <v>1.3</v>
       </c>
-      <c r="T50">
-        <v>3.1</v>
-      </c>
-      <c r="U50">
-        <v>2.49</v>
-      </c>
-      <c r="V50">
-        <v>1.44</v>
-      </c>
-      <c r="W50">
-        <v>1.08</v>
-      </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,65 +8622,65 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.27</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>3.19</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>2.96</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
+        <v>1.81</v>
+      </c>
+      <c r="AB51">
+        <v>1.99</v>
+      </c>
+      <c r="AC51">
+        <v>2.83</v>
+      </c>
+      <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.08</v>
+      </c>
+      <c r="AF51">
+        <v>1.71</v>
+      </c>
+      <c r="AG51">
         <v>2</v>
       </c>
-      <c r="AB51">
-        <v>1.83</v>
-      </c>
-      <c r="AC51">
-        <v>3.2</v>
-      </c>
-      <c r="AD51">
-        <v>1.3</v>
-      </c>
-      <c r="AE51">
-        <v>1.06</v>
-      </c>
-      <c r="AF51">
-        <v>1.73</v>
-      </c>
-      <c r="AG51">
-        <v>1.98</v>
-      </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.45</v>
+        <v>1.46</v>
       </c>
       <c r="O106">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q106">
+        <v>1.97</v>
+      </c>
+      <c r="R106">
+        <v>2.36</v>
+      </c>
+      <c r="S106">
+        <v>1.33</v>
+      </c>
+      <c r="T106">
         <v>3</v>
       </c>
-      <c r="R106">
-        <v>2.25</v>
-      </c>
-      <c r="S106">
-        <v>1.29</v>
-      </c>
-      <c r="T106">
+      <c r="U106">
+        <v>2.72</v>
+      </c>
+      <c r="V106">
+        <v>1.36</v>
+      </c>
+      <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>1.01</v>
+      </c>
+      <c r="Y106">
+        <v>1.3</v>
+      </c>
+      <c r="Z106">
+        <v>3.34</v>
+      </c>
+      <c r="AA106">
+        <v>1.86</v>
+      </c>
+      <c r="AB106">
+        <v>1.81</v>
+      </c>
+      <c r="AC106">
         <v>3.3</v>
       </c>
-      <c r="U106">
-        <v>2.44</v>
-      </c>
-      <c r="V106">
-        <v>1.5</v>
-      </c>
-      <c r="W106">
-        <v>1.11</v>
-      </c>
-      <c r="X106">
-        <v>1.03</v>
-      </c>
-      <c r="Y106">
-        <v>1.16</v>
-      </c>
-      <c r="Z106">
-        <v>4.1</v>
-      </c>
-      <c r="AA106">
-        <v>1.65</v>
-      </c>
-      <c r="AB106">
-        <v>2.06</v>
-      </c>
-      <c r="AC106">
-        <v>2.56</v>
-      </c>
       <c r="AD106">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE106">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG106">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK106">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="O107">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q107">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="R107">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T107">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U107">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z107">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA107">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB107">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AD107">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE107">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF107">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="O108">
         <v>3.65</v>
       </c>
       <c r="P108">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q108">
         <v>2.25</v>
       </c>
       <c r="R108">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T108">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U108">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA108">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB108">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC108">
-        <v>2.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD108">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG108">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O109">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P109">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q109">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R109">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S109">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
+        <v>2.83</v>
+      </c>
+      <c r="U109">
+        <v>2.5</v>
+      </c>
+      <c r="V109">
+        <v>1.44</v>
+      </c>
+      <c r="W109">
+        <v>1.07</v>
+      </c>
+      <c r="X109">
+        <v>1</v>
+      </c>
+      <c r="Y109">
+        <v>1.23</v>
+      </c>
+      <c r="Z109">
+        <v>3.5</v>
+      </c>
+      <c r="AA109">
+        <v>1.75</v>
+      </c>
+      <c r="AB109">
+        <v>1.93</v>
+      </c>
+      <c r="AC109">
         <v>2.89</v>
       </c>
-      <c r="U109">
-        <v>2.97</v>
-      </c>
-      <c r="V109">
-        <v>1.37</v>
-      </c>
-      <c r="W109">
-        <v>1.05</v>
-      </c>
-      <c r="X109">
-        <v>1.02</v>
-      </c>
-      <c r="Y109">
-        <v>1.27</v>
-      </c>
-      <c r="Z109">
-        <v>3.14</v>
-      </c>
-      <c r="AA109">
-        <v>2</v>
-      </c>
-      <c r="AB109">
-        <v>1.8</v>
-      </c>
-      <c r="AC109">
-        <v>3.34</v>
-      </c>
       <c r="AD109">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE109">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG109">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>2.56</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P22">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q22">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R22">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
         <v>1.55</v>
@@ -3925,34 +3925,34 @@
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
         <v>4.38</v>
       </c>
       <c r="AA22">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB22">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC22">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="Q23">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.17</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23">
+        <v>1.64</v>
+      </c>
+      <c r="AB23">
+        <v>2.08</v>
+      </c>
+      <c r="AC23">
+        <v>2.62</v>
+      </c>
+      <c r="AD23">
+        <v>1.38</v>
+      </c>
+      <c r="AE23">
         <v>1.16</v>
       </c>
-      <c r="Z23">
-        <v>4.38</v>
-      </c>
-      <c r="AA23">
-        <v>1.81</v>
-      </c>
-      <c r="AB23">
-        <v>1.96</v>
-      </c>
-      <c r="AC23">
-        <v>2.49</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
-      <c r="AE23">
-        <v>1.13</v>
-      </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>2.74</v>
+        <v>4.83</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P28">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q28">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.25</v>
+      </c>
+      <c r="Z34">
+        <v>3.82</v>
+      </c>
+      <c r="AA34">
+        <v>1.79</v>
+      </c>
+      <c r="AB34">
+        <v>2.15</v>
+      </c>
+      <c r="AC34">
+        <v>2.83</v>
+      </c>
+      <c r="AD34">
+        <v>1.33</v>
+      </c>
+      <c r="AE34">
         <v>1.09</v>
       </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.19</v>
-      </c>
-      <c r="Z34">
-        <v>3.74</v>
-      </c>
-      <c r="AA34">
-        <v>1.73</v>
-      </c>
-      <c r="AB34">
-        <v>1.99</v>
-      </c>
-      <c r="AC34">
-        <v>2.7</v>
-      </c>
-      <c r="AD34">
-        <v>1.35</v>
-      </c>
-      <c r="AE34">
-        <v>1.11</v>
-      </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="O35">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="P35">
-        <v>3.87</v>
+        <v>4.73</v>
       </c>
       <c r="Q35">
         <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC35">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="AD35">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
         <v>2.05</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
+        <v>2.17</v>
+      </c>
+      <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.14</v>
+      </c>
+      <c r="U36">
+        <v>2.61</v>
+      </c>
+      <c r="V36">
+        <v>1.45</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.19</v>
+      </c>
+      <c r="Z36">
+        <v>3.74</v>
+      </c>
+      <c r="AA36">
+        <v>1.73</v>
+      </c>
+      <c r="AB36">
+        <v>1.99</v>
+      </c>
+      <c r="AC36">
+        <v>2.7</v>
+      </c>
+      <c r="AD36">
+        <v>1.35</v>
+      </c>
+      <c r="AE36">
+        <v>1.11</v>
+      </c>
+      <c r="AF36">
+        <v>1.6</v>
+      </c>
+      <c r="AG36">
         <v>2.2</v>
       </c>
-      <c r="S36">
-        <v>1.38</v>
-      </c>
-      <c r="T36">
-        <v>2.91</v>
-      </c>
-      <c r="U36">
-        <v>2.88</v>
-      </c>
-      <c r="V36">
-        <v>1.36</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.28</v>
-      </c>
-      <c r="Z36">
-        <v>3.08</v>
-      </c>
-      <c r="AA36">
-        <v>1.94</v>
-      </c>
-      <c r="AB36">
-        <v>1.83</v>
-      </c>
-      <c r="AC36">
-        <v>3.28</v>
-      </c>
-      <c r="AD36">
-        <v>1.25</v>
-      </c>
-      <c r="AE36">
-        <v>1.1</v>
-      </c>
-      <c r="AF36">
-        <v>1.75</v>
-      </c>
-      <c r="AG36">
-        <v>1.94</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="U37">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC37">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>3.87</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q39">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>2.56</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>2.56</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G114">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="P2">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="Q2">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.39</v>
+      </c>
+      <c r="Z2">
+        <v>2.85</v>
+      </c>
+      <c r="AA2">
+        <v>2.2</v>
+      </c>
+      <c r="AB2">
+        <v>1.61</v>
+      </c>
+      <c r="AC2">
+        <v>4.19</v>
+      </c>
+      <c r="AD2">
+        <v>1.21</v>
+      </c>
+      <c r="AE2">
         <v>1.02</v>
       </c>
-      <c r="Y2">
-        <v>1.32</v>
-      </c>
-      <c r="Z2">
-        <v>3.19</v>
-      </c>
-      <c r="AA2">
-        <v>2.08</v>
-      </c>
-      <c r="AB2">
-        <v>1.73</v>
-      </c>
-      <c r="AC2">
-        <v>3.61</v>
-      </c>
-      <c r="AD2">
-        <v>1.26</v>
-      </c>
-      <c r="AE2">
-        <v>1.04</v>
-      </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="O3">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="P3">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>4.19</v>
+        <v>3.61</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
+        <v>1.17</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>1.64</v>
+      </c>
+      <c r="AB22">
+        <v>2.08</v>
+      </c>
+      <c r="AC22">
+        <v>2.62</v>
+      </c>
+      <c r="AD22">
+        <v>1.38</v>
+      </c>
+      <c r="AE22">
         <v>1.16</v>
       </c>
-      <c r="Z22">
-        <v>4.38</v>
-      </c>
-      <c r="AA22">
-        <v>1.81</v>
-      </c>
-      <c r="AB22">
-        <v>1.96</v>
-      </c>
-      <c r="AC22">
-        <v>2.49</v>
-      </c>
-      <c r="AD22">
-        <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
       <c r="AF22">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG22">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AK22">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O23">
+        <v>3.62</v>
+      </c>
+      <c r="P23">
+        <v>3.04</v>
+      </c>
+      <c r="Q23">
+        <v>2.52</v>
+      </c>
+      <c r="R23">
+        <v>2.27</v>
+      </c>
+      <c r="S23">
+        <v>1.25</v>
+      </c>
+      <c r="T23">
         <v>3.5</v>
       </c>
-      <c r="P23">
-        <v>2.74</v>
-      </c>
-      <c r="Q23">
-        <v>3.3</v>
-      </c>
-      <c r="R23">
-        <v>2.25</v>
-      </c>
-      <c r="S23">
-        <v>1.29</v>
-      </c>
-      <c r="T23">
-        <v>3.25</v>
-      </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
+        <v>1.55</v>
+      </c>
+      <c r="W23">
+        <v>1.14</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.16</v>
+      </c>
+      <c r="Z23">
+        <v>4.38</v>
+      </c>
+      <c r="AA23">
+        <v>1.81</v>
+      </c>
+      <c r="AB23">
+        <v>1.96</v>
+      </c>
+      <c r="AC23">
+        <v>2.49</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.13</v>
+      </c>
+      <c r="AF23">
         <v>1.53</v>
       </c>
-      <c r="W23">
-        <v>1.11</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.17</v>
-      </c>
-      <c r="Z23">
-        <v>4</v>
-      </c>
-      <c r="AA23">
-        <v>1.64</v>
-      </c>
-      <c r="AB23">
-        <v>2.08</v>
-      </c>
-      <c r="AC23">
-        <v>2.62</v>
-      </c>
-      <c r="AD23">
-        <v>1.38</v>
-      </c>
-      <c r="AE23">
-        <v>1.16</v>
-      </c>
-      <c r="AF23">
-        <v>1.56</v>
-      </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q34">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
         <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
+        <v>2.91</v>
+      </c>
+      <c r="U35">
+        <v>2.88</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.07</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
         <v>3.08</v>
       </c>
-      <c r="U35">
-        <v>2.48</v>
-      </c>
-      <c r="V35">
-        <v>1.46</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.26</v>
-      </c>
-      <c r="Z35">
-        <v>3.58</v>
-      </c>
       <c r="AA35">
+        <v>1.94</v>
+      </c>
+      <c r="AB35">
         <v>1.83</v>
       </c>
-      <c r="AB35">
-        <v>1.94</v>
-      </c>
       <c r="AC35">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="U36">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="V36">
+        <v>1.36</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.27</v>
+      </c>
+      <c r="Z36">
+        <v>3.42</v>
+      </c>
+      <c r="AA36">
+        <v>1.88</v>
+      </c>
+      <c r="AB36">
+        <v>1.88</v>
+      </c>
+      <c r="AC36">
+        <v>3.08</v>
+      </c>
+      <c r="AD36">
+        <v>1.28</v>
+      </c>
+      <c r="AE36">
+        <v>1.06</v>
+      </c>
+      <c r="AF36">
+        <v>1.75</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.25</v>
+      </c>
+      <c r="AK36">
         <v>1.45</v>
-      </c>
-      <c r="W36">
-        <v>1.09</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.19</v>
-      </c>
-      <c r="Z36">
-        <v>3.74</v>
-      </c>
-      <c r="AA36">
-        <v>1.73</v>
-      </c>
-      <c r="AB36">
-        <v>1.99</v>
-      </c>
-      <c r="AC36">
-        <v>2.7</v>
-      </c>
-      <c r="AD36">
-        <v>1.35</v>
-      </c>
-      <c r="AE36">
-        <v>1.11</v>
-      </c>
-      <c r="AF36">
-        <v>1.6</v>
-      </c>
-      <c r="AG36">
-        <v>2.2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.3</v>
-      </c>
-      <c r="AK36">
-        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P37">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="Q37">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O39">
         <v>3.42</v>
       </c>
       <c r="P39">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q39">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R39">
         <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA39">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB39">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC39">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="O102">
-        <v>3.66</v>
+        <v>3.06</v>
       </c>
       <c r="P102">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="Q102">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="R102">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S102">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T102">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="U102">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z102">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB102">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AD102">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
         <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O103">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="P103">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="Q103">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="R103">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="U103">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE103">
         <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="O106">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P106">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q106">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="R106">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T106">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U106">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB106">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC106">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AD106">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="O107">
         <v>3.65</v>
       </c>
       <c r="P107">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
       </c>
       <c r="R107">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S107">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="V107">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA107">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC107">
-        <v>2.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD107">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE107">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O108">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q108">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R108">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S108">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
+        <v>2.83</v>
+      </c>
+      <c r="U108">
+        <v>2.5</v>
+      </c>
+      <c r="V108">
+        <v>1.44</v>
+      </c>
+      <c r="W108">
+        <v>1.07</v>
+      </c>
+      <c r="X108">
+        <v>1</v>
+      </c>
+      <c r="Y108">
+        <v>1.23</v>
+      </c>
+      <c r="Z108">
+        <v>3.5</v>
+      </c>
+      <c r="AA108">
+        <v>1.75</v>
+      </c>
+      <c r="AB108">
+        <v>1.93</v>
+      </c>
+      <c r="AC108">
         <v>2.89</v>
       </c>
-      <c r="U108">
-        <v>2.97</v>
-      </c>
-      <c r="V108">
-        <v>1.37</v>
-      </c>
-      <c r="W108">
-        <v>1.05</v>
-      </c>
-      <c r="X108">
-        <v>1.02</v>
-      </c>
-      <c r="Y108">
-        <v>1.27</v>
-      </c>
-      <c r="Z108">
-        <v>3.14</v>
-      </c>
-      <c r="AA108">
-        <v>2</v>
-      </c>
-      <c r="AB108">
-        <v>1.8</v>
-      </c>
-      <c r="AC108">
-        <v>3.34</v>
-      </c>
       <c r="AD108">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG108">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="O109">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P109">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q109">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R109">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T109">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="U109">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V109">
+        <v>1.5</v>
+      </c>
+      <c r="W109">
+        <v>1.11</v>
+      </c>
+      <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.16</v>
+      </c>
+      <c r="Z109">
+        <v>4.1</v>
+      </c>
+      <c r="AA109">
+        <v>1.65</v>
+      </c>
+      <c r="AB109">
+        <v>2.06</v>
+      </c>
+      <c r="AC109">
+        <v>2.56</v>
+      </c>
+      <c r="AD109">
+        <v>1.4</v>
+      </c>
+      <c r="AE109">
+        <v>1.12</v>
+      </c>
+      <c r="AF109">
+        <v>1.52</v>
+      </c>
+      <c r="AG109">
+        <v>2.34</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.44</v>
       </c>
-      <c r="W109">
-        <v>1.07</v>
-      </c>
-      <c r="X109">
-        <v>1</v>
-      </c>
-      <c r="Y109">
-        <v>1.23</v>
-      </c>
-      <c r="Z109">
-        <v>3.5</v>
-      </c>
-      <c r="AA109">
-        <v>1.75</v>
-      </c>
-      <c r="AB109">
-        <v>1.93</v>
-      </c>
-      <c r="AC109">
-        <v>2.89</v>
-      </c>
-      <c r="AD109">
-        <v>1.38</v>
-      </c>
-      <c r="AE109">
-        <v>1.1</v>
-      </c>
-      <c r="AF109">
-        <v>1.64</v>
-      </c>
-      <c r="AG109">
-        <v>2.1</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.3</v>
-      </c>
       <c r="AK109">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q110">
+        <v>1.97</v>
+      </c>
+      <c r="R110">
+        <v>2.36</v>
+      </c>
+      <c r="S110">
+        <v>1.33</v>
+      </c>
+      <c r="T110">
         <v>3</v>
       </c>
-      <c r="R110">
-        <v>2.25</v>
-      </c>
-      <c r="S110">
-        <v>1.29</v>
-      </c>
-      <c r="T110">
+      <c r="U110">
+        <v>2.72</v>
+      </c>
+      <c r="V110">
+        <v>1.36</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.3</v>
+      </c>
+      <c r="Z110">
+        <v>3.34</v>
+      </c>
+      <c r="AA110">
+        <v>1.86</v>
+      </c>
+      <c r="AB110">
+        <v>1.81</v>
+      </c>
+      <c r="AC110">
         <v>3.3</v>
       </c>
-      <c r="U110">
-        <v>2.44</v>
-      </c>
-      <c r="V110">
-        <v>1.5</v>
-      </c>
-      <c r="W110">
-        <v>1.11</v>
-      </c>
-      <c r="X110">
-        <v>1.03</v>
-      </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
-      <c r="Z110">
-        <v>4.1</v>
-      </c>
-      <c r="AA110">
-        <v>1.65</v>
-      </c>
-      <c r="AB110">
-        <v>2.06</v>
-      </c>
-      <c r="AC110">
-        <v>2.56</v>
-      </c>
       <c r="AD110">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N120">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="O2">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="P2">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>4.19</v>
+        <v>3.61</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="P3">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="Q3">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.39</v>
+      </c>
+      <c r="Z3">
+        <v>2.85</v>
+      </c>
+      <c r="AA3">
+        <v>2.2</v>
+      </c>
+      <c r="AB3">
+        <v>1.61</v>
+      </c>
+      <c r="AC3">
+        <v>4.19</v>
+      </c>
+      <c r="AD3">
+        <v>1.21</v>
+      </c>
+      <c r="AE3">
         <v>1.02</v>
       </c>
-      <c r="Y3">
-        <v>1.32</v>
-      </c>
-      <c r="Z3">
-        <v>3.19</v>
-      </c>
-      <c r="AA3">
-        <v>2.08</v>
-      </c>
-      <c r="AB3">
-        <v>1.73</v>
-      </c>
-      <c r="AC3">
-        <v>3.61</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
-      </c>
-      <c r="AE3">
-        <v>1.04</v>
-      </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.5</v>
+      </c>
+      <c r="O23">
+        <v>4.3</v>
+      </c>
+      <c r="P23">
+        <v>4.83</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>3.62</v>
-      </c>
-      <c r="P23">
-        <v>3.04</v>
-      </c>
-      <c r="Q23">
-        <v>2.52</v>
-      </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>4.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
+        <v>2.71</v>
+      </c>
+      <c r="U34">
+        <v>2.81</v>
+      </c>
+      <c r="V34">
+        <v>1.36</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.27</v>
+      </c>
+      <c r="Z34">
+        <v>3.42</v>
+      </c>
+      <c r="AA34">
+        <v>1.88</v>
+      </c>
+      <c r="AB34">
+        <v>1.88</v>
+      </c>
+      <c r="AC34">
         <v>3.08</v>
       </c>
-      <c r="U34">
-        <v>2.48</v>
-      </c>
-      <c r="V34">
-        <v>1.46</v>
-      </c>
-      <c r="W34">
-        <v>1.08</v>
-      </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.26</v>
-      </c>
-      <c r="Z34">
-        <v>3.58</v>
-      </c>
-      <c r="AA34">
-        <v>1.83</v>
-      </c>
-      <c r="AB34">
-        <v>1.94</v>
-      </c>
-      <c r="AC34">
-        <v>3.11</v>
-      </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB35">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="U36">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
         <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
         <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O107">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P107">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q107">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R107">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S107">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
+        <v>2.83</v>
+      </c>
+      <c r="U107">
+        <v>2.5</v>
+      </c>
+      <c r="V107">
+        <v>1.44</v>
+      </c>
+      <c r="W107">
+        <v>1.07</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107">
+        <v>1.23</v>
+      </c>
+      <c r="Z107">
+        <v>3.5</v>
+      </c>
+      <c r="AA107">
+        <v>1.75</v>
+      </c>
+      <c r="AB107">
+        <v>1.93</v>
+      </c>
+      <c r="AC107">
         <v>2.89</v>
       </c>
-      <c r="U107">
-        <v>2.97</v>
-      </c>
-      <c r="V107">
-        <v>1.37</v>
-      </c>
-      <c r="W107">
-        <v>1.05</v>
-      </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.27</v>
-      </c>
-      <c r="Z107">
-        <v>3.14</v>
-      </c>
-      <c r="AA107">
-        <v>2</v>
-      </c>
-      <c r="AB107">
-        <v>1.8</v>
-      </c>
-      <c r="AC107">
-        <v>3.34</v>
-      </c>
       <c r="AD107">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE107">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG107">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,80 +17913,80 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="O108">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P108">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q108">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R108">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V108">
+        <v>1.5</v>
+      </c>
+      <c r="W108">
+        <v>1.11</v>
+      </c>
+      <c r="X108">
+        <v>1.03</v>
+      </c>
+      <c r="Y108">
+        <v>1.16</v>
+      </c>
+      <c r="Z108">
+        <v>4.1</v>
+      </c>
+      <c r="AA108">
+        <v>1.65</v>
+      </c>
+      <c r="AB108">
+        <v>2.06</v>
+      </c>
+      <c r="AC108">
+        <v>2.56</v>
+      </c>
+      <c r="AD108">
+        <v>1.4</v>
+      </c>
+      <c r="AE108">
+        <v>1.12</v>
+      </c>
+      <c r="AF108">
+        <v>1.52</v>
+      </c>
+      <c r="AG108">
+        <v>2.34</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108">
         <v>1.44</v>
       </c>
-      <c r="W108">
-        <v>1.07</v>
-      </c>
-      <c r="X108">
-        <v>1</v>
-      </c>
-      <c r="Y108">
-        <v>1.23</v>
-      </c>
-      <c r="Z108">
-        <v>3.5</v>
-      </c>
-      <c r="AA108">
-        <v>1.75</v>
-      </c>
-      <c r="AB108">
-        <v>1.93</v>
-      </c>
-      <c r="AC108">
-        <v>2.89</v>
-      </c>
-      <c r="AD108">
-        <v>1.38</v>
-      </c>
-      <c r="AE108">
-        <v>1.1</v>
-      </c>
-      <c r="AF108">
-        <v>1.64</v>
-      </c>
-      <c r="AG108">
-        <v>2.1</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>1.3</v>
-      </c>
       <c r="AK108">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O109">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P109">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q109">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R109">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S109">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U109">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="V109">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z109">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="AA109">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AB109">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AC109">
-        <v>2.56</v>
+        <v>3.67</v>
       </c>
       <c r="AD109">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE109">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF109">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AG109">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P110">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U110">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z110">
+        <v>3.14</v>
+      </c>
+      <c r="AA110">
+        <v>2</v>
+      </c>
+      <c r="AB110">
+        <v>1.8</v>
+      </c>
+      <c r="AC110">
         <v>3.34</v>
       </c>
-      <c r="AA110">
+      <c r="AD110">
+        <v>1.24</v>
+      </c>
+      <c r="AE110">
+        <v>1.04</v>
+      </c>
+      <c r="AF110">
         <v>1.86</v>
       </c>
-      <c r="AB110">
-        <v>1.81</v>
-      </c>
-      <c r="AC110">
-        <v>3.3</v>
-      </c>
-      <c r="AD110">
-        <v>1.31</v>
-      </c>
-      <c r="AE110">
-        <v>1.1</v>
-      </c>
-      <c r="AF110">
-        <v>2</v>
-      </c>
       <c r="AG110">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,31 +21173,31 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.13</v>
+        <v>1.55</v>
       </c>
       <c r="O128">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="P128">
-        <v>1.68</v>
+        <v>5.05</v>
       </c>
       <c r="Q128">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="R128">
         <v>2.3</v>
       </c>
       <c r="S128">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T128">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U128">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V128">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W128">
         <v>1.11</v>
@@ -21206,31 +21206,31 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA128">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB128">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC128">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD128">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE128">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF128">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG128">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK128">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.55</v>
+        <v>4.13</v>
       </c>
       <c r="O129">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="P129">
-        <v>5.05</v>
+        <v>1.68</v>
       </c>
       <c r="Q129">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="R129">
         <v>2.3</v>
       </c>
       <c r="S129">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U129">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V129">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W129">
         <v>1.11</v>
@@ -21369,31 +21369,31 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA129">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB129">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC129">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD129">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF129">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG129">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL129">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q25">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA35">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC35">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD35">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
         <v>3.42</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
+        <v>3.08</v>
+      </c>
+      <c r="AA37">
+        <v>1.94</v>
+      </c>
+      <c r="AB37">
+        <v>1.83</v>
+      </c>
+      <c r="AC37">
+        <v>3.28</v>
+      </c>
+      <c r="AD37">
         <v>1.25</v>
       </c>
-      <c r="Z37">
-        <v>3.82</v>
-      </c>
-      <c r="AA37">
-        <v>1.79</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.83</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
         <v>3.42</v>
       </c>
       <c r="P38">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
         <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
+        <v>2.71</v>
+      </c>
+      <c r="U39">
+        <v>2.81</v>
+      </c>
+      <c r="V39">
+        <v>1.36</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.27</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.88</v>
+      </c>
+      <c r="AB39">
+        <v>1.88</v>
+      </c>
+      <c r="AC39">
         <v>3.08</v>
       </c>
-      <c r="U39">
-        <v>2.48</v>
-      </c>
-      <c r="V39">
-        <v>1.46</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.26</v>
-      </c>
-      <c r="Z39">
-        <v>3.58</v>
-      </c>
-      <c r="AA39">
-        <v>1.83</v>
-      </c>
-      <c r="AB39">
-        <v>1.94</v>
-      </c>
-      <c r="AC39">
-        <v>3.11</v>
-      </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="O101">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="P101">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="Q101">
+        <v>2.77</v>
+      </c>
+      <c r="R101">
+        <v>1.99</v>
+      </c>
+      <c r="S101">
+        <v>1.42</v>
+      </c>
+      <c r="T101">
+        <v>2.74</v>
+      </c>
+      <c r="U101">
+        <v>2.82</v>
+      </c>
+      <c r="V101">
+        <v>1.4</v>
+      </c>
+      <c r="W101">
+        <v>1.04</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="Y101">
+        <v>1.32</v>
+      </c>
+      <c r="Z101">
         <v>3.16</v>
       </c>
-      <c r="R101">
-        <v>2.09</v>
-      </c>
-      <c r="S101">
-        <v>1.5</v>
-      </c>
-      <c r="T101">
-        <v>2.39</v>
-      </c>
-      <c r="U101">
-        <v>3.2</v>
-      </c>
-      <c r="V101">
-        <v>1.3</v>
-      </c>
-      <c r="W101">
-        <v>1.01</v>
-      </c>
-      <c r="X101">
-        <v>1.03</v>
-      </c>
-      <c r="Y101">
-        <v>1.36</v>
-      </c>
-      <c r="Z101">
-        <v>2.7</v>
-      </c>
       <c r="AA101">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB101">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC101">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="AD101">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF101">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="P102">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="Q102">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="R102">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S102">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T102">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="U102">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="AA102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AD102">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE102">
         <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="O103">
-        <v>3.66</v>
+        <v>3.02</v>
       </c>
       <c r="P103">
-        <v>3.57</v>
+        <v>3.1</v>
       </c>
       <c r="Q103">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="R103">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S103">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T103">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U103">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V103">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X103">
         <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z103">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA103">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB103">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC103">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="AD103">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE103">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF103">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK103">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="O107">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P107">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q107">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R107">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V107">
+        <v>1.5</v>
+      </c>
+      <c r="W107">
+        <v>1.11</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.16</v>
+      </c>
+      <c r="Z107">
+        <v>4.1</v>
+      </c>
+      <c r="AA107">
+        <v>1.65</v>
+      </c>
+      <c r="AB107">
+        <v>2.06</v>
+      </c>
+      <c r="AC107">
+        <v>2.56</v>
+      </c>
+      <c r="AD107">
+        <v>1.4</v>
+      </c>
+      <c r="AE107">
+        <v>1.12</v>
+      </c>
+      <c r="AF107">
+        <v>1.52</v>
+      </c>
+      <c r="AG107">
+        <v>2.34</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.44</v>
       </c>
-      <c r="W107">
-        <v>1.07</v>
-      </c>
-      <c r="X107">
-        <v>1</v>
-      </c>
-      <c r="Y107">
-        <v>1.23</v>
-      </c>
-      <c r="Z107">
-        <v>3.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.75</v>
-      </c>
-      <c r="AB107">
-        <v>1.93</v>
-      </c>
-      <c r="AC107">
-        <v>2.89</v>
-      </c>
-      <c r="AD107">
-        <v>1.38</v>
-      </c>
-      <c r="AE107">
-        <v>1.1</v>
-      </c>
-      <c r="AF107">
-        <v>1.64</v>
-      </c>
-      <c r="AG107">
-        <v>2.1</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.3</v>
-      </c>
       <c r="AK107">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="O108">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P108">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q108">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R108">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T108">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U108">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="V108">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W108">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z108">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA108">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB108">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC108">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AG108">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O109">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P109">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q109">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R109">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V109">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W109">
         <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z109">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA109">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB109">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC109">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD109">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE109">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG109">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK109">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
+        <v>2.83</v>
+      </c>
+      <c r="U110">
+        <v>2.5</v>
+      </c>
+      <c r="V110">
+        <v>1.44</v>
+      </c>
+      <c r="W110">
+        <v>1.07</v>
+      </c>
+      <c r="X110">
+        <v>1</v>
+      </c>
+      <c r="Y110">
+        <v>1.23</v>
+      </c>
+      <c r="Z110">
+        <v>3.5</v>
+      </c>
+      <c r="AA110">
+        <v>1.75</v>
+      </c>
+      <c r="AB110">
+        <v>1.93</v>
+      </c>
+      <c r="AC110">
         <v>2.89</v>
       </c>
-      <c r="U110">
-        <v>2.97</v>
-      </c>
-      <c r="V110">
-        <v>1.37</v>
-      </c>
-      <c r="W110">
-        <v>1.05</v>
-      </c>
-      <c r="X110">
-        <v>1.02</v>
-      </c>
-      <c r="Y110">
-        <v>1.27</v>
-      </c>
-      <c r="Z110">
-        <v>3.14</v>
-      </c>
-      <c r="AA110">
-        <v>2</v>
-      </c>
-      <c r="AB110">
-        <v>1.8</v>
-      </c>
-      <c r="AC110">
-        <v>3.34</v>
-      </c>
       <c r="AD110">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
+        <v>3.17</v>
+      </c>
+      <c r="R37">
+        <v>2.23</v>
+      </c>
+      <c r="S37">
+        <v>1.39</v>
+      </c>
+      <c r="T37">
         <v>2.71</v>
       </c>
-      <c r="R37">
-        <v>2.2</v>
-      </c>
-      <c r="S37">
-        <v>1.38</v>
-      </c>
-      <c r="T37">
-        <v>2.91</v>
-      </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V37">
         <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.27</v>
+      </c>
+      <c r="Z37">
+        <v>3.42</v>
+      </c>
+      <c r="AA37">
+        <v>1.88</v>
+      </c>
+      <c r="AB37">
+        <v>1.88</v>
+      </c>
+      <c r="AC37">
+        <v>3.08</v>
+      </c>
+      <c r="AD37">
         <v>1.28</v>
       </c>
-      <c r="Z37">
-        <v>3.08</v>
-      </c>
-      <c r="AA37">
-        <v>1.94</v>
-      </c>
-      <c r="AB37">
-        <v>1.83</v>
-      </c>
-      <c r="AC37">
-        <v>3.28</v>
-      </c>
-      <c r="AD37">
-        <v>1.25</v>
-      </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="O38">
         <v>3.42</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="R38">
         <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
+        <v>1.28</v>
+      </c>
+      <c r="Z38">
+        <v>3.08</v>
+      </c>
+      <c r="AA38">
+        <v>1.94</v>
+      </c>
+      <c r="AB38">
+        <v>1.83</v>
+      </c>
+      <c r="AC38">
+        <v>3.28</v>
+      </c>
+      <c r="AD38">
         <v>1.25</v>
       </c>
-      <c r="Z38">
-        <v>3.82</v>
-      </c>
-      <c r="AA38">
-        <v>1.79</v>
-      </c>
-      <c r="AB38">
-        <v>2.15</v>
-      </c>
-      <c r="AC38">
-        <v>2.83</v>
-      </c>
-      <c r="AD38">
-        <v>1.33</v>
-      </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
         <v>0</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -16455,55 +16455,55 @@
         <v>2.3</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
+        <v>1.68</v>
+      </c>
+      <c r="O104">
+        <v>3.8</v>
+      </c>
+      <c r="P104">
+        <v>4.5</v>
+      </c>
+      <c r="Q104">
+        <v>2.2</v>
+      </c>
+      <c r="R104">
+        <v>2.25</v>
+      </c>
+      <c r="S104">
+        <v>1.3</v>
+      </c>
+      <c r="T104">
+        <v>2.95</v>
+      </c>
+      <c r="U104">
+        <v>2.55</v>
+      </c>
+      <c r="V104">
+        <v>1.44</v>
+      </c>
+      <c r="W104">
+        <v>1.07</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>1.26</v>
+      </c>
+      <c r="Z104">
+        <v>3.66</v>
+      </c>
+      <c r="AA104">
         <v>1.81</v>
       </c>
-      <c r="O104">
-        <v>3.35</v>
-      </c>
-      <c r="P104">
-        <v>4.4</v>
-      </c>
-      <c r="Q104">
-        <v>2.38</v>
-      </c>
-      <c r="R104">
+      <c r="AB104">
+        <v>1.86</v>
+      </c>
+      <c r="AC104">
+        <v>3.04</v>
+      </c>
+      <c r="AD104">
+        <v>1.29</v>
+      </c>
+      <c r="AE104">
+        <v>1.07</v>
+      </c>
+      <c r="AF104">
+        <v>1.78</v>
+      </c>
+      <c r="AG104">
+        <v>1.88</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
+        <v>1.25</v>
+      </c>
+      <c r="AK104">
         <v>2.1</v>
-      </c>
-      <c r="S104">
-        <v>1.42</v>
-      </c>
-      <c r="T104">
-        <v>2.62</v>
-      </c>
-      <c r="U104">
-        <v>3</v>
-      </c>
-      <c r="V104">
-        <v>1.29</v>
-      </c>
-      <c r="W104">
-        <v>1.04</v>
-      </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
-      <c r="Y104">
-        <v>1.4</v>
-      </c>
-      <c r="Z104">
-        <v>2.7</v>
-      </c>
-      <c r="AA104">
-        <v>2.2</v>
-      </c>
-      <c r="AB104">
-        <v>1.58</v>
-      </c>
-      <c r="AC104">
-        <v>4.05</v>
-      </c>
-      <c r="AD104">
-        <v>1.17</v>
-      </c>
-      <c r="AE104">
-        <v>1.02</v>
-      </c>
-      <c r="AF104">
-        <v>2</v>
-      </c>
-      <c r="AG104">
-        <v>1.67</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.24</v>
-      </c>
-      <c r="AK104">
-        <v>1.91</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O105">
+        <v>3.65</v>
+      </c>
+      <c r="P105">
         <v>3.8</v>
       </c>
-      <c r="P105">
-        <v>4.5</v>
-      </c>
       <c r="Q105">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T105">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W105">
         <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB105">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD105">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="O106">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P106">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q106">
+        <v>3</v>
+      </c>
+      <c r="R106">
         <v>2.25</v>
       </c>
-      <c r="R106">
-        <v>2.3</v>
-      </c>
       <c r="S106">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U106">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V106">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB106">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AC106">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD106">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE106">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK106">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="O107">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q107">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S107">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="V107">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA107">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC107">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AD107">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF107">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AG107">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O108">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q108">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R108">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S108">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
+        <v>2.83</v>
+      </c>
+      <c r="U108">
+        <v>2.5</v>
+      </c>
+      <c r="V108">
+        <v>1.44</v>
+      </c>
+      <c r="W108">
+        <v>1.07</v>
+      </c>
+      <c r="X108">
+        <v>1</v>
+      </c>
+      <c r="Y108">
+        <v>1.23</v>
+      </c>
+      <c r="Z108">
+        <v>3.5</v>
+      </c>
+      <c r="AA108">
+        <v>1.75</v>
+      </c>
+      <c r="AB108">
+        <v>1.93</v>
+      </c>
+      <c r="AC108">
         <v>2.89</v>
       </c>
-      <c r="U108">
-        <v>2.97</v>
-      </c>
-      <c r="V108">
-        <v>1.37</v>
-      </c>
-      <c r="W108">
-        <v>1.05</v>
-      </c>
-      <c r="X108">
-        <v>1.02</v>
-      </c>
-      <c r="Y108">
-        <v>1.27</v>
-      </c>
-      <c r="Z108">
-        <v>3.14</v>
-      </c>
-      <c r="AA108">
-        <v>2</v>
-      </c>
-      <c r="AB108">
-        <v>1.8</v>
-      </c>
-      <c r="AC108">
-        <v>3.34</v>
-      </c>
       <c r="AD108">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG108">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,58 +18076,58 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="O109">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q109">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="R109">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T109">
+        <v>2.62</v>
+      </c>
+      <c r="U109">
         <v>3</v>
       </c>
-      <c r="U109">
-        <v>2.72</v>
-      </c>
       <c r="V109">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z109">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AA109">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AB109">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AC109">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD109">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE109">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF109">
         <v>2</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC118">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB34">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
         <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA35">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD35">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q37">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA37">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD37">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
+        <v>2.17</v>
+      </c>
+      <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.14</v>
+      </c>
+      <c r="U38">
+        <v>2.61</v>
+      </c>
+      <c r="V38">
+        <v>1.45</v>
+      </c>
+      <c r="W38">
+        <v>1.09</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.19</v>
+      </c>
+      <c r="Z38">
+        <v>3.74</v>
+      </c>
+      <c r="AA38">
+        <v>1.73</v>
+      </c>
+      <c r="AB38">
+        <v>1.99</v>
+      </c>
+      <c r="AC38">
+        <v>2.7</v>
+      </c>
+      <c r="AD38">
+        <v>1.35</v>
+      </c>
+      <c r="AE38">
+        <v>1.11</v>
+      </c>
+      <c r="AF38">
+        <v>1.6</v>
+      </c>
+      <c r="AG38">
         <v>2.2</v>
       </c>
-      <c r="S38">
-        <v>1.38</v>
-      </c>
-      <c r="T38">
-        <v>2.91</v>
-      </c>
-      <c r="U38">
-        <v>2.88</v>
-      </c>
-      <c r="V38">
-        <v>1.36</v>
-      </c>
-      <c r="W38">
-        <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.28</v>
-      </c>
-      <c r="Z38">
-        <v>3.08</v>
-      </c>
-      <c r="AA38">
-        <v>1.94</v>
-      </c>
-      <c r="AB38">
-        <v>1.83</v>
-      </c>
-      <c r="AC38">
-        <v>3.28</v>
-      </c>
-      <c r="AD38">
-        <v>1.25</v>
-      </c>
-      <c r="AE38">
-        <v>1.1</v>
-      </c>
-      <c r="AF38">
-        <v>1.75</v>
-      </c>
-      <c r="AG38">
-        <v>1.94</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
+        <v>2.91</v>
+      </c>
+      <c r="U39">
+        <v>2.88</v>
+      </c>
+      <c r="V39">
+        <v>1.36</v>
+      </c>
+      <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.28</v>
+      </c>
+      <c r="Z39">
         <v>3.08</v>
       </c>
-      <c r="U39">
-        <v>2.48</v>
-      </c>
-      <c r="V39">
-        <v>1.46</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.26</v>
-      </c>
-      <c r="Z39">
-        <v>3.58</v>
-      </c>
       <c r="AA39">
+        <v>1.94</v>
+      </c>
+      <c r="AB39">
         <v>1.83</v>
       </c>
-      <c r="AB39">
-        <v>1.94</v>
-      </c>
       <c r="AC39">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -19552,34 +19552,34 @@
         <v>17</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X118">
         <v>0</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AA118">
         <v>1.53</v>
@@ -19588,19 +19588,19 @@
         <v>2.3</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>2.9</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.5</v>
+      </c>
+      <c r="O25">
+        <v>4.3</v>
+      </c>
+      <c r="P25">
+        <v>4.83</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="O25">
-        <v>3.62</v>
-      </c>
-      <c r="P25">
-        <v>3.04</v>
-      </c>
-      <c r="Q25">
-        <v>2.52</v>
-      </c>
       <c r="R25">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
         <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
+        <v>3.08</v>
+      </c>
+      <c r="AA35">
+        <v>1.94</v>
+      </c>
+      <c r="AB35">
+        <v>1.83</v>
+      </c>
+      <c r="AC35">
+        <v>3.28</v>
+      </c>
+      <c r="AD35">
         <v>1.25</v>
       </c>
-      <c r="Z35">
-        <v>3.82</v>
-      </c>
-      <c r="AA35">
-        <v>1.79</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.83</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="U36">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
+        <v>1.12</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.25</v>
+      </c>
+      <c r="Z38">
+        <v>3.82</v>
+      </c>
+      <c r="AA38">
+        <v>1.79</v>
+      </c>
+      <c r="AB38">
+        <v>2.15</v>
+      </c>
+      <c r="AC38">
+        <v>2.83</v>
+      </c>
+      <c r="AD38">
+        <v>1.33</v>
+      </c>
+      <c r="AE38">
         <v>1.09</v>
       </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>3.74</v>
-      </c>
-      <c r="AA38">
-        <v>1.73</v>
-      </c>
-      <c r="AB38">
-        <v>1.99</v>
-      </c>
-      <c r="AC38">
-        <v>2.7</v>
-      </c>
-      <c r="AD38">
-        <v>1.35</v>
-      </c>
-      <c r="AE38">
-        <v>1.11</v>
-      </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="O39">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P39">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q39">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA39">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB39">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="O73">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="P73">
-        <v>3.64</v>
+        <v>4.39</v>
       </c>
       <c r="Q73">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="R73">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S73">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T73">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="U73">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V73">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z73">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA73">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB73">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AC73">
-        <v>3.96</v>
+        <v>3.43</v>
       </c>
       <c r="AD73">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE73">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
         <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-10-03 13:00:00</t>
+          <t>2026-10-03 12:30:00</t>
         </is>
       </c>
     </row>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK77">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G80">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-10-03 13:30:00</t>
+          <t>2026-10-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="O82">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="P82">
-        <v>2.84</v>
+        <v>3.67</v>
       </c>
       <c r="Q82">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB82">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC82">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-03 13:45:00</t>
+          <t>2026-10-03 13:30:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-03 14:00:00</t>
+          <t>2026-10-03 13:45:00</t>
         </is>
       </c>
     </row>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,68 +14160,68 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N85">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P85">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S85">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T85">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="U85">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="V85">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.38</v>
+      </c>
+      <c r="Z85">
+        <v>2.91</v>
+      </c>
+      <c r="AA85">
+        <v>2.12</v>
+      </c>
+      <c r="AB85">
+        <v>1.72</v>
+      </c>
+      <c r="AC85">
+        <v>3.72</v>
+      </c>
+      <c r="AD85">
+        <v>1.24</v>
+      </c>
+      <c r="AE85">
         <v>1.03</v>
       </c>
-      <c r="Y85">
-        <v>1.24</v>
-      </c>
-      <c r="Z85">
-        <v>3.4</v>
-      </c>
-      <c r="AA85">
-        <v>1.88</v>
-      </c>
-      <c r="AB85">
-        <v>1.82</v>
-      </c>
-      <c r="AC85">
-        <v>3.4</v>
-      </c>
-      <c r="AD85">
-        <v>1.29</v>
-      </c>
-      <c r="AE85">
-        <v>1.06</v>
-      </c>
       <c r="AF85">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-10-03 15:00:00</t>
+          <t>2026-10-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P86">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q86">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U86">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="V86">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z86">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="AA86">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AB86">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC86">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD86">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE86">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O87">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>4.27</v>
+        <v>3.3</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y87">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z87">
+        <v>2.91</v>
+      </c>
+      <c r="AA87">
         <v>2.15</v>
       </c>
-      <c r="AA87">
-        <v>0</v>
-      </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O88">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14689,7 +14689,7 @@
         <v>1.6</v>
       </c>
       <c r="Z88">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O89">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="P89">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z89">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
+        <v>2.25</v>
+      </c>
+      <c r="O90">
         <v>2.55</v>
       </c>
-      <c r="O90">
-        <v>2.7</v>
-      </c>
       <c r="P90">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z90">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,14 +15142,14 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O91">
+        <v>2.7</v>
+      </c>
+      <c r="P91">
         <v>2.95</v>
       </c>
-      <c r="P91">
-        <v>3.2</v>
-      </c>
       <c r="Q91">
         <v>0</v>
       </c>
@@ -15175,10 +15175,10 @@
         <v>0</v>
       </c>
       <c r="Y91">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Z91">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O92">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P92">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15338,10 +15338,10 @@
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA92">
         <v>0</v>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T95">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U95">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V95">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC95">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK95">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G96">
@@ -15960,61 +15960,61 @@
         <v>1.91</v>
       </c>
       <c r="O96">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P96">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q96">
         <v>2.4</v>
       </c>
       <c r="R96">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S96">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T96">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U96">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="V96">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA96">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AC96">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AD96">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AE96">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF96">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG96">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
+        <v>1.91</v>
+      </c>
+      <c r="O97">
+        <v>3.7</v>
+      </c>
+      <c r="P97">
+        <v>3.1</v>
+      </c>
+      <c r="Q97">
+        <v>2.4</v>
+      </c>
+      <c r="R97">
+        <v>2.5</v>
+      </c>
+      <c r="S97">
+        <v>1.2</v>
+      </c>
+      <c r="T97">
+        <v>4</v>
+      </c>
+      <c r="U97">
+        <v>2.1</v>
+      </c>
+      <c r="V97">
+        <v>1.69</v>
+      </c>
+      <c r="W97">
+        <v>1.18</v>
+      </c>
+      <c r="X97">
+        <v>1.02</v>
+      </c>
+      <c r="Y97">
+        <v>1.11</v>
+      </c>
+      <c r="Z97">
+        <v>5.75</v>
+      </c>
+      <c r="AA97">
+        <v>1.39</v>
+      </c>
+      <c r="AB97">
+        <v>2.59</v>
+      </c>
+      <c r="AC97">
+        <v>2.06</v>
+      </c>
+      <c r="AD97">
+        <v>1.7</v>
+      </c>
+      <c r="AE97">
+        <v>1.25</v>
+      </c>
+      <c r="AF97">
+        <v>1.39</v>
+      </c>
+      <c r="AG97">
+        <v>2.77</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.2</v>
+      </c>
+      <c r="AK97">
         <v>1.8</v>
-      </c>
-      <c r="O97">
-        <v>3.8</v>
-      </c>
-      <c r="P97">
-        <v>3.3</v>
-      </c>
-      <c r="Q97">
-        <v>2.3</v>
-      </c>
-      <c r="R97">
-        <v>2.51</v>
-      </c>
-      <c r="S97">
-        <v>1.15</v>
-      </c>
-      <c r="T97">
-        <v>4.3</v>
-      </c>
-      <c r="U97">
-        <v>1.97</v>
-      </c>
-      <c r="V97">
-        <v>1.75</v>
-      </c>
-      <c r="W97">
-        <v>1.22</v>
-      </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
-      <c r="Y97">
-        <v>1.07</v>
-      </c>
-      <c r="Z97">
-        <v>7</v>
-      </c>
-      <c r="AA97">
-        <v>1.32</v>
-      </c>
-      <c r="AB97">
-        <v>2.88</v>
-      </c>
-      <c r="AC97">
-        <v>1.89</v>
-      </c>
-      <c r="AD97">
-        <v>1.84</v>
-      </c>
-      <c r="AE97">
-        <v>1.32</v>
-      </c>
-      <c r="AF97">
-        <v>1.35</v>
-      </c>
-      <c r="AG97">
-        <v>2.9</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.18</v>
-      </c>
-      <c r="AK97">
-        <v>1.87</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,65 +16283,65 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.82</v>
+        <v>1.8</v>
       </c>
       <c r="O98">
         <v>3.8</v>
       </c>
       <c r="P98">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q98">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="R98">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S98">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T98">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U98">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V98">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W98">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z98">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA98">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB98">
+        <v>2.88</v>
+      </c>
+      <c r="AC98">
+        <v>1.89</v>
+      </c>
+      <c r="AD98">
+        <v>1.84</v>
+      </c>
+      <c r="AE98">
+        <v>1.32</v>
+      </c>
+      <c r="AF98">
+        <v>1.35</v>
+      </c>
+      <c r="AG98">
         <v>2.9</v>
       </c>
-      <c r="AC98">
-        <v>1.99</v>
-      </c>
-      <c r="AD98">
-        <v>1.75</v>
-      </c>
-      <c r="AE98">
-        <v>1.33</v>
-      </c>
-      <c r="AF98">
-        <v>1.33</v>
-      </c>
-      <c r="AG98">
-        <v>3</v>
-      </c>
       <c r="AH98" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="O99">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="P99">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q99">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="R99">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="S99">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="T99">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="U99">
-        <v>3.04</v>
+        <v>1.99</v>
       </c>
       <c r="V99">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="W99">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="Z99">
-        <v>2.76</v>
+        <v>6.5</v>
       </c>
       <c r="AA99">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AB99">
-        <v>1.61</v>
+        <v>2.9</v>
       </c>
       <c r="AC99">
-        <v>4.01</v>
+        <v>1.99</v>
       </c>
       <c r="AD99">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AE99">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AF99">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AG99">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AK99">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-03 15:30:00</t>
+          <t>2026-10-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="O100">
-        <v>4.07</v>
+        <v>3.05</v>
       </c>
       <c r="P100">
-        <v>5.06</v>
+        <v>2.3</v>
       </c>
       <c r="Q100">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="R100">
+        <v>2.11</v>
+      </c>
+      <c r="S100">
+        <v>1.48</v>
+      </c>
+      <c r="T100">
+        <v>2.58</v>
+      </c>
+      <c r="U100">
+        <v>3.04</v>
+      </c>
+      <c r="V100">
+        <v>1.35</v>
+      </c>
+      <c r="W100">
+        <v>1.02</v>
+      </c>
+      <c r="X100">
+        <v>1.02</v>
+      </c>
+      <c r="Y100">
+        <v>1.42</v>
+      </c>
+      <c r="Z100">
+        <v>2.76</v>
+      </c>
+      <c r="AA100">
         <v>2.25</v>
       </c>
-      <c r="S100">
-        <v>1.33</v>
-      </c>
-      <c r="T100">
-        <v>3</v>
-      </c>
-      <c r="U100">
-        <v>2.75</v>
-      </c>
-      <c r="V100">
-        <v>1.39</v>
-      </c>
-      <c r="W100">
-        <v>1.08</v>
-      </c>
-      <c r="X100">
-        <v>1</v>
-      </c>
-      <c r="Y100">
+      <c r="AB100">
+        <v>1.61</v>
+      </c>
+      <c r="AC100">
+        <v>4.01</v>
+      </c>
+      <c r="AD100">
+        <v>1.2</v>
+      </c>
+      <c r="AE100">
+        <v>1.01</v>
+      </c>
+      <c r="AF100">
+        <v>1.88</v>
+      </c>
+      <c r="AG100">
+        <v>1.81</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.27</v>
       </c>
-      <c r="Z100">
-        <v>3.44</v>
-      </c>
-      <c r="AA100">
-        <v>1.98</v>
-      </c>
-      <c r="AB100">
-        <v>1.83</v>
-      </c>
-      <c r="AC100">
-        <v>3.06</v>
-      </c>
-      <c r="AD100">
-        <v>1.34</v>
-      </c>
-      <c r="AE100">
-        <v>1.08</v>
-      </c>
-      <c r="AF100">
-        <v>1.97</v>
-      </c>
-      <c r="AG100">
-        <v>1.69</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.17</v>
-      </c>
       <c r="AK100">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="O101">
-        <v>3.06</v>
+        <v>4.07</v>
       </c>
       <c r="P101">
-        <v>2.66</v>
+        <v>5.06</v>
       </c>
       <c r="Q101">
-        <v>2.77</v>
+        <v>2</v>
       </c>
       <c r="R101">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S101">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U101">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W101">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="AA101">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC101">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE101">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AG101">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK101">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="O102">
-        <v>3.66</v>
+        <v>3.06</v>
       </c>
       <c r="P102">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="Q102">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="R102">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S102">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T102">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="U102">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z102">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB102">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AD102">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
         <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="O103">
-        <v>3.02</v>
+        <v>3.66</v>
       </c>
       <c r="P103">
-        <v>3.1</v>
+        <v>3.57</v>
       </c>
       <c r="Q103">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="R103">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S103">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="U103">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V103">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
         <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA103">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB103">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
-        <v>3.99</v>
+        <v>3.58</v>
       </c>
       <c r="AD103">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.68</v>
+        <v>2.21</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="P104">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q104">
-        <v>2.2</v>
+        <v>3.16</v>
       </c>
       <c r="R104">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S104">
+        <v>1.5</v>
+      </c>
+      <c r="T104">
+        <v>2.39</v>
+      </c>
+      <c r="U104">
+        <v>3.2</v>
+      </c>
+      <c r="V104">
         <v>1.3</v>
       </c>
-      <c r="T104">
-        <v>2.95</v>
-      </c>
-      <c r="U104">
-        <v>2.55</v>
-      </c>
-      <c r="V104">
-        <v>1.44</v>
-      </c>
       <c r="W104">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z104">
-        <v>3.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA104">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AB104">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AC104">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="AD104">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE104">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG104">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK104">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-03 15:45:00</t>
+          <t>2026-10-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="O105">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q105">
+        <v>2.2</v>
+      </c>
+      <c r="R105">
         <v>2.25</v>
       </c>
-      <c r="R105">
-        <v>2.3</v>
-      </c>
       <c r="S105">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U105">
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
         <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA105">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC105">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD105">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="O106">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q106">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S106">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T106">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U106">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB106">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AC106">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD106">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE106">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="O107">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P107">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q107">
+        <v>3</v>
+      </c>
+      <c r="R107">
         <v>2.25</v>
       </c>
-      <c r="R107">
-        <v>2.09</v>
-      </c>
       <c r="S107">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.97</v>
+        <v>2.44</v>
       </c>
       <c r="V107">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="AA107">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB107">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC107">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AD107">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE107">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF107">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AG107">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK107">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="O108">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P108">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q108">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="R108">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T108">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA108">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB108">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC108">
-        <v>2.89</v>
+        <v>3.34</v>
       </c>
       <c r="AD108">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AG108">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,31 +18565,31 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>6.88</v>
+        <v>6.4</v>
       </c>
       <c r="Q112">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
         <v>1.06</v>
@@ -18598,31 +18598,31 @@
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC112">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
         <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG112">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK112">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-03 16:00:00</t>
+          <t>2026-10-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-03 17:00:00</t>
+          <t>2026-10-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S117">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T117">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U117">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V117">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB117">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD117">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE117">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK117">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.16</v>
+        <v>3.6</v>
       </c>
       <c r="O118">
-        <v>7.8</v>
+        <v>3.69</v>
       </c>
       <c r="P118">
-        <v>17</v>
+        <v>1.78</v>
       </c>
       <c r="Q118">
-        <v>1.48</v>
+        <v>3.48</v>
       </c>
       <c r="R118">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S118">
+        <v>1.2</v>
+      </c>
+      <c r="T118">
+        <v>3.9</v>
+      </c>
+      <c r="U118">
+        <v>2.12</v>
+      </c>
+      <c r="V118">
+        <v>1.67</v>
+      </c>
+      <c r="W118">
+        <v>1.17</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.12</v>
+      </c>
+      <c r="Z118">
+        <v>5</v>
+      </c>
+      <c r="AA118">
+        <v>1.4</v>
+      </c>
+      <c r="AB118">
+        <v>2.56</v>
+      </c>
+      <c r="AC118">
+        <v>2.08</v>
+      </c>
+      <c r="AD118">
+        <v>1.64</v>
+      </c>
+      <c r="AE118">
+        <v>1.23</v>
+      </c>
+      <c r="AF118">
+        <v>1.39</v>
+      </c>
+      <c r="AG118">
+        <v>2.63</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.17</v>
+      </c>
+      <c r="AK118">
         <v>1.25</v>
-      </c>
-      <c r="T118">
-        <v>3.64</v>
-      </c>
-      <c r="U118">
-        <v>2.2</v>
-      </c>
-      <c r="V118">
-        <v>1.6</v>
-      </c>
-      <c r="W118">
-        <v>1.15</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>1.1</v>
-      </c>
-      <c r="Z118">
-        <v>5.17</v>
-      </c>
-      <c r="AA118">
-        <v>1.53</v>
-      </c>
-      <c r="AB118">
-        <v>2.3</v>
-      </c>
-      <c r="AC118">
-        <v>2.23</v>
-      </c>
-      <c r="AD118">
-        <v>1.63</v>
-      </c>
-      <c r="AE118">
-        <v>1.2</v>
-      </c>
-      <c r="AF118">
-        <v>2.28</v>
-      </c>
-      <c r="AG118">
-        <v>1.56</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.05</v>
-      </c>
-      <c r="AK118">
-        <v>5.15</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G119">
@@ -19702,68 +19702,68 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N119">
-        <v>2.45</v>
+        <v>1.16</v>
       </c>
       <c r="O119">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="P119">
-        <v>2.49</v>
+        <v>17</v>
       </c>
       <c r="Q119">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="R119">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="S119">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T119">
-        <v>2.79</v>
+        <v>3.64</v>
       </c>
       <c r="U119">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="V119">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="Z119">
-        <v>3.6</v>
+        <v>5.17</v>
       </c>
       <c r="AA119">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AB119">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC119">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AD119">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AE119">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF119">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="AG119">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AK119">
-        <v>1.5</v>
+        <v>5.15</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-03 17:30:00</t>
+          <t>2026-10-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G120">
@@ -19865,68 +19865,68 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N120">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O120">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P120">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="Q120">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R120">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S120">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T120">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U120">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V120">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
         <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z120">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA120">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB120">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC120">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD120">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG120">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK120">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-03 18:30:00</t>
+          <t>2026-10-03 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,65 +20032,65 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O121">
+        <v>3.4</v>
+      </c>
+      <c r="P121">
+        <v>3.42</v>
+      </c>
+      <c r="Q121">
+        <v>2.75</v>
+      </c>
+      <c r="R121">
+        <v>2.1</v>
+      </c>
+      <c r="S121">
+        <v>1.4</v>
+      </c>
+      <c r="T121">
+        <v>2.75</v>
+      </c>
+      <c r="U121">
         <v>3.1</v>
       </c>
-      <c r="P121">
-        <v>2.9</v>
-      </c>
-      <c r="Q121">
+      <c r="V121">
+        <v>1.32</v>
+      </c>
+      <c r="W121">
+        <v>1.07</v>
+      </c>
+      <c r="X121">
+        <v>1.03</v>
+      </c>
+      <c r="Y121">
+        <v>1.33</v>
+      </c>
+      <c r="Z121">
         <v>3.1</v>
       </c>
-      <c r="R121">
+      <c r="AA121">
+        <v>2.1</v>
+      </c>
+      <c r="AB121">
+        <v>1.7</v>
+      </c>
+      <c r="AC121">
+        <v>3.85</v>
+      </c>
+      <c r="AD121">
+        <v>1.23</v>
+      </c>
+      <c r="AE121">
+        <v>1.06</v>
+      </c>
+      <c r="AF121">
+        <v>1.85</v>
+      </c>
+      <c r="AG121">
         <v>1.91</v>
       </c>
-      <c r="S121">
-        <v>1.53</v>
-      </c>
-      <c r="T121">
-        <v>2.45</v>
-      </c>
-      <c r="U121">
-        <v>3.3</v>
-      </c>
-      <c r="V121">
-        <v>1.3</v>
-      </c>
-      <c r="W121">
-        <v>1.03</v>
-      </c>
-      <c r="X121">
-        <v>1.04</v>
-      </c>
-      <c r="Y121">
-        <v>1.49</v>
-      </c>
-      <c r="Z121">
-        <v>2.56</v>
-      </c>
-      <c r="AA121">
-        <v>2.38</v>
-      </c>
-      <c r="AB121">
-        <v>1.57</v>
-      </c>
-      <c r="AC121">
-        <v>4.53</v>
-      </c>
-      <c r="AD121">
-        <v>1.16</v>
-      </c>
-      <c r="AE121">
-        <v>1.01</v>
-      </c>
-      <c r="AF121">
-        <v>2.03</v>
-      </c>
-      <c r="AG121">
-        <v>1.7</v>
-      </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK121">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="O122">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q122">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R122">
+        <v>1.91</v>
+      </c>
+      <c r="S122">
+        <v>1.53</v>
+      </c>
+      <c r="T122">
+        <v>2.45</v>
+      </c>
+      <c r="U122">
+        <v>3.3</v>
+      </c>
+      <c r="V122">
+        <v>1.3</v>
+      </c>
+      <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
+        <v>1.04</v>
+      </c>
+      <c r="Y122">
+        <v>1.49</v>
+      </c>
+      <c r="Z122">
+        <v>2.56</v>
+      </c>
+      <c r="AA122">
         <v>2.38</v>
       </c>
-      <c r="S122">
-        <v>1.22</v>
-      </c>
-      <c r="T122">
-        <v>3.75</v>
-      </c>
-      <c r="U122">
-        <v>2.13</v>
-      </c>
-      <c r="V122">
+      <c r="AB122">
         <v>1.57</v>
       </c>
-      <c r="W122">
-        <v>1.14</v>
-      </c>
-      <c r="X122">
-        <v>1</v>
-      </c>
-      <c r="Y122">
-        <v>1.13</v>
-      </c>
-      <c r="Z122">
-        <v>4.5</v>
-      </c>
-      <c r="AA122">
-        <v>1.53</v>
-      </c>
-      <c r="AB122">
-        <v>2.29</v>
-      </c>
       <c r="AC122">
-        <v>2.28</v>
+        <v>4.53</v>
       </c>
       <c r="AD122">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AE122">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AF122">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="AG122">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK122">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-10-03 19:30:00</t>
+          <t>2026-10-03 19:00:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G126">
@@ -20843,68 +20843,68 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N126">
-        <v>2.97</v>
+        <v>1.43</v>
       </c>
       <c r="O126">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="P126">
-        <v>2.22</v>
+        <v>5.65</v>
       </c>
       <c r="Q126">
-        <v>3.78</v>
+        <v>1.97</v>
       </c>
       <c r="R126">
-        <v>2.02</v>
+        <v>2.47</v>
       </c>
       <c r="S126">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="T126">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U126">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="V126">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
-        <v>2.74</v>
+        <v>5.2</v>
       </c>
       <c r="AA126">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AB126">
-        <v>1.63</v>
+        <v>2.43</v>
       </c>
       <c r="AC126">
-        <v>3.84</v>
+        <v>2.17</v>
       </c>
       <c r="AD126">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="AE126">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AF126">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AG126">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK126">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-03 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G127">
@@ -21006,68 +21006,68 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>2.97</v>
       </c>
       <c r="O127">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P127">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="Q127">
-        <v>2.5</v>
+        <v>3.78</v>
       </c>
       <c r="R127">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="S127">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="T127">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
-        <v>2.34</v>
+        <v>3.08</v>
       </c>
       <c r="V127">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
         <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z127">
-        <v>4.05</v>
+        <v>2.74</v>
       </c>
       <c r="AA127">
+        <v>2.14</v>
+      </c>
+      <c r="AB127">
         <v>1.63</v>
       </c>
-      <c r="AB127">
-        <v>2.1</v>
-      </c>
       <c r="AC127">
-        <v>2.68</v>
+        <v>3.84</v>
       </c>
       <c r="AD127">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE127">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF127">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AG127">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK127">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O128">
-        <v>3.78</v>
+        <v>3.46</v>
       </c>
       <c r="P128">
-        <v>5.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q128">
+        <v>2.5</v>
+      </c>
+      <c r="R128">
+        <v>2.27</v>
+      </c>
+      <c r="S128">
+        <v>1.26</v>
+      </c>
+      <c r="T128">
+        <v>3.3</v>
+      </c>
+      <c r="U128">
+        <v>2.34</v>
+      </c>
+      <c r="V128">
+        <v>1.48</v>
+      </c>
+      <c r="W128">
+        <v>1.08</v>
+      </c>
+      <c r="X128">
+        <v>1.03</v>
+      </c>
+      <c r="Y128">
+        <v>1.16</v>
+      </c>
+      <c r="Z128">
+        <v>4.05</v>
+      </c>
+      <c r="AA128">
+        <v>1.63</v>
+      </c>
+      <c r="AB128">
         <v>2.1</v>
       </c>
-      <c r="R128">
-        <v>2.3</v>
-      </c>
-      <c r="S128">
-        <v>1.3</v>
-      </c>
-      <c r="T128">
-        <v>3.2</v>
-      </c>
-      <c r="U128">
-        <v>2.63</v>
-      </c>
-      <c r="V128">
+      <c r="AC128">
+        <v>2.68</v>
+      </c>
+      <c r="AD128">
         <v>1.44</v>
       </c>
-      <c r="W128">
-        <v>1.11</v>
-      </c>
-      <c r="X128">
-        <v>1.01</v>
-      </c>
-      <c r="Y128">
-        <v>1.18</v>
-      </c>
-      <c r="Z128">
-        <v>3.84</v>
-      </c>
-      <c r="AA128">
-        <v>1.8</v>
-      </c>
-      <c r="AB128">
-        <v>2</v>
-      </c>
-      <c r="AC128">
-        <v>2.74</v>
-      </c>
-      <c r="AD128">
-        <v>1.35</v>
-      </c>
       <c r="AE128">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF128">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.13</v>
+        <v>1.55</v>
       </c>
       <c r="O129">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="P129">
-        <v>1.68</v>
+        <v>5.05</v>
       </c>
       <c r="Q129">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="R129">
         <v>2.3</v>
       </c>
       <c r="S129">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T129">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U129">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V129">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W129">
         <v>1.11</v>
@@ -21369,31 +21369,31 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z129">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA129">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB129">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC129">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD129">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE129">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG129">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21452,7 +21452,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.37</v>
+        <v>4.13</v>
       </c>
       <c r="O130">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="P130">
-        <v>7.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q130">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R130">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U130">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V130">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W130">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X130">
         <v>1.01</v>
       </c>
       <c r="Y130">
+        <v>1.16</v>
+      </c>
+      <c r="Z130">
+        <v>4.1</v>
+      </c>
+      <c r="AA130">
+        <v>1.63</v>
+      </c>
+      <c r="AB130">
+        <v>2.1</v>
+      </c>
+      <c r="AC130">
+        <v>2.56</v>
+      </c>
+      <c r="AD130">
+        <v>1.4</v>
+      </c>
+      <c r="AE130">
         <v>1.13</v>
       </c>
-      <c r="Z130">
-        <v>4.55</v>
-      </c>
-      <c r="AA130">
-        <v>1.53</v>
-      </c>
-      <c r="AB130">
-        <v>2.29</v>
-      </c>
-      <c r="AC130">
-        <v>2.26</v>
-      </c>
-      <c r="AD130">
-        <v>1.51</v>
-      </c>
-      <c r="AE130">
-        <v>1.18</v>
-      </c>
       <c r="AF130">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AG130">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK130">
-        <v>2.7</v>
+        <v>1.17</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-10-03 20:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,7 +21615,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.72</v>
+        <v>1.37</v>
       </c>
       <c r="O131">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="P131">
-        <v>2.34</v>
+        <v>7.37</v>
       </c>
       <c r="Q131">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="R131">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="S131">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T131">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U131">
-        <v>3.08</v>
+        <v>2.22</v>
       </c>
       <c r="V131">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z131">
-        <v>2.83</v>
+        <v>4.55</v>
       </c>
       <c r="AA131">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AB131">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AC131">
-        <v>3.96</v>
+        <v>2.26</v>
       </c>
       <c r="AD131">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="AE131">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF131">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG131">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK131">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-03 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q132">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S132">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T132">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U132">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="V132">
+        <v>1.28</v>
+      </c>
+      <c r="W132">
+        <v>1.05</v>
+      </c>
+      <c r="X132">
+        <v>1.01</v>
+      </c>
+      <c r="Y132">
         <v>1.33</v>
       </c>
-      <c r="W132">
-        <v>1.03</v>
-      </c>
-      <c r="X132">
-        <v>1.03</v>
-      </c>
-      <c r="Y132">
-        <v>1.36</v>
-      </c>
       <c r="Z132">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA132">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB132">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC132">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="AD132">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF132">
         <v>1.85</v>
       </c>
       <c r="AG132">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
+        <v>2.17</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.61</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.19</v>
+      </c>
+      <c r="Z35">
+        <v>3.74</v>
+      </c>
+      <c r="AA35">
+        <v>1.73</v>
+      </c>
+      <c r="AB35">
+        <v>1.99</v>
+      </c>
+      <c r="AC35">
+        <v>2.7</v>
+      </c>
+      <c r="AD35">
+        <v>1.35</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
         <v>2.2</v>
       </c>
-      <c r="S35">
-        <v>1.38</v>
-      </c>
-      <c r="T35">
-        <v>2.91</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.08</v>
-      </c>
-      <c r="AA35">
-        <v>1.94</v>
-      </c>
-      <c r="AB35">
-        <v>1.83</v>
-      </c>
-      <c r="AC35">
-        <v>3.28</v>
-      </c>
-      <c r="AD35">
-        <v>1.25</v>
-      </c>
-      <c r="AE35">
-        <v>1.1</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>1.94</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
+        <v>2.91</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.36</v>
+      </c>
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
         <v>3.08</v>
       </c>
-      <c r="U37">
-        <v>2.48</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.08</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.26</v>
-      </c>
-      <c r="Z37">
-        <v>3.58</v>
-      </c>
       <c r="AA37">
+        <v>1.94</v>
+      </c>
+      <c r="AB37">
         <v>1.83</v>
       </c>
-      <c r="AB37">
-        <v>1.94</v>
-      </c>
       <c r="AC37">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U39">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z39">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA39">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC39">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD39">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="O44">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="P44">
-        <v>2.53</v>
+        <v>3.03</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W44">
+        <v>1.09</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>1.16</v>
+      </c>
+      <c r="Z44">
+        <v>4.1</v>
+      </c>
+      <c r="AA44">
+        <v>1.68</v>
+      </c>
+      <c r="AB44">
+        <v>2.11</v>
+      </c>
+      <c r="AC44">
+        <v>2.62</v>
+      </c>
+      <c r="AD44">
+        <v>1.38</v>
+      </c>
+      <c r="AE44">
         <v>1.11</v>
       </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.14</v>
-      </c>
-      <c r="Z44">
-        <v>4.7</v>
-      </c>
-      <c r="AA44">
-        <v>1.53</v>
-      </c>
-      <c r="AB44">
-        <v>2.21</v>
-      </c>
-      <c r="AC44">
-        <v>2.4</v>
-      </c>
-      <c r="AD44">
-        <v>1.53</v>
-      </c>
-      <c r="AE44">
-        <v>1.17</v>
-      </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="O45">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="P45">
-        <v>3.03</v>
+        <v>2.53</v>
       </c>
       <c r="Q45">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R45">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA45">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AC45">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AD45">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG45">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q28">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.81</v>
+      </c>
+      <c r="AB34">
+        <v>1.95</v>
+      </c>
+      <c r="AC34">
+        <v>2.66</v>
+      </c>
+      <c r="AD34">
+        <v>1.41</v>
+      </c>
+      <c r="AE34">
         <v>1.12</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.25</v>
-      </c>
-      <c r="Z34">
-        <v>3.82</v>
-      </c>
-      <c r="AA34">
-        <v>1.79</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.83</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="U35">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.42</v>
+      </c>
+      <c r="AA35">
+        <v>1.88</v>
+      </c>
+      <c r="AB35">
+        <v>1.88</v>
+      </c>
+      <c r="AC35">
+        <v>3.08</v>
+      </c>
+      <c r="AD35">
+        <v>1.28</v>
+      </c>
+      <c r="AE35">
+        <v>1.06</v>
+      </c>
+      <c r="AF35">
+        <v>1.75</v>
+      </c>
+      <c r="AG35">
+        <v>2</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.45</v>
-      </c>
-      <c r="W35">
-        <v>1.09</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.19</v>
-      </c>
-      <c r="Z35">
-        <v>3.74</v>
-      </c>
-      <c r="AA35">
-        <v>1.73</v>
-      </c>
-      <c r="AB35">
-        <v>1.99</v>
-      </c>
-      <c r="AC35">
-        <v>2.7</v>
-      </c>
-      <c r="AD35">
-        <v>1.35</v>
-      </c>
-      <c r="AE35">
-        <v>1.11</v>
-      </c>
-      <c r="AF35">
-        <v>1.6</v>
-      </c>
-      <c r="AG35">
-        <v>2.2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.3</v>
-      </c>
-      <c r="AK35">
-        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
+        <v>2.17</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.14</v>
+      </c>
+      <c r="U37">
+        <v>2.61</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.09</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.19</v>
+      </c>
+      <c r="Z37">
+        <v>3.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>1.99</v>
+      </c>
+      <c r="AC37">
+        <v>2.7</v>
+      </c>
+      <c r="AD37">
+        <v>1.35</v>
+      </c>
+      <c r="AE37">
+        <v>1.11</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.2</v>
       </c>
-      <c r="S37">
-        <v>1.38</v>
-      </c>
-      <c r="T37">
-        <v>2.91</v>
-      </c>
-      <c r="U37">
-        <v>2.88</v>
-      </c>
-      <c r="V37">
-        <v>1.36</v>
-      </c>
-      <c r="W37">
-        <v>1.07</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.28</v>
-      </c>
-      <c r="Z37">
-        <v>3.08</v>
-      </c>
-      <c r="AA37">
-        <v>1.94</v>
-      </c>
-      <c r="AB37">
-        <v>1.83</v>
-      </c>
-      <c r="AC37">
-        <v>3.28</v>
-      </c>
-      <c r="AD37">
-        <v>1.25</v>
-      </c>
-      <c r="AE37">
-        <v>1.1</v>
-      </c>
-      <c r="AF37">
-        <v>1.75</v>
-      </c>
-      <c r="AG37">
-        <v>1.94</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE81">
         <v>0</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
         <v>3.55</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="R15">
         <v>2.02</v>
@@ -2775,10 +2775,10 @@
         <v>2.74</v>
       </c>
       <c r="U15">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA15">
         <v>2</v>
@@ -2799,10 +2799,10 @@
         <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
         <v>1.05</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
+        <v>2.41</v>
+      </c>
+      <c r="O16">
+        <v>3.57</v>
+      </c>
+      <c r="P16">
         <v>2.8</v>
       </c>
-      <c r="O16">
-        <v>3.51</v>
-      </c>
-      <c r="P16">
-        <v>2.44</v>
-      </c>
       <c r="Q16">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="R16">
         <v>2.02</v>
@@ -2938,10 +2938,10 @@
         <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.04</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
         <v>2</v>
@@ -2962,10 +2962,10 @@
         <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.05</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,68 +5358,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="O31">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="P31">
-        <v>4.1</v>
+        <v>2.73</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S31">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>4.85</v>
+        <v>3.92</v>
       </c>
       <c r="AA31">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AC31">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="AD31">
+        <v>1.39</v>
+      </c>
+      <c r="AE31">
+        <v>1.15</v>
+      </c>
+      <c r="AF31">
         <v>1.61</v>
       </c>
-      <c r="AE31">
-        <v>1.19</v>
-      </c>
-      <c r="AF31">
-        <v>1.52</v>
-      </c>
       <c r="AG31">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32">
@@ -5521,68 +5521,68 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N32">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O32">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P32">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q32">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
         <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="AA32">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,68 +5684,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="O33">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="R33">
         <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U33">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="P35">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q35">
-        <v>3.17</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="T35">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>2.27</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB37">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
+        <v>2.71</v>
+      </c>
+      <c r="U39">
+        <v>2.81</v>
+      </c>
+      <c r="V39">
+        <v>1.36</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.27</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.88</v>
+      </c>
+      <c r="AB39">
+        <v>1.88</v>
+      </c>
+      <c r="AC39">
         <v>3.08</v>
       </c>
-      <c r="U39">
-        <v>2.48</v>
-      </c>
-      <c r="V39">
-        <v>1.46</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.26</v>
-      </c>
-      <c r="Z39">
-        <v>3.58</v>
-      </c>
-      <c r="AA39">
-        <v>1.83</v>
-      </c>
-      <c r="AB39">
-        <v>1.94</v>
-      </c>
-      <c r="AC39">
-        <v>3.11</v>
-      </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.11</v>
+        <v>2.27</v>
       </c>
       <c r="O49">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="P49">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
       <c r="Q49">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T49">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA49">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AC49">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
+        <v>1.73</v>
+      </c>
+      <c r="AG49">
+        <v>1.98</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.31</v>
+      </c>
+      <c r="AK49">
         <v>1.56</v>
-      </c>
-      <c r="AG49">
-        <v>2.24</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.26</v>
-      </c>
-      <c r="AK49">
-        <v>1.29</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.27</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>3.19</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>2.96</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
+        <v>1.81</v>
+      </c>
+      <c r="AB50">
+        <v>1.99</v>
+      </c>
+      <c r="AC50">
+        <v>2.83</v>
+      </c>
+      <c r="AD50">
+        <v>1.36</v>
+      </c>
+      <c r="AE50">
+        <v>1.08</v>
+      </c>
+      <c r="AF50">
+        <v>1.71</v>
+      </c>
+      <c r="AG50">
         <v>2</v>
       </c>
-      <c r="AB50">
-        <v>1.83</v>
-      </c>
-      <c r="AC50">
-        <v>3.2</v>
-      </c>
-      <c r="AD50">
-        <v>1.3</v>
-      </c>
-      <c r="AE50">
-        <v>1.06</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>1.98</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.77</v>
+        <v>1.75</v>
       </c>
       <c r="O66">
-        <v>3.55</v>
+        <v>4.19</v>
       </c>
       <c r="P66">
+        <v>4.16</v>
+      </c>
+      <c r="Q66">
+        <v>2.38</v>
+      </c>
+      <c r="R66">
+        <v>2.42</v>
+      </c>
+      <c r="S66">
+        <v>1.32</v>
+      </c>
+      <c r="T66">
+        <v>3.16</v>
+      </c>
+      <c r="U66">
         <v>2.44</v>
       </c>
-      <c r="Q66">
-        <v>3.5</v>
-      </c>
-      <c r="R66">
-        <v>2.21</v>
-      </c>
-      <c r="S66">
-        <v>1.41</v>
-      </c>
-      <c r="T66">
-        <v>2.79</v>
-      </c>
-      <c r="U66">
-        <v>2.77</v>
-      </c>
       <c r="V66">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA66">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB66">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC66">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD66">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK66">
-        <v>1.35</v>
+        <v>1.96</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
+        <v>2.77</v>
+      </c>
+      <c r="O68">
+        <v>3.55</v>
+      </c>
+      <c r="P68">
+        <v>2.44</v>
+      </c>
+      <c r="Q68">
+        <v>3.5</v>
+      </c>
+      <c r="R68">
+        <v>2.21</v>
+      </c>
+      <c r="S68">
+        <v>1.41</v>
+      </c>
+      <c r="T68">
+        <v>2.79</v>
+      </c>
+      <c r="U68">
+        <v>2.77</v>
+      </c>
+      <c r="V68">
+        <v>1.42</v>
+      </c>
+      <c r="W68">
+        <v>1.04</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>1.34</v>
+      </c>
+      <c r="Z68">
+        <v>3.08</v>
+      </c>
+      <c r="AA68">
+        <v>2.03</v>
+      </c>
+      <c r="AB68">
+        <v>1.78</v>
+      </c>
+      <c r="AC68">
+        <v>3.45</v>
+      </c>
+      <c r="AD68">
+        <v>1.27</v>
+      </c>
+      <c r="AE68">
+        <v>1.05</v>
+      </c>
+      <c r="AF68">
         <v>1.75</v>
       </c>
-      <c r="O68">
-        <v>4.19</v>
-      </c>
-      <c r="P68">
-        <v>4.16</v>
-      </c>
-      <c r="Q68">
-        <v>2.38</v>
-      </c>
-      <c r="R68">
-        <v>2.42</v>
-      </c>
-      <c r="S68">
-        <v>1.32</v>
-      </c>
-      <c r="T68">
-        <v>3.16</v>
-      </c>
-      <c r="U68">
-        <v>2.44</v>
-      </c>
-      <c r="V68">
-        <v>1.54</v>
-      </c>
-      <c r="W68">
-        <v>1.09</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>1.19</v>
-      </c>
-      <c r="Z68">
-        <v>4.1</v>
-      </c>
-      <c r="AA68">
-        <v>1.7</v>
-      </c>
-      <c r="AB68">
-        <v>2.15</v>
-      </c>
-      <c r="AC68">
-        <v>2.6</v>
-      </c>
-      <c r="AD68">
-        <v>1.47</v>
-      </c>
-      <c r="AE68">
-        <v>1.15</v>
-      </c>
-      <c r="AF68">
-        <v>1.64</v>
-      </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>2.99</v>
+        <v>4.39</v>
       </c>
       <c r="Q72">
-        <v>2.99</v>
+        <v>2.27</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S72">
+        <v>1.44</v>
+      </c>
+      <c r="T72">
+        <v>2.69</v>
+      </c>
+      <c r="U72">
+        <v>2.9</v>
+      </c>
+      <c r="V72">
         <v>1.38</v>
       </c>
-      <c r="T72">
-        <v>2.88</v>
-      </c>
-      <c r="U72">
-        <v>2.67</v>
-      </c>
-      <c r="V72">
-        <v>1.45</v>
-      </c>
       <c r="W72">
+        <v>1.03</v>
+      </c>
+      <c r="X72">
+        <v>1.03</v>
+      </c>
+      <c r="Y72">
+        <v>1.33</v>
+      </c>
+      <c r="Z72">
+        <v>3.1</v>
+      </c>
+      <c r="AA72">
+        <v>2.02</v>
+      </c>
+      <c r="AB72">
+        <v>1.79</v>
+      </c>
+      <c r="AC72">
+        <v>3.43</v>
+      </c>
+      <c r="AD72">
+        <v>1.27</v>
+      </c>
+      <c r="AE72">
         <v>1.05</v>
       </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.27</v>
-      </c>
-      <c r="Z72">
-        <v>3.43</v>
-      </c>
-      <c r="AA72">
-        <v>1.77</v>
-      </c>
-      <c r="AB72">
+      <c r="AF72">
         <v>1.93</v>
       </c>
-      <c r="AC72">
-        <v>3.14</v>
-      </c>
-      <c r="AD72">
-        <v>1.34</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.68</v>
-      </c>
       <c r="AG72">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK72">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O73">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
-        <v>4.39</v>
+        <v>2.99</v>
       </c>
       <c r="Q73">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="R73">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T73">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U73">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V73">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z73">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="AA73">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC73">
-        <v>3.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD73">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q112">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R112">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC112">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE112">
         <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P28">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q28">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="P30">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC30">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AD30">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE30">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,68 +5358,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O31">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P31">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T31">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
         <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
         <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC31">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="O32">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="R32">
+        <v>2.4</v>
+      </c>
+      <c r="S32">
+        <v>1.18</v>
+      </c>
+      <c r="T32">
+        <v>3.8</v>
+      </c>
+      <c r="U32">
         <v>2.2</v>
       </c>
-      <c r="S32">
-        <v>1.31</v>
-      </c>
-      <c r="T32">
-        <v>3.2</v>
-      </c>
-      <c r="U32">
-        <v>2.57</v>
-      </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z32">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC32">
-        <v>3.08</v>
+        <v>2.27</v>
       </c>
       <c r="AD32">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P33">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q33">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
         <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1.2</v>
+      </c>
+      <c r="Z33">
+        <v>4.1</v>
+      </c>
+      <c r="AA33">
+        <v>1.81</v>
+      </c>
+      <c r="AB33">
+        <v>1.95</v>
+      </c>
+      <c r="AC33">
+        <v>2.66</v>
+      </c>
+      <c r="AD33">
+        <v>1.41</v>
+      </c>
+      <c r="AE33">
         <v>1.12</v>
       </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.25</v>
-      </c>
-      <c r="Z33">
-        <v>3.82</v>
-      </c>
-      <c r="AA33">
-        <v>1.79</v>
-      </c>
-      <c r="AB33">
-        <v>2.15</v>
-      </c>
-      <c r="AC33">
-        <v>2.83</v>
-      </c>
-      <c r="AD33">
-        <v>1.33</v>
-      </c>
-      <c r="AE33">
-        <v>1.09</v>
-      </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>4.73</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>2.15</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AA35">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>2.27</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="O67">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="P67">
-        <v>3.49</v>
+        <v>2.44</v>
       </c>
       <c r="Q67">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="R67">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="S67">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="T67">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="U67">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V67">
+        <v>1.42</v>
+      </c>
+      <c r="W67">
+        <v>1.04</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>1.34</v>
+      </c>
+      <c r="Z67">
+        <v>3.08</v>
+      </c>
+      <c r="AA67">
+        <v>2.03</v>
+      </c>
+      <c r="AB67">
+        <v>1.78</v>
+      </c>
+      <c r="AC67">
+        <v>3.45</v>
+      </c>
+      <c r="AD67">
+        <v>1.27</v>
+      </c>
+      <c r="AE67">
+        <v>1.05</v>
+      </c>
+      <c r="AF67">
+        <v>1.75</v>
+      </c>
+      <c r="AG67">
+        <v>1.95</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.25</v>
+      </c>
+      <c r="AK67">
         <v>1.35</v>
-      </c>
-      <c r="W67">
-        <v>1.02</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.4</v>
-      </c>
-      <c r="Z67">
-        <v>2.85</v>
-      </c>
-      <c r="AA67">
-        <v>2.16</v>
-      </c>
-      <c r="AB67">
-        <v>1.69</v>
-      </c>
-      <c r="AC67">
-        <v>3.84</v>
-      </c>
-      <c r="AD67">
-        <v>1.22</v>
-      </c>
-      <c r="AE67">
-        <v>1.02</v>
-      </c>
-      <c r="AF67">
-        <v>1.91</v>
-      </c>
-      <c r="AG67">
-        <v>1.8</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.26</v>
-      </c>
-      <c r="AK67">
-        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="P68">
-        <v>2.44</v>
+        <v>3.49</v>
       </c>
       <c r="Q68">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R68">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="S68">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T68">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="U68">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="V68">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z68">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AA68">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AB68">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AC68">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="AD68">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>4.39</v>
+        <v>2.99</v>
       </c>
       <c r="Q72">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="R72">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T72">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U72">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V72">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W72">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z72">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="AA72">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB72">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>3.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD72">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AG72">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK72">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O73">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P73">
-        <v>2.99</v>
+        <v>4.39</v>
       </c>
       <c r="Q73">
-        <v>2.99</v>
+        <v>2.27</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S73">
+        <v>1.44</v>
+      </c>
+      <c r="T73">
+        <v>2.69</v>
+      </c>
+      <c r="U73">
+        <v>2.9</v>
+      </c>
+      <c r="V73">
         <v>1.38</v>
       </c>
-      <c r="T73">
-        <v>2.88</v>
-      </c>
-      <c r="U73">
-        <v>2.67</v>
-      </c>
-      <c r="V73">
-        <v>1.45</v>
-      </c>
       <c r="W73">
+        <v>1.03</v>
+      </c>
+      <c r="X73">
+        <v>1.03</v>
+      </c>
+      <c r="Y73">
+        <v>1.33</v>
+      </c>
+      <c r="Z73">
+        <v>3.1</v>
+      </c>
+      <c r="AA73">
+        <v>2.02</v>
+      </c>
+      <c r="AB73">
+        <v>1.79</v>
+      </c>
+      <c r="AC73">
+        <v>3.43</v>
+      </c>
+      <c r="AD73">
+        <v>1.27</v>
+      </c>
+      <c r="AE73">
         <v>1.05</v>
       </c>
-      <c r="X73">
-        <v>1.01</v>
-      </c>
-      <c r="Y73">
-        <v>1.27</v>
-      </c>
-      <c r="Z73">
-        <v>3.43</v>
-      </c>
-      <c r="AA73">
-        <v>1.77</v>
-      </c>
-      <c r="AB73">
+      <c r="AF73">
         <v>1.93</v>
       </c>
-      <c r="AC73">
-        <v>3.14</v>
-      </c>
-      <c r="AD73">
-        <v>1.34</v>
-      </c>
-      <c r="AE73">
-        <v>1.08</v>
-      </c>
-      <c r="AF73">
-        <v>1.68</v>
-      </c>
       <c r="AG73">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
         <v>1.55</v>
@@ -4088,50 +4088,50 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
         <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
+        <v>1.97</v>
+      </c>
+      <c r="AC23">
+        <v>2.38</v>
+      </c>
+      <c r="AD23">
+        <v>1.46</v>
+      </c>
+      <c r="AE23">
+        <v>1.16</v>
+      </c>
+      <c r="AF23">
+        <v>1.6</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.16</v>
+      </c>
+      <c r="AK23">
         <v>1.96</v>
-      </c>
-      <c r="AC23">
-        <v>2.49</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
-      <c r="AE23">
-        <v>1.13</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
-      <c r="AG23">
-        <v>2.32</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q25">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q28">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD33">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,84 +6010,84 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>2.86</v>
+      </c>
+      <c r="U35">
+        <v>2.46</v>
+      </c>
+      <c r="V35">
+        <v>1.46</v>
+      </c>
+      <c r="W35">
+        <v>1.12</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.82</v>
+      </c>
+      <c r="AA35">
+        <v>1.79</v>
+      </c>
+      <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.83</v>
+      </c>
+      <c r="AD35">
+        <v>1.33</v>
+      </c>
+      <c r="AE35">
+        <v>1.09</v>
+      </c>
+      <c r="AF35">
+        <v>1.62</v>
+      </c>
+      <c r="AG35">
+        <v>2.15</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.88</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.05</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.42</v>
-      </c>
-      <c r="AD35">
-        <v>1.23</v>
-      </c>
-      <c r="AE35">
-        <v>1.05</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>1.96</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.29</v>
-      </c>
-      <c r="AK35">
-        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>4.1</v>
+      </c>
+      <c r="AA36">
+        <v>1.81</v>
+      </c>
+      <c r="AB36">
+        <v>1.95</v>
+      </c>
+      <c r="AC36">
+        <v>2.66</v>
+      </c>
+      <c r="AD36">
+        <v>1.41</v>
+      </c>
+      <c r="AE36">
         <v>1.12</v>
       </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.82</v>
-      </c>
-      <c r="AA36">
-        <v>1.79</v>
-      </c>
-      <c r="AB36">
-        <v>2.15</v>
-      </c>
-      <c r="AC36">
-        <v>2.83</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.09</v>
-      </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,32 +6662,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
+        <v>3.1</v>
+      </c>
+      <c r="P39">
+        <v>2.59</v>
+      </c>
+      <c r="Q39">
         <v>3.25</v>
       </c>
-      <c r="P39">
-        <v>2.95</v>
-      </c>
-      <c r="Q39">
-        <v>3.17</v>
-      </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
+        <v>3.05</v>
+      </c>
+      <c r="AA39">
+        <v>1.95</v>
+      </c>
+      <c r="AB39">
+        <v>1.75</v>
+      </c>
+      <c r="AC39">
         <v>3.42</v>
       </c>
-      <c r="AA39">
-        <v>1.88</v>
-      </c>
-      <c r="AB39">
-        <v>1.88</v>
-      </c>
-      <c r="AC39">
-        <v>3.08</v>
-      </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>1.55</v>
@@ -4088,34 +4088,34 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
         <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P28">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q28">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q33">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB34">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="Q35">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA35">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC35">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
         <v>3.42</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.21</v>
+      </c>
+      <c r="O60">
+        <v>3.37</v>
+      </c>
+      <c r="P60">
+        <v>3.34</v>
+      </c>
+      <c r="Q60">
+        <v>3.06</v>
+      </c>
+      <c r="R60">
+        <v>2.07</v>
+      </c>
+      <c r="S60">
+        <v>1.51</v>
+      </c>
+      <c r="T60">
+        <v>2.38</v>
+      </c>
+      <c r="U60">
+        <v>3.3</v>
+      </c>
+      <c r="V60">
+        <v>1.25</v>
+      </c>
+      <c r="W60">
+        <v>1.01</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.46</v>
+      </c>
+      <c r="Z60">
+        <v>2.64</v>
+      </c>
+      <c r="AA60">
+        <v>2.37</v>
+      </c>
+      <c r="AB60">
         <v>1.53</v>
       </c>
-      <c r="O60">
-        <v>3.7</v>
-      </c>
-      <c r="P60">
-        <v>5.25</v>
-      </c>
-      <c r="Q60">
-        <v>2.13</v>
-      </c>
-      <c r="R60">
-        <v>2.14</v>
-      </c>
-      <c r="S60">
-        <v>1.38</v>
-      </c>
-      <c r="T60">
-        <v>2.89</v>
-      </c>
-      <c r="U60">
-        <v>2.66</v>
-      </c>
-      <c r="V60">
-        <v>1.45</v>
-      </c>
-      <c r="W60">
-        <v>1.06</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>1.2</v>
-      </c>
-      <c r="Z60">
-        <v>3.68</v>
-      </c>
-      <c r="AA60">
-        <v>1.75</v>
-      </c>
-      <c r="AB60">
-        <v>1.93</v>
-      </c>
       <c r="AC60">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O61">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q61">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R61">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S61">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U61">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC61">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD61">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U110">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.5</v>
+      </c>
+      <c r="O23">
+        <v>4.3</v>
+      </c>
+      <c r="P23">
+        <v>4.83</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>3.62</v>
-      </c>
-      <c r="P23">
-        <v>3.04</v>
-      </c>
-      <c r="Q23">
-        <v>2.52</v>
-      </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q28">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
+        <v>3.1</v>
+      </c>
+      <c r="P35">
+        <v>2.59</v>
+      </c>
+      <c r="Q35">
         <v>3.25</v>
       </c>
-      <c r="P35">
-        <v>2.95</v>
-      </c>
-      <c r="Q35">
-        <v>3.17</v>
-      </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
         <v>1.36</v>
@@ -6044,34 +6044,34 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
+        <v>3.05</v>
+      </c>
+      <c r="AA35">
+        <v>1.95</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
         <v>3.42</v>
       </c>
-      <c r="AA35">
-        <v>1.88</v>
-      </c>
-      <c r="AB35">
-        <v>1.88</v>
-      </c>
-      <c r="AC35">
-        <v>3.08</v>
-      </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>3.87</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="O54">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="P54">
-        <v>3.33</v>
+        <v>15.5</v>
       </c>
       <c r="Q54">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="R54">
-        <v>2.55</v>
+        <v>3.74</v>
       </c>
       <c r="S54">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="T54">
+        <v>6.5</v>
+      </c>
+      <c r="U54">
+        <v>1.58</v>
+      </c>
+      <c r="V54">
+        <v>2.19</v>
+      </c>
+      <c r="W54">
+        <v>1.36</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.01</v>
+      </c>
+      <c r="Z54">
+        <v>10</v>
+      </c>
+      <c r="AA54">
+        <v>1.14</v>
+      </c>
+      <c r="AB54">
         <v>4.8</v>
       </c>
-      <c r="U54">
-        <v>1.78</v>
-      </c>
-      <c r="V54">
-        <v>2</v>
-      </c>
-      <c r="W54">
-        <v>1.25</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.05</v>
-      </c>
-      <c r="Z54">
-        <v>8</v>
-      </c>
-      <c r="AA54">
-        <v>1.28</v>
-      </c>
-      <c r="AB54">
-        <v>3.6</v>
-      </c>
       <c r="AC54">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AD54">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="AE54">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AF54">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>3.24</v>
+        <v>2.32</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK54">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="O55">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>15.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q55">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="R55">
-        <v>3.74</v>
+        <v>2.55</v>
       </c>
       <c r="S55">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T55">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="U55">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V55">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="W55">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z55">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA55">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AB55">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC55">
+        <v>1.7</v>
+      </c>
+      <c r="AD55">
+        <v>1.99</v>
+      </c>
+      <c r="AE55">
         <v>1.44</v>
       </c>
-      <c r="AD55">
-        <v>2.42</v>
-      </c>
-      <c r="AE55">
-        <v>1.67</v>
-      </c>
       <c r="AF55">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AG55">
-        <v>2.32</v>
+        <v>3.24</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK55">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R60">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S60">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T60">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U60">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA60">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD60">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG60">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>2.21</v>
+      </c>
+      <c r="O61">
+        <v>3.37</v>
+      </c>
+      <c r="P61">
+        <v>3.34</v>
+      </c>
+      <c r="Q61">
+        <v>3.06</v>
+      </c>
+      <c r="R61">
+        <v>2.07</v>
+      </c>
+      <c r="S61">
+        <v>1.51</v>
+      </c>
+      <c r="T61">
+        <v>2.38</v>
+      </c>
+      <c r="U61">
+        <v>3.3</v>
+      </c>
+      <c r="V61">
+        <v>1.25</v>
+      </c>
+      <c r="W61">
+        <v>1.01</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.46</v>
+      </c>
+      <c r="Z61">
+        <v>2.64</v>
+      </c>
+      <c r="AA61">
+        <v>2.37</v>
+      </c>
+      <c r="AB61">
         <v>1.53</v>
       </c>
-      <c r="O61">
-        <v>3.7</v>
-      </c>
-      <c r="P61">
-        <v>5.25</v>
-      </c>
-      <c r="Q61">
-        <v>2.13</v>
-      </c>
-      <c r="R61">
-        <v>2.14</v>
-      </c>
-      <c r="S61">
-        <v>1.38</v>
-      </c>
-      <c r="T61">
-        <v>2.89</v>
-      </c>
-      <c r="U61">
-        <v>2.66</v>
-      </c>
-      <c r="V61">
-        <v>1.45</v>
-      </c>
-      <c r="W61">
-        <v>1.06</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>1.2</v>
-      </c>
-      <c r="Z61">
-        <v>3.68</v>
-      </c>
-      <c r="AA61">
-        <v>1.75</v>
-      </c>
-      <c r="AB61">
-        <v>1.93</v>
-      </c>
       <c r="AC61">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG61">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>4.73</v>
       </c>
       <c r="Q33">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA33">
+        <v>1.83</v>
+      </c>
+      <c r="AB33">
         <v>1.94</v>
       </c>
-      <c r="AB33">
-        <v>1.83</v>
-      </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
         <v>2.88</v>
@@ -6041,37 +6041,37 @@
         <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
+        <v>1.12</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.25</v>
+      </c>
+      <c r="Z36">
+        <v>3.82</v>
+      </c>
+      <c r="AA36">
+        <v>1.79</v>
+      </c>
+      <c r="AB36">
+        <v>2.15</v>
+      </c>
+      <c r="AC36">
+        <v>2.83</v>
+      </c>
+      <c r="AD36">
+        <v>1.33</v>
+      </c>
+      <c r="AE36">
         <v>1.09</v>
       </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.19</v>
-      </c>
-      <c r="Z36">
-        <v>3.74</v>
-      </c>
-      <c r="AA36">
-        <v>1.73</v>
-      </c>
-      <c r="AB36">
-        <v>1.99</v>
-      </c>
-      <c r="AC36">
-        <v>2.7</v>
-      </c>
-      <c r="AD36">
-        <v>1.35</v>
-      </c>
-      <c r="AE36">
-        <v>1.11</v>
-      </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
+        <v>2.17</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.14</v>
+      </c>
+      <c r="U37">
+        <v>2.61</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.09</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.19</v>
+      </c>
+      <c r="Z37">
+        <v>3.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>1.99</v>
+      </c>
+      <c r="AC37">
+        <v>2.7</v>
+      </c>
+      <c r="AD37">
+        <v>1.35</v>
+      </c>
+      <c r="AE37">
+        <v>1.11</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.2</v>
       </c>
-      <c r="S37">
-        <v>1.29</v>
-      </c>
-      <c r="T37">
-        <v>2.86</v>
-      </c>
-      <c r="U37">
-        <v>2.46</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.12</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>3.82</v>
-      </c>
-      <c r="AA37">
-        <v>1.79</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.83</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
-      <c r="AF37">
-        <v>1.62</v>
-      </c>
-      <c r="AG37">
-        <v>2.15</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O38">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z38">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD38">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
+        <v>3.25</v>
+      </c>
+      <c r="R39">
         <v>2.1</v>
       </c>
-      <c r="R39">
-        <v>2.3</v>
-      </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O112">
         <v>3.55</v>
       </c>
       <c r="P112">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S112">
+        <v>1.37</v>
+      </c>
+      <c r="T112">
+        <v>2.69</v>
+      </c>
+      <c r="U112">
+        <v>2.8</v>
+      </c>
+      <c r="V112">
+        <v>1.35</v>
+      </c>
+      <c r="W112">
+        <v>1.06</v>
+      </c>
+      <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
         <v>1.33</v>
       </c>
-      <c r="T112">
-        <v>2.83</v>
-      </c>
-      <c r="U112">
-        <v>2.5</v>
-      </c>
-      <c r="V112">
-        <v>1.44</v>
-      </c>
-      <c r="W112">
-        <v>1.07</v>
-      </c>
-      <c r="X112">
-        <v>1</v>
-      </c>
-      <c r="Y112">
-        <v>1.23</v>
-      </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC112">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD112">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF112">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.5</v>
+      </c>
+      <c r="O23">
+        <v>4.3</v>
+      </c>
+      <c r="P23">
+        <v>4.83</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>3.62</v>
-      </c>
-      <c r="P23">
-        <v>3.04</v>
-      </c>
-      <c r="Q23">
-        <v>2.52</v>
-      </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,68 +5684,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q33">
+        <v>3.25</v>
+      </c>
+      <c r="R33">
         <v>2.1</v>
       </c>
-      <c r="R33">
-        <v>2.3</v>
-      </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
         <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA35">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
+        <v>2.17</v>
+      </c>
+      <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.14</v>
+      </c>
+      <c r="U36">
+        <v>2.61</v>
+      </c>
+      <c r="V36">
+        <v>1.45</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.19</v>
+      </c>
+      <c r="Z36">
+        <v>3.74</v>
+      </c>
+      <c r="AA36">
+        <v>1.73</v>
+      </c>
+      <c r="AB36">
+        <v>1.99</v>
+      </c>
+      <c r="AC36">
+        <v>2.7</v>
+      </c>
+      <c r="AD36">
+        <v>1.35</v>
+      </c>
+      <c r="AE36">
+        <v>1.11</v>
+      </c>
+      <c r="AF36">
+        <v>1.6</v>
+      </c>
+      <c r="AG36">
         <v>2.2</v>
       </c>
-      <c r="S36">
-        <v>1.29</v>
-      </c>
-      <c r="T36">
-        <v>2.86</v>
-      </c>
-      <c r="U36">
-        <v>2.46</v>
-      </c>
-      <c r="V36">
-        <v>1.46</v>
-      </c>
-      <c r="W36">
-        <v>1.12</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.82</v>
-      </c>
-      <c r="AA36">
-        <v>1.79</v>
-      </c>
-      <c r="AB36">
-        <v>2.15</v>
-      </c>
-      <c r="AC36">
-        <v>2.83</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.09</v>
-      </c>
-      <c r="AF36">
-        <v>1.62</v>
-      </c>
-      <c r="AG36">
-        <v>2.15</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q38">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
         <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC38">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U110">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O112">
         <v>3.55</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q112">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R112">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB112">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC112">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD112">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE112">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P28">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q28">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,32 +5684,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
         <v>1.36</v>
@@ -5718,34 +5718,34 @@
         <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
+        <v>1.27</v>
+      </c>
+      <c r="Z33">
+        <v>3.42</v>
+      </c>
+      <c r="AA33">
+        <v>1.88</v>
+      </c>
+      <c r="AB33">
+        <v>1.88</v>
+      </c>
+      <c r="AC33">
+        <v>3.08</v>
+      </c>
+      <c r="AD33">
         <v>1.28</v>
       </c>
-      <c r="Z33">
-        <v>3.05</v>
-      </c>
-      <c r="AA33">
-        <v>1.95</v>
-      </c>
-      <c r="AB33">
-        <v>1.75</v>
-      </c>
-      <c r="AC33">
-        <v>3.42</v>
-      </c>
-      <c r="AD33">
-        <v>1.23</v>
-      </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
         <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
+        <v>3.08</v>
+      </c>
+      <c r="AA35">
+        <v>1.94</v>
+      </c>
+      <c r="AB35">
+        <v>1.83</v>
+      </c>
+      <c r="AC35">
+        <v>3.28</v>
+      </c>
+      <c r="AD35">
         <v>1.25</v>
       </c>
-      <c r="Z35">
-        <v>3.82</v>
-      </c>
-      <c r="AA35">
-        <v>1.79</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.83</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>4.73</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="AD36">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.56</v>
+        <v>2.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q38">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB38">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC38">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
+        <v>3.25</v>
+      </c>
+      <c r="R39">
         <v>2.1</v>
       </c>
-      <c r="R39">
-        <v>2.3</v>
-      </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -11260,7 +11260,7 @@
         <v>1.04</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.34</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q112">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC112">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
         <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL117">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1785,55 +1785,55 @@
         <v>2.65</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>2.99</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>2.66</v>
+      </c>
+      <c r="O13">
+        <v>3.56</v>
+      </c>
+      <c r="P13">
+        <v>2.53</v>
+      </c>
+      <c r="Q13">
+        <v>3.48</v>
+      </c>
+      <c r="R13">
+        <v>2.03</v>
+      </c>
+      <c r="S13">
+        <v>1.42</v>
+      </c>
+      <c r="T13">
+        <v>2.75</v>
+      </c>
+      <c r="U13">
         <v>2.81</v>
       </c>
-      <c r="O13">
-        <v>3.44</v>
-      </c>
-      <c r="P13">
-        <v>2.46</v>
-      </c>
-      <c r="Q13">
-        <v>3.54</v>
-      </c>
-      <c r="R13">
-        <v>1.95</v>
-      </c>
-      <c r="S13">
-        <v>1.39</v>
-      </c>
-      <c r="T13">
-        <v>2.59</v>
-      </c>
-      <c r="U13">
-        <v>3.03</v>
-      </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>2.78</v>
+        <v>3.06</v>
       </c>
       <c r="AA13">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC13">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
         <v>1.36</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="O14">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="R14">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC14">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.36</v>
@@ -3578,55 +3578,55 @@
         <v>1.63</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.5</v>
+      </c>
+      <c r="O23">
+        <v>4.3</v>
+      </c>
+      <c r="P23">
+        <v>4.83</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>3.62</v>
-      </c>
-      <c r="P23">
-        <v>3.04</v>
-      </c>
-      <c r="Q23">
-        <v>2.52</v>
-      </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="Q33">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5847,68 +5847,68 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
         <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA35">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
+        <v>2.91</v>
+      </c>
+      <c r="U36">
+        <v>2.88</v>
+      </c>
+      <c r="V36">
+        <v>1.36</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
         <v>3.08</v>
       </c>
-      <c r="U36">
-        <v>2.48</v>
-      </c>
-      <c r="V36">
-        <v>1.46</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.26</v>
-      </c>
-      <c r="Z36">
-        <v>3.58</v>
-      </c>
       <c r="AA36">
+        <v>1.94</v>
+      </c>
+      <c r="AB36">
         <v>1.83</v>
       </c>
-      <c r="AB36">
-        <v>1.94</v>
-      </c>
       <c r="AC36">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
+        <v>2.17</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.14</v>
+      </c>
+      <c r="U37">
+        <v>2.61</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.09</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.19</v>
+      </c>
+      <c r="Z37">
+        <v>3.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>1.99</v>
+      </c>
+      <c r="AC37">
+        <v>2.7</v>
+      </c>
+      <c r="AD37">
+        <v>1.35</v>
+      </c>
+      <c r="AE37">
+        <v>1.11</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.2</v>
       </c>
-      <c r="S37">
-        <v>1.29</v>
-      </c>
-      <c r="T37">
-        <v>2.86</v>
-      </c>
-      <c r="U37">
-        <v>2.46</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.12</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>3.82</v>
-      </c>
-      <c r="AA37">
-        <v>1.79</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.83</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
-      <c r="AF37">
-        <v>1.62</v>
-      </c>
-      <c r="AG37">
-        <v>2.15</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>3.87</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,32 +6662,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.27</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.88</v>
+      </c>
+      <c r="AB39">
+        <v>1.88</v>
+      </c>
+      <c r="AC39">
+        <v>3.08</v>
+      </c>
+      <c r="AD39">
         <v>1.28</v>
       </c>
-      <c r="Z39">
-        <v>3.05</v>
-      </c>
-      <c r="AA39">
-        <v>1.95</v>
-      </c>
-      <c r="AB39">
-        <v>1.75</v>
-      </c>
-      <c r="AC39">
-        <v>3.42</v>
-      </c>
-      <c r="AD39">
-        <v>1.23</v>
-      </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.21</v>
+      </c>
+      <c r="O60">
+        <v>3.37</v>
+      </c>
+      <c r="P60">
+        <v>3.34</v>
+      </c>
+      <c r="Q60">
+        <v>3.06</v>
+      </c>
+      <c r="R60">
+        <v>2.07</v>
+      </c>
+      <c r="S60">
+        <v>1.51</v>
+      </c>
+      <c r="T60">
+        <v>2.38</v>
+      </c>
+      <c r="U60">
+        <v>3.3</v>
+      </c>
+      <c r="V60">
+        <v>1.25</v>
+      </c>
+      <c r="W60">
+        <v>1.01</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.46</v>
+      </c>
+      <c r="Z60">
+        <v>2.64</v>
+      </c>
+      <c r="AA60">
+        <v>2.37</v>
+      </c>
+      <c r="AB60">
         <v>1.53</v>
       </c>
-      <c r="O60">
-        <v>3.7</v>
-      </c>
-      <c r="P60">
-        <v>5.25</v>
-      </c>
-      <c r="Q60">
-        <v>2.13</v>
-      </c>
-      <c r="R60">
-        <v>2.14</v>
-      </c>
-      <c r="S60">
-        <v>1.38</v>
-      </c>
-      <c r="T60">
-        <v>2.89</v>
-      </c>
-      <c r="U60">
-        <v>2.66</v>
-      </c>
-      <c r="V60">
-        <v>1.45</v>
-      </c>
-      <c r="W60">
-        <v>1.06</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>1.2</v>
-      </c>
-      <c r="Z60">
-        <v>3.68</v>
-      </c>
-      <c r="AA60">
-        <v>1.75</v>
-      </c>
-      <c r="AB60">
-        <v>1.93</v>
-      </c>
       <c r="AC60">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O61">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q61">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R61">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S61">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U61">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC61">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD61">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q112">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R112">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC112">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE112">
         <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q125">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q28">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AD33">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5847,84 +5847,84 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>2.59</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
+        <v>2.28</v>
+      </c>
+      <c r="S34">
+        <v>1.29</v>
+      </c>
+      <c r="T34">
+        <v>3.3</v>
+      </c>
+      <c r="U34">
+        <v>2.45</v>
+      </c>
+      <c r="V34">
+        <v>1.47</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.81</v>
+      </c>
+      <c r="AB34">
+        <v>1.95</v>
+      </c>
+      <c r="AC34">
+        <v>2.66</v>
+      </c>
+      <c r="AD34">
+        <v>1.41</v>
+      </c>
+      <c r="AE34">
+        <v>1.12</v>
+      </c>
+      <c r="AF34">
+        <v>1.7</v>
+      </c>
+      <c r="AG34">
+        <v>2.05</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.2</v>
+      </c>
+      <c r="AK34">
         <v>2.1</v>
-      </c>
-      <c r="S34">
-        <v>1.36</v>
-      </c>
-      <c r="T34">
-        <v>2.88</v>
-      </c>
-      <c r="U34">
-        <v>2.88</v>
-      </c>
-      <c r="V34">
-        <v>1.36</v>
-      </c>
-      <c r="W34">
-        <v>1.06</v>
-      </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.28</v>
-      </c>
-      <c r="Z34">
-        <v>3.05</v>
-      </c>
-      <c r="AA34">
-        <v>1.95</v>
-      </c>
-      <c r="AB34">
-        <v>1.75</v>
-      </c>
-      <c r="AC34">
-        <v>3.42</v>
-      </c>
-      <c r="AD34">
-        <v>1.23</v>
-      </c>
-      <c r="AE34">
-        <v>1.05</v>
-      </c>
-      <c r="AF34">
-        <v>1.75</v>
-      </c>
-      <c r="AG34">
-        <v>1.96</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.29</v>
-      </c>
-      <c r="AK34">
-        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q35">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
+        <v>2.17</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.61</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.19</v>
+      </c>
+      <c r="Z35">
+        <v>3.74</v>
+      </c>
+      <c r="AA35">
+        <v>1.73</v>
+      </c>
+      <c r="AB35">
+        <v>1.99</v>
+      </c>
+      <c r="AC35">
+        <v>2.7</v>
+      </c>
+      <c r="AD35">
+        <v>1.35</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
         <v>2.2</v>
       </c>
-      <c r="S35">
-        <v>1.29</v>
-      </c>
-      <c r="T35">
-        <v>2.86</v>
-      </c>
-      <c r="U35">
-        <v>2.46</v>
-      </c>
-      <c r="V35">
-        <v>1.46</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.82</v>
-      </c>
-      <c r="AA35">
-        <v>1.79</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.83</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.09</v>
-      </c>
-      <c r="AF35">
-        <v>1.62</v>
-      </c>
-      <c r="AG35">
-        <v>2.15</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
         <v>3.42</v>
       </c>
       <c r="P36">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
         <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB37">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,32 +6662,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
+        <v>3.1</v>
+      </c>
+      <c r="P39">
+        <v>2.59</v>
+      </c>
+      <c r="Q39">
         <v>3.25</v>
       </c>
-      <c r="P39">
-        <v>2.95</v>
-      </c>
-      <c r="Q39">
-        <v>3.17</v>
-      </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
+        <v>3.05</v>
+      </c>
+      <c r="AA39">
+        <v>1.95</v>
+      </c>
+      <c r="AB39">
+        <v>1.75</v>
+      </c>
+      <c r="AC39">
         <v>3.42</v>
       </c>
-      <c r="AA39">
-        <v>1.88</v>
-      </c>
-      <c r="AB39">
-        <v>1.88</v>
-      </c>
-      <c r="AC39">
-        <v>3.08</v>
-      </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R60">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S60">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T60">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U60">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA60">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD60">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG60">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>2.21</v>
+      </c>
+      <c r="O61">
+        <v>3.37</v>
+      </c>
+      <c r="P61">
+        <v>3.34</v>
+      </c>
+      <c r="Q61">
+        <v>3.06</v>
+      </c>
+      <c r="R61">
+        <v>2.07</v>
+      </c>
+      <c r="S61">
+        <v>1.51</v>
+      </c>
+      <c r="T61">
+        <v>2.38</v>
+      </c>
+      <c r="U61">
+        <v>3.3</v>
+      </c>
+      <c r="V61">
+        <v>1.25</v>
+      </c>
+      <c r="W61">
+        <v>1.01</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.46</v>
+      </c>
+      <c r="Z61">
+        <v>2.64</v>
+      </c>
+      <c r="AA61">
+        <v>2.37</v>
+      </c>
+      <c r="AB61">
         <v>1.53</v>
       </c>
-      <c r="O61">
-        <v>3.7</v>
-      </c>
-      <c r="P61">
-        <v>5.25</v>
-      </c>
-      <c r="Q61">
-        <v>2.13</v>
-      </c>
-      <c r="R61">
-        <v>2.14</v>
-      </c>
-      <c r="S61">
-        <v>1.38</v>
-      </c>
-      <c r="T61">
-        <v>2.89</v>
-      </c>
-      <c r="U61">
-        <v>2.66</v>
-      </c>
-      <c r="V61">
-        <v>1.45</v>
-      </c>
-      <c r="W61">
-        <v>1.06</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>1.2</v>
-      </c>
-      <c r="Z61">
-        <v>3.68</v>
-      </c>
-      <c r="AA61">
-        <v>1.75</v>
-      </c>
-      <c r="AB61">
-        <v>1.93</v>
-      </c>
       <c r="AC61">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG61">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q112">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC112">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
         <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
         <v>1.55</v>
@@ -4088,50 +4088,50 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
         <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
+        <v>1.97</v>
+      </c>
+      <c r="AC23">
+        <v>2.38</v>
+      </c>
+      <c r="AD23">
+        <v>1.46</v>
+      </c>
+      <c r="AE23">
+        <v>1.16</v>
+      </c>
+      <c r="AF23">
+        <v>1.6</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.16</v>
+      </c>
+      <c r="AK23">
         <v>1.96</v>
-      </c>
-      <c r="AC23">
-        <v>2.49</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
-      <c r="AE23">
-        <v>1.13</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
-      <c r="AG23">
-        <v>2.32</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q25">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="AA35">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>4.1</v>
+      </c>
+      <c r="AA36">
+        <v>1.81</v>
+      </c>
+      <c r="AB36">
+        <v>1.95</v>
+      </c>
+      <c r="AC36">
+        <v>2.66</v>
+      </c>
+      <c r="AD36">
+        <v>1.41</v>
+      </c>
+      <c r="AE36">
         <v>1.12</v>
       </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.82</v>
-      </c>
-      <c r="AA36">
-        <v>1.79</v>
-      </c>
-      <c r="AB36">
-        <v>2.15</v>
-      </c>
-      <c r="AC36">
-        <v>2.83</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.09</v>
-      </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>4.73</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA37">
+        <v>1.83</v>
+      </c>
+      <c r="AB37">
         <v>1.94</v>
       </c>
-      <c r="AB37">
-        <v>1.83</v>
-      </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V38">
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,29 +6662,29 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U39">
         <v>2.88</v>
@@ -6693,37 +6693,37 @@
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC112">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF112">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG112">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>1.55</v>
@@ -4088,34 +4088,34 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
         <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q33">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
+        <v>1.36</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.27</v>
+      </c>
+      <c r="Z34">
+        <v>3.42</v>
+      </c>
+      <c r="AA34">
+        <v>1.88</v>
+      </c>
+      <c r="AB34">
+        <v>1.88</v>
+      </c>
+      <c r="AC34">
+        <v>3.08</v>
+      </c>
+      <c r="AD34">
+        <v>1.28</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.75</v>
+      </c>
+      <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.25</v>
+      </c>
+      <c r="AK34">
         <v>1.45</v>
-      </c>
-      <c r="W34">
-        <v>1.09</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.19</v>
-      </c>
-      <c r="Z34">
-        <v>3.74</v>
-      </c>
-      <c r="AA34">
-        <v>1.73</v>
-      </c>
-      <c r="AB34">
-        <v>1.99</v>
-      </c>
-      <c r="AC34">
-        <v>2.7</v>
-      </c>
-      <c r="AD34">
-        <v>1.35</v>
-      </c>
-      <c r="AE34">
-        <v>1.11</v>
-      </c>
-      <c r="AF34">
-        <v>1.6</v>
-      </c>
-      <c r="AG34">
-        <v>2.2</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.3</v>
-      </c>
-      <c r="AK34">
-        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>4.73</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC35">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="AD35">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,61 +6340,61 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="P37">
-        <v>4.73</v>
+        <v>3.87</v>
       </c>
       <c r="Q37">
         <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
         <v>2.05</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
+        <v>2.17</v>
+      </c>
+      <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.14</v>
+      </c>
+      <c r="U38">
+        <v>2.61</v>
+      </c>
+      <c r="V38">
+        <v>1.45</v>
+      </c>
+      <c r="W38">
+        <v>1.09</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.19</v>
+      </c>
+      <c r="Z38">
+        <v>3.74</v>
+      </c>
+      <c r="AA38">
+        <v>1.73</v>
+      </c>
+      <c r="AB38">
+        <v>1.99</v>
+      </c>
+      <c r="AC38">
+        <v>2.7</v>
+      </c>
+      <c r="AD38">
+        <v>1.35</v>
+      </c>
+      <c r="AE38">
+        <v>1.11</v>
+      </c>
+      <c r="AF38">
+        <v>1.6</v>
+      </c>
+      <c r="AG38">
         <v>2.2</v>
       </c>
-      <c r="S38">
-        <v>1.29</v>
-      </c>
-      <c r="T38">
-        <v>2.86</v>
-      </c>
-      <c r="U38">
-        <v>2.46</v>
-      </c>
-      <c r="V38">
-        <v>1.46</v>
-      </c>
-      <c r="W38">
-        <v>1.12</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.82</v>
-      </c>
-      <c r="AA38">
-        <v>1.79</v>
-      </c>
-      <c r="AB38">
-        <v>2.15</v>
-      </c>
-      <c r="AC38">
-        <v>2.83</v>
-      </c>
-      <c r="AD38">
-        <v>1.33</v>
-      </c>
-      <c r="AE38">
-        <v>1.09</v>
-      </c>
-      <c r="AF38">
-        <v>1.62</v>
-      </c>
-      <c r="AG38">
-        <v>2.15</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,29 +6662,29 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>2.93</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
         <v>2.88</v>
@@ -6693,37 +6693,37 @@
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
         <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9956,7 +9956,7 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.22</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.21</v>
+      </c>
+      <c r="O60">
+        <v>3.37</v>
+      </c>
+      <c r="P60">
+        <v>3.34</v>
+      </c>
+      <c r="Q60">
+        <v>3.06</v>
+      </c>
+      <c r="R60">
+        <v>2.07</v>
+      </c>
+      <c r="S60">
+        <v>1.51</v>
+      </c>
+      <c r="T60">
+        <v>2.38</v>
+      </c>
+      <c r="U60">
+        <v>3.3</v>
+      </c>
+      <c r="V60">
+        <v>1.25</v>
+      </c>
+      <c r="W60">
+        <v>1.01</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.46</v>
+      </c>
+      <c r="Z60">
+        <v>2.64</v>
+      </c>
+      <c r="AA60">
+        <v>2.37</v>
+      </c>
+      <c r="AB60">
         <v>1.53</v>
       </c>
-      <c r="O60">
-        <v>3.7</v>
-      </c>
-      <c r="P60">
-        <v>5.25</v>
-      </c>
-      <c r="Q60">
-        <v>2.13</v>
-      </c>
-      <c r="R60">
-        <v>2.14</v>
-      </c>
-      <c r="S60">
-        <v>1.38</v>
-      </c>
-      <c r="T60">
-        <v>2.89</v>
-      </c>
-      <c r="U60">
-        <v>2.66</v>
-      </c>
-      <c r="V60">
-        <v>1.45</v>
-      </c>
-      <c r="W60">
-        <v>1.06</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>1.2</v>
-      </c>
-      <c r="Z60">
-        <v>3.68</v>
-      </c>
-      <c r="AA60">
-        <v>1.75</v>
-      </c>
-      <c r="AB60">
-        <v>1.93</v>
-      </c>
       <c r="AC60">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O61">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q61">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R61">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S61">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U61">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC61">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD61">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q112">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA112">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC112">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG112">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK112">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.5</v>
+      </c>
+      <c r="O23">
+        <v>4.3</v>
+      </c>
+      <c r="P23">
+        <v>4.83</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>3.62</v>
-      </c>
-      <c r="P23">
-        <v>3.04</v>
-      </c>
-      <c r="Q23">
-        <v>2.52</v>
-      </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
+        <v>3.17</v>
+      </c>
+      <c r="R33">
+        <v>2.23</v>
+      </c>
+      <c r="S33">
+        <v>1.39</v>
+      </c>
+      <c r="T33">
         <v>2.71</v>
       </c>
-      <c r="R33">
-        <v>2.2</v>
-      </c>
-      <c r="S33">
-        <v>1.38</v>
-      </c>
-      <c r="T33">
-        <v>2.91</v>
-      </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
+        <v>1.27</v>
+      </c>
+      <c r="Z33">
+        <v>3.42</v>
+      </c>
+      <c r="AA33">
+        <v>1.88</v>
+      </c>
+      <c r="AB33">
+        <v>1.88</v>
+      </c>
+      <c r="AC33">
+        <v>3.08</v>
+      </c>
+      <c r="AD33">
         <v>1.28</v>
       </c>
-      <c r="Z33">
-        <v>3.08</v>
-      </c>
-      <c r="AA33">
-        <v>1.94</v>
-      </c>
-      <c r="AB33">
-        <v>1.83</v>
-      </c>
-      <c r="AC33">
-        <v>3.28</v>
-      </c>
-      <c r="AD33">
-        <v>1.25</v>
-      </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q35">
+        <v>3.25</v>
+      </c>
+      <c r="R35">
         <v>2.1</v>
       </c>
-      <c r="R35">
-        <v>2.3</v>
-      </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA35">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>4.1</v>
+      </c>
+      <c r="AA36">
+        <v>1.81</v>
+      </c>
+      <c r="AB36">
+        <v>1.95</v>
+      </c>
+      <c r="AC36">
+        <v>2.66</v>
+      </c>
+      <c r="AD36">
+        <v>1.41</v>
+      </c>
+      <c r="AE36">
         <v>1.12</v>
       </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.82</v>
-      </c>
-      <c r="AA36">
-        <v>1.79</v>
-      </c>
-      <c r="AB36">
-        <v>2.15</v>
-      </c>
-      <c r="AC36">
-        <v>2.83</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.09</v>
-      </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>1.53</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA76">
         <v>1.5</v>
@@ -12742,19 +12742,19 @@
         <v>2.5</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q112">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R112">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC112">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE112">
         <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>3</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>3.22</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,34 +19226,34 @@
         <v>5.87</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AA116">
         <v>1.61</v>
@@ -19262,19 +19262,19 @@
         <v>2.25</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O124">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="P124">
-        <v>3.98</v>
+        <v>3.06</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
+        <v>1.92</v>
+      </c>
+      <c r="O125">
+        <v>3.57</v>
+      </c>
+      <c r="P125">
+        <v>3.98</v>
+      </c>
+      <c r="Q125">
         <v>2.25</v>
       </c>
-      <c r="O125">
-        <v>3.47</v>
-      </c>
-      <c r="P125">
-        <v>3.06</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,32 +5684,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
+        <v>3.1</v>
+      </c>
+      <c r="P33">
+        <v>2.59</v>
+      </c>
+      <c r="Q33">
         <v>3.25</v>
       </c>
-      <c r="P33">
-        <v>2.95</v>
-      </c>
-      <c r="Q33">
-        <v>3.17</v>
-      </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.36</v>
@@ -5718,34 +5718,34 @@
         <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
+        <v>3.05</v>
+      </c>
+      <c r="AA33">
+        <v>1.95</v>
+      </c>
+      <c r="AB33">
+        <v>1.75</v>
+      </c>
+      <c r="AC33">
         <v>3.42</v>
       </c>
-      <c r="AA33">
-        <v>1.88</v>
-      </c>
-      <c r="AB33">
-        <v>1.88</v>
-      </c>
-      <c r="AC33">
-        <v>3.08</v>
-      </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,84 +6010,84 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>2.86</v>
+      </c>
+      <c r="U35">
+        <v>2.46</v>
+      </c>
+      <c r="V35">
+        <v>1.46</v>
+      </c>
+      <c r="W35">
+        <v>1.12</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.82</v>
+      </c>
+      <c r="AA35">
+        <v>1.79</v>
+      </c>
+      <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.83</v>
+      </c>
+      <c r="AD35">
+        <v>1.33</v>
+      </c>
+      <c r="AE35">
+        <v>1.09</v>
+      </c>
+      <c r="AF35">
+        <v>1.62</v>
+      </c>
+      <c r="AG35">
+        <v>2.15</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.88</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.05</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.42</v>
-      </c>
-      <c r="AD35">
-        <v>1.23</v>
-      </c>
-      <c r="AE35">
-        <v>1.05</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>1.96</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.29</v>
-      </c>
-      <c r="AK35">
-        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
+        <v>2.17</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.14</v>
+      </c>
+      <c r="U37">
+        <v>2.61</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.09</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.19</v>
+      </c>
+      <c r="Z37">
+        <v>3.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>1.99</v>
+      </c>
+      <c r="AC37">
+        <v>2.7</v>
+      </c>
+      <c r="AD37">
+        <v>1.35</v>
+      </c>
+      <c r="AE37">
+        <v>1.11</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.2</v>
       </c>
-      <c r="S37">
-        <v>1.29</v>
-      </c>
-      <c r="T37">
-        <v>2.86</v>
-      </c>
-      <c r="U37">
-        <v>2.46</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.12</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>3.82</v>
-      </c>
-      <c r="AA37">
-        <v>1.79</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.83</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
-      <c r="AF37">
-        <v>1.62</v>
-      </c>
-      <c r="AG37">
-        <v>2.15</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>2.93</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
+        <v>1.83</v>
+      </c>
+      <c r="AB38">
         <v>1.94</v>
       </c>
-      <c r="AB38">
-        <v>1.83</v>
-      </c>
       <c r="AC38">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
+        <v>2.71</v>
+      </c>
+      <c r="U39">
+        <v>2.81</v>
+      </c>
+      <c r="V39">
+        <v>1.36</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.27</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.88</v>
+      </c>
+      <c r="AB39">
+        <v>1.88</v>
+      </c>
+      <c r="AC39">
         <v>3.08</v>
       </c>
-      <c r="U39">
-        <v>2.48</v>
-      </c>
-      <c r="V39">
-        <v>1.46</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.26</v>
-      </c>
-      <c r="Z39">
-        <v>3.58</v>
-      </c>
-      <c r="AA39">
-        <v>1.83</v>
-      </c>
-      <c r="AB39">
-        <v>1.94</v>
-      </c>
-      <c r="AC39">
-        <v>3.11</v>
-      </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="R60">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S60">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T60">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="U60">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>2.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA60">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AD60">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG60">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>2.21</v>
+      </c>
+      <c r="O61">
+        <v>3.37</v>
+      </c>
+      <c r="P61">
+        <v>3.34</v>
+      </c>
+      <c r="Q61">
+        <v>3.06</v>
+      </c>
+      <c r="R61">
+        <v>2.07</v>
+      </c>
+      <c r="S61">
+        <v>1.51</v>
+      </c>
+      <c r="T61">
+        <v>2.38</v>
+      </c>
+      <c r="U61">
+        <v>3.3</v>
+      </c>
+      <c r="V61">
+        <v>1.25</v>
+      </c>
+      <c r="W61">
+        <v>1.01</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.46</v>
+      </c>
+      <c r="Z61">
+        <v>2.64</v>
+      </c>
+      <c r="AA61">
+        <v>2.37</v>
+      </c>
+      <c r="AB61">
         <v>1.53</v>
       </c>
-      <c r="O61">
-        <v>3.7</v>
-      </c>
-      <c r="P61">
-        <v>5.25</v>
-      </c>
-      <c r="Q61">
-        <v>2.13</v>
-      </c>
-      <c r="R61">
-        <v>2.14</v>
-      </c>
-      <c r="S61">
-        <v>1.38</v>
-      </c>
-      <c r="T61">
-        <v>2.89</v>
-      </c>
-      <c r="U61">
-        <v>2.66</v>
-      </c>
-      <c r="V61">
-        <v>1.45</v>
-      </c>
-      <c r="W61">
-        <v>1.06</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>1.2</v>
-      </c>
-      <c r="Z61">
-        <v>3.68</v>
-      </c>
-      <c r="AA61">
-        <v>1.75</v>
-      </c>
-      <c r="AB61">
-        <v>1.93</v>
-      </c>
       <c r="AC61">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG61">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
         <v>1.33</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O112">
         <v>3.55</v>
       </c>
       <c r="P112">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S112">
+        <v>1.37</v>
+      </c>
+      <c r="T112">
+        <v>2.69</v>
+      </c>
+      <c r="U112">
+        <v>2.8</v>
+      </c>
+      <c r="V112">
+        <v>1.35</v>
+      </c>
+      <c r="W112">
+        <v>1.06</v>
+      </c>
+      <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
         <v>1.33</v>
       </c>
-      <c r="T112">
-        <v>2.83</v>
-      </c>
-      <c r="U112">
-        <v>2.5</v>
-      </c>
-      <c r="V112">
-        <v>1.44</v>
-      </c>
-      <c r="W112">
-        <v>1.07</v>
-      </c>
-      <c r="X112">
-        <v>1</v>
-      </c>
-      <c r="Y112">
-        <v>1.23</v>
-      </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC112">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD112">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF112">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.5</v>
+      </c>
+      <c r="O24">
+        <v>4.3</v>
+      </c>
+      <c r="P24">
+        <v>4.83</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="O24">
-        <v>3.62</v>
-      </c>
-      <c r="P24">
-        <v>3.04</v>
-      </c>
-      <c r="Q24">
-        <v>2.52</v>
-      </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,68 +5684,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P33">
-        <v>2.59</v>
+        <v>4.73</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
         <v>3.42</v>
       </c>
       <c r="P34">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="AA34">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,84 +6010,84 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
+        <v>3.1</v>
+      </c>
+      <c r="P35">
+        <v>2.59</v>
+      </c>
+      <c r="Q35">
+        <v>3.25</v>
+      </c>
+      <c r="R35">
+        <v>2.1</v>
+      </c>
+      <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.88</v>
+      </c>
+      <c r="U35">
+        <v>2.88</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
+        <v>3.05</v>
+      </c>
+      <c r="AA35">
+        <v>1.95</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
         <v>3.42</v>
       </c>
-      <c r="P35">
-        <v>2.26</v>
-      </c>
-      <c r="Q35">
-        <v>3.56</v>
-      </c>
-      <c r="R35">
-        <v>2.2</v>
-      </c>
-      <c r="S35">
+      <c r="AD35">
+        <v>1.23</v>
+      </c>
+      <c r="AE35">
+        <v>1.05</v>
+      </c>
+      <c r="AF35">
+        <v>1.75</v>
+      </c>
+      <c r="AG35">
+        <v>1.96</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.29</v>
       </c>
-      <c r="T35">
-        <v>2.86</v>
-      </c>
-      <c r="U35">
-        <v>2.46</v>
-      </c>
-      <c r="V35">
-        <v>1.46</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.82</v>
-      </c>
-      <c r="AA35">
-        <v>1.79</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.83</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.09</v>
-      </c>
-      <c r="AF35">
-        <v>1.62</v>
-      </c>
-      <c r="AG35">
-        <v>2.15</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AB37">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
+        <v>1.92</v>
+      </c>
+      <c r="O124">
+        <v>3.57</v>
+      </c>
+      <c r="P124">
+        <v>3.98</v>
+      </c>
+      <c r="Q124">
         <v>2.25</v>
       </c>
-      <c r="O124">
-        <v>3.47</v>
-      </c>
-      <c r="P124">
-        <v>3.06</v>
-      </c>
-      <c r="Q124">
-        <v>3.15</v>
-      </c>
       <c r="R124">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T124">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U124">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="V124">
         <v>1.35</v>
       </c>
       <c r="W124">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X124">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
         <v>1.38</v>
       </c>
       <c r="Z124">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AA124">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB124">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC124">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AD124">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG124">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK124">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O125">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="P125">
-        <v>3.98</v>
+        <v>3.06</v>
       </c>
       <c r="Q125">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="R125">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S125">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T125">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U125">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="V125">
         <v>1.35</v>
       </c>
       <c r="W125">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
         <v>1.38</v>
       </c>
       <c r="Z125">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA125">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB125">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC125">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AD125">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE125">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG125">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
         <v>1.55</v>
@@ -4088,50 +4088,50 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
         <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
+        <v>1.97</v>
+      </c>
+      <c r="AC23">
+        <v>2.38</v>
+      </c>
+      <c r="AD23">
+        <v>1.46</v>
+      </c>
+      <c r="AE23">
+        <v>1.16</v>
+      </c>
+      <c r="AF23">
+        <v>1.6</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.16</v>
+      </c>
+      <c r="AK23">
         <v>1.96</v>
-      </c>
-      <c r="AC23">
-        <v>2.49</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
-      <c r="AE23">
-        <v>1.13</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
-      <c r="AG23">
-        <v>2.32</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q25">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
         <v>1.55</v>
@@ -4414,34 +4414,34 @@
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
         <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q27">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P28">
-        <v>5.86</v>
+        <v>6.77</v>
       </c>
       <c r="Q28">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,68 +5684,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q33">
+        <v>3.25</v>
+      </c>
+      <c r="R33">
         <v>2.1</v>
       </c>
-      <c r="R33">
-        <v>2.3</v>
-      </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
+        <v>2.17</v>
+      </c>
+      <c r="S34">
+        <v>1.3</v>
+      </c>
+      <c r="T34">
+        <v>3.14</v>
+      </c>
+      <c r="U34">
+        <v>2.61</v>
+      </c>
+      <c r="V34">
+        <v>1.45</v>
+      </c>
+      <c r="W34">
+        <v>1.09</v>
+      </c>
+      <c r="X34">
+        <v>1.03</v>
+      </c>
+      <c r="Y34">
+        <v>1.19</v>
+      </c>
+      <c r="Z34">
+        <v>3.74</v>
+      </c>
+      <c r="AA34">
+        <v>1.73</v>
+      </c>
+      <c r="AB34">
+        <v>1.99</v>
+      </c>
+      <c r="AC34">
+        <v>2.7</v>
+      </c>
+      <c r="AD34">
+        <v>1.35</v>
+      </c>
+      <c r="AE34">
+        <v>1.11</v>
+      </c>
+      <c r="AF34">
+        <v>1.6</v>
+      </c>
+      <c r="AG34">
         <v>2.2</v>
       </c>
-      <c r="S34">
-        <v>1.29</v>
-      </c>
-      <c r="T34">
-        <v>2.86</v>
-      </c>
-      <c r="U34">
-        <v>2.46</v>
-      </c>
-      <c r="V34">
-        <v>1.46</v>
-      </c>
-      <c r="W34">
-        <v>1.12</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.25</v>
-      </c>
-      <c r="Z34">
-        <v>3.82</v>
-      </c>
-      <c r="AA34">
-        <v>1.79</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.83</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
-      <c r="AF34">
-        <v>1.62</v>
-      </c>
-      <c r="AG34">
-        <v>2.15</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V35">
         <v>1.36</v>
@@ -6044,34 +6044,34 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.42</v>
+      </c>
+      <c r="AA35">
+        <v>1.88</v>
+      </c>
+      <c r="AB35">
+        <v>1.88</v>
+      </c>
+      <c r="AC35">
+        <v>3.08</v>
+      </c>
+      <c r="AD35">
         <v>1.28</v>
       </c>
-      <c r="Z35">
-        <v>3.05</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.42</v>
-      </c>
-      <c r="AD35">
-        <v>1.23</v>
-      </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.87</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="O103">
-        <v>3.66</v>
+        <v>3.02</v>
       </c>
       <c r="P103">
-        <v>3.57</v>
+        <v>3.1</v>
       </c>
       <c r="Q103">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="R103">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S103">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T103">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U103">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V103">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X103">
         <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z103">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA103">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB103">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC103">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="AD103">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE103">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF103">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK103">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="O104">
-        <v>3.02</v>
+        <v>3.66</v>
       </c>
       <c r="P104">
-        <v>3.1</v>
+        <v>3.57</v>
       </c>
       <c r="Q104">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="R104">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S104">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="U104">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA104">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB104">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC104">
-        <v>3.99</v>
+        <v>3.58</v>
       </c>
       <c r="AD104">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE104">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG104">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
         <v>1.33</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
         <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O111">
         <v>3.55</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S111">
+        <v>1.37</v>
+      </c>
+      <c r="T111">
+        <v>2.69</v>
+      </c>
+      <c r="U111">
+        <v>2.8</v>
+      </c>
+      <c r="V111">
+        <v>1.35</v>
+      </c>
+      <c r="W111">
+        <v>1.06</v>
+      </c>
+      <c r="X111">
+        <v>1.02</v>
+      </c>
+      <c r="Y111">
         <v>1.33</v>
       </c>
-      <c r="T111">
-        <v>2.83</v>
-      </c>
-      <c r="U111">
-        <v>2.5</v>
-      </c>
-      <c r="V111">
-        <v>1.44</v>
-      </c>
-      <c r="W111">
-        <v>1.07</v>
-      </c>
-      <c r="X111">
-        <v>1</v>
-      </c>
-      <c r="Y111">
-        <v>1.23</v>
-      </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q112">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA112">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC112">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG112">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK112">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
         <v>1.35</v>
@@ -1809,25 +1809,25 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z9">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="Q10">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.35</v>
@@ -1972,25 +1972,25 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
         <v>1.6</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
+        <v>2.41</v>
+      </c>
+      <c r="O15">
+        <v>3.57</v>
+      </c>
+      <c r="P15">
         <v>2.8</v>
       </c>
-      <c r="O15">
-        <v>3.51</v>
-      </c>
-      <c r="P15">
-        <v>2.44</v>
-      </c>
       <c r="Q15">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="R15">
         <v>2.02</v>
@@ -2775,10 +2775,10 @@
         <v>2.74</v>
       </c>
       <c r="U15">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
         <v>2</v>
@@ -2799,10 +2799,10 @@
         <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
         <v>1.05</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q16">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="R16">
         <v>2.02</v>
@@ -2938,10 +2938,10 @@
         <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
         <v>1.04</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
         <v>2</v>
@@ -2962,10 +2962,10 @@
         <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
         <v>1.05</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>4.83</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
         <v>1.55</v>
@@ -4414,50 +4414,50 @@
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
         <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB25">
+        <v>1.97</v>
+      </c>
+      <c r="AC25">
+        <v>2.38</v>
+      </c>
+      <c r="AD25">
+        <v>1.46</v>
+      </c>
+      <c r="AE25">
+        <v>1.16</v>
+      </c>
+      <c r="AF25">
+        <v>1.6</v>
+      </c>
+      <c r="AG25">
+        <v>2.25</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.16</v>
+      </c>
+      <c r="AK25">
         <v>1.96</v>
-      </c>
-      <c r="AC25">
-        <v>2.49</v>
-      </c>
-      <c r="AD25">
-        <v>1.44</v>
-      </c>
-      <c r="AE25">
-        <v>1.13</v>
-      </c>
-      <c r="AF25">
-        <v>1.53</v>
-      </c>
-      <c r="AG25">
-        <v>2.32</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.33</v>
-      </c>
-      <c r="AK25">
-        <v>1.7</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P26">
-        <v>1.66</v>
+        <v>5.86</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>2.66</v>
+        <v>3.23</v>
       </c>
       <c r="U26">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.19</v>
+        <v>3.68</v>
       </c>
       <c r="AA26">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AC26">
-        <v>3.34</v>
+        <v>2.89</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,65 +4710,65 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>5.86</v>
+        <v>1.66</v>
       </c>
       <c r="Q27">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>3.23</v>
+        <v>2.66</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.19</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB27">
+        <v>1.77</v>
+      </c>
+      <c r="AC27">
+        <v>3.34</v>
+      </c>
+      <c r="AD27">
+        <v>1.24</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
         <v>1.91</v>
       </c>
-      <c r="AC27">
-        <v>2.89</v>
-      </c>
-      <c r="AD27">
-        <v>1.38</v>
-      </c>
-      <c r="AE27">
-        <v>1.13</v>
-      </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>1.76</v>
       </c>
-      <c r="AG27">
-        <v>1.94</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,29 +5684,29 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
         <v>2.88</v>
@@ -5715,37 +5715,37 @@
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>3.17</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="U35">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>3.87</v>
+        <v>4.73</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA38">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
+        <v>3.25</v>
+      </c>
+      <c r="R39">
         <v>2.1</v>
       </c>
-      <c r="R39">
-        <v>2.3</v>
-      </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>3.11</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O51">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q51">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC79">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="P102">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="Q102">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="R102">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S102">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T102">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="U102">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="AA102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AD102">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE102">
         <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="O103">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="P103">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="Q103">
+        <v>2.77</v>
+      </c>
+      <c r="R103">
+        <v>1.99</v>
+      </c>
+      <c r="S103">
+        <v>1.42</v>
+      </c>
+      <c r="T103">
+        <v>2.74</v>
+      </c>
+      <c r="U103">
+        <v>2.82</v>
+      </c>
+      <c r="V103">
+        <v>1.4</v>
+      </c>
+      <c r="W103">
+        <v>1.04</v>
+      </c>
+      <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
+        <v>1.32</v>
+      </c>
+      <c r="Z103">
         <v>3.16</v>
       </c>
-      <c r="R103">
-        <v>2.09</v>
-      </c>
-      <c r="S103">
-        <v>1.5</v>
-      </c>
-      <c r="T103">
-        <v>2.39</v>
-      </c>
-      <c r="U103">
-        <v>3.2</v>
-      </c>
-      <c r="V103">
-        <v>1.3</v>
-      </c>
-      <c r="W103">
-        <v>1.01</v>
-      </c>
-      <c r="X103">
-        <v>1.03</v>
-      </c>
-      <c r="Y103">
-        <v>1.36</v>
-      </c>
-      <c r="Z103">
-        <v>2.7</v>
-      </c>
       <c r="AA103">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="AD103">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="O104">
-        <v>3.66</v>
+        <v>3.02</v>
       </c>
       <c r="P104">
-        <v>3.57</v>
+        <v>3.1</v>
       </c>
       <c r="Q104">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="R104">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S104">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T104">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U104">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X104">
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z104">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA104">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB104">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC104">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="AD104">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE104">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG104">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK104">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O105">
+        <v>3.65</v>
+      </c>
+      <c r="P105">
         <v>3.8</v>
       </c>
-      <c r="P105">
-        <v>4.5</v>
-      </c>
       <c r="Q105">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T105">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W105">
         <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB105">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD105">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="O106">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P106">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q106">
+        <v>3</v>
+      </c>
+      <c r="R106">
         <v>2.25</v>
       </c>
-      <c r="R106">
-        <v>2.3</v>
-      </c>
       <c r="S106">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U106">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V106">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB106">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AC106">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD106">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE106">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK106">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O107">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P107">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q107">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S107">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T107">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U107">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="V107">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z107">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="AA107">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AB107">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AC107">
-        <v>2.56</v>
+        <v>3.67</v>
       </c>
       <c r="AD107">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF107">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AG107">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O108">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q108">
+        <v>2.2</v>
+      </c>
+      <c r="R108">
         <v>2.25</v>
       </c>
-      <c r="R108">
-        <v>2.09</v>
-      </c>
       <c r="S108">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="U108">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="V108">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>3.14</v>
+        <v>3.66</v>
       </c>
       <c r="AA108">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB108">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC108">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD108">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P109">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q109">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S109">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T109">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U109">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V109">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W109">
+        <v>1.05</v>
+      </c>
+      <c r="X109">
+        <v>1.02</v>
+      </c>
+      <c r="Y109">
+        <v>1.27</v>
+      </c>
+      <c r="Z109">
+        <v>3.14</v>
+      </c>
+      <c r="AA109">
+        <v>2</v>
+      </c>
+      <c r="AB109">
+        <v>1.8</v>
+      </c>
+      <c r="AC109">
+        <v>3.34</v>
+      </c>
+      <c r="AD109">
+        <v>1.24</v>
+      </c>
+      <c r="AE109">
         <v>1.04</v>
       </c>
-      <c r="X109">
-        <v>1.03</v>
-      </c>
-      <c r="Y109">
-        <v>1.4</v>
-      </c>
-      <c r="Z109">
-        <v>2.7</v>
-      </c>
-      <c r="AA109">
-        <v>2.2</v>
-      </c>
-      <c r="AB109">
-        <v>1.58</v>
-      </c>
-      <c r="AC109">
-        <v>4.05</v>
-      </c>
-      <c r="AD109">
-        <v>1.17</v>
-      </c>
-      <c r="AE109">
-        <v>1.02</v>
-      </c>
       <c r="AF109">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG109">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S110">
         <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U110">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
         <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O111">
         <v>3.55</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R111">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AD111">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,58 +18565,58 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="P112">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q112">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="R112">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T112">
+        <v>2.62</v>
+      </c>
+      <c r="U112">
         <v>3</v>
       </c>
-      <c r="U112">
-        <v>2.72</v>
-      </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z112">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AC112">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF112">
         <v>2</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK112">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O114">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="P114">
+        <v>3.22</v>
+      </c>
+      <c r="Q114">
         <v>3</v>
       </c>
-      <c r="Q114">
-        <v>3.39</v>
-      </c>
       <c r="R114">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S114">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T114">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U114">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="V114">
         <v>1.22</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z114">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AA114">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB114">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC114">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD114">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE114">
         <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG114">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK114">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O115">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P115">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="Q115">
-        <v>3</v>
+        <v>3.39</v>
       </c>
       <c r="R115">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="S115">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T115">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U115">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="V115">
         <v>1.22</v>
       </c>
       <c r="W115">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X115">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y115">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z115">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AA115">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB115">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC115">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD115">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE115">
         <v>1.01</v>
       </c>
       <c r="AF115">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG115">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK115">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
+        <v>1.55</v>
+      </c>
+      <c r="O128">
+        <v>3.78</v>
+      </c>
+      <c r="P128">
+        <v>5.05</v>
+      </c>
+      <c r="Q128">
+        <v>2.1</v>
+      </c>
+      <c r="R128">
+        <v>2.3</v>
+      </c>
+      <c r="S128">
+        <v>1.3</v>
+      </c>
+      <c r="T128">
+        <v>3.2</v>
+      </c>
+      <c r="U128">
+        <v>2.63</v>
+      </c>
+      <c r="V128">
+        <v>1.44</v>
+      </c>
+      <c r="W128">
+        <v>1.11</v>
+      </c>
+      <c r="X128">
+        <v>1.01</v>
+      </c>
+      <c r="Y128">
+        <v>1.18</v>
+      </c>
+      <c r="Z128">
+        <v>3.84</v>
+      </c>
+      <c r="AA128">
+        <v>1.8</v>
+      </c>
+      <c r="AB128">
         <v>2</v>
       </c>
-      <c r="O128">
-        <v>3.46</v>
-      </c>
-      <c r="P128">
-        <v>3.15</v>
-      </c>
-      <c r="Q128">
-        <v>2.5</v>
-      </c>
-      <c r="R128">
-        <v>2.27</v>
-      </c>
-      <c r="S128">
-        <v>1.26</v>
-      </c>
-      <c r="T128">
-        <v>3.3</v>
-      </c>
-      <c r="U128">
-        <v>2.34</v>
-      </c>
-      <c r="V128">
-        <v>1.48</v>
-      </c>
-      <c r="W128">
-        <v>1.08</v>
-      </c>
-      <c r="X128">
-        <v>1.03</v>
-      </c>
-      <c r="Y128">
-        <v>1.16</v>
-      </c>
-      <c r="Z128">
-        <v>4.05</v>
-      </c>
-      <c r="AA128">
-        <v>1.63</v>
-      </c>
-      <c r="AB128">
-        <v>2.1</v>
-      </c>
       <c r="AC128">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AD128">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF128">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG128">
+        <v>1.95</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>1.2</v>
+      </c>
+      <c r="AK128">
         <v>2.25</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.25</v>
-      </c>
-      <c r="AK128">
-        <v>1.73</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.55</v>
+        <v>4.13</v>
       </c>
       <c r="O129">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="P129">
-        <v>5.05</v>
+        <v>1.68</v>
       </c>
       <c r="Q129">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="R129">
         <v>2.3</v>
       </c>
       <c r="S129">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U129">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V129">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W129">
         <v>1.11</v>
@@ -21369,31 +21369,31 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA129">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB129">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC129">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD129">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF129">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG129">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,43 +21499,43 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.13</v>
+        <v>2</v>
       </c>
       <c r="O130">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P130">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q130">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="R130">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S130">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T130">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U130">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="V130">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W130">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
         <v>1.16</v>
       </c>
       <c r="Z130">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA130">
         <v>1.63</v>
@@ -21544,19 +21544,19 @@
         <v>2.1</v>
       </c>
       <c r="AC130">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AD130">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE130">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF130">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG130">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="R15">
         <v>2.02</v>
@@ -2775,10 +2775,10 @@
         <v>2.74</v>
       </c>
       <c r="U15">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA15">
         <v>2</v>
@@ -2799,10 +2799,10 @@
         <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
         <v>1.05</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
+        <v>2.41</v>
+      </c>
+      <c r="O16">
+        <v>3.57</v>
+      </c>
+      <c r="P16">
         <v>2.8</v>
       </c>
-      <c r="O16">
-        <v>3.51</v>
-      </c>
-      <c r="P16">
-        <v>2.44</v>
-      </c>
       <c r="Q16">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="R16">
         <v>2.02</v>
@@ -2938,10 +2938,10 @@
         <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.04</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
         <v>2</v>
@@ -2962,10 +2962,10 @@
         <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.05</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O24">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="Q24">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
         <v>1.55</v>
@@ -4251,50 +4251,50 @@
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
         <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
+        <v>1.97</v>
+      </c>
+      <c r="AC24">
+        <v>2.38</v>
+      </c>
+      <c r="AD24">
+        <v>1.46</v>
+      </c>
+      <c r="AE24">
+        <v>1.16</v>
+      </c>
+      <c r="AF24">
+        <v>1.6</v>
+      </c>
+      <c r="AG24">
+        <v>2.25</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.16</v>
+      </c>
+      <c r="AK24">
         <v>1.96</v>
-      </c>
-      <c r="AC24">
-        <v>2.49</v>
-      </c>
-      <c r="AD24">
-        <v>1.44</v>
-      </c>
-      <c r="AE24">
-        <v>1.13</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
-      <c r="AG24">
-        <v>2.32</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.33</v>
-      </c>
-      <c r="AK24">
-        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q25">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
         <v>1.55</v>
@@ -4414,34 +4414,34 @@
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
         <v>4.38</v>
       </c>
       <c r="AA25">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.25</v>
+      </c>
+      <c r="Z34">
+        <v>3.82</v>
+      </c>
+      <c r="AA34">
+        <v>1.79</v>
+      </c>
+      <c r="AB34">
+        <v>2.15</v>
+      </c>
+      <c r="AC34">
+        <v>2.83</v>
+      </c>
+      <c r="AD34">
+        <v>1.33</v>
+      </c>
+      <c r="AE34">
         <v>1.09</v>
       </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.19</v>
-      </c>
-      <c r="Z34">
-        <v>3.74</v>
-      </c>
-      <c r="AA34">
-        <v>1.73</v>
-      </c>
-      <c r="AB34">
-        <v>1.99</v>
-      </c>
-      <c r="AC34">
-        <v>2.7</v>
-      </c>
-      <c r="AD34">
-        <v>1.35</v>
-      </c>
-      <c r="AE34">
-        <v>1.11</v>
-      </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,84 +6010,84 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
+        <v>3.1</v>
+      </c>
+      <c r="P35">
+        <v>2.59</v>
+      </c>
+      <c r="Q35">
+        <v>3.25</v>
+      </c>
+      <c r="R35">
+        <v>2.1</v>
+      </c>
+      <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.88</v>
+      </c>
+      <c r="U35">
+        <v>2.88</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
+        <v>3.05</v>
+      </c>
+      <c r="AA35">
+        <v>1.95</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
         <v>3.42</v>
       </c>
-      <c r="P35">
-        <v>2.26</v>
-      </c>
-      <c r="Q35">
-        <v>3.56</v>
-      </c>
-      <c r="R35">
-        <v>2.2</v>
-      </c>
-      <c r="S35">
+      <c r="AD35">
+        <v>1.23</v>
+      </c>
+      <c r="AE35">
+        <v>1.05</v>
+      </c>
+      <c r="AF35">
+        <v>1.75</v>
+      </c>
+      <c r="AG35">
+        <v>1.96</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.29</v>
       </c>
-      <c r="T35">
-        <v>2.86</v>
-      </c>
-      <c r="U35">
-        <v>2.46</v>
-      </c>
-      <c r="V35">
-        <v>1.46</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.82</v>
-      </c>
-      <c r="AA35">
-        <v>1.79</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.83</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.09</v>
-      </c>
-      <c r="AF35">
-        <v>1.62</v>
-      </c>
-      <c r="AG35">
-        <v>2.15</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,32 +6662,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.27</v>
+      </c>
+      <c r="Z39">
+        <v>3.42</v>
+      </c>
+      <c r="AA39">
+        <v>1.88</v>
+      </c>
+      <c r="AB39">
+        <v>1.88</v>
+      </c>
+      <c r="AC39">
+        <v>3.08</v>
+      </c>
+      <c r="AD39">
         <v>1.28</v>
       </c>
-      <c r="Z39">
-        <v>3.05</v>
-      </c>
-      <c r="AA39">
-        <v>1.95</v>
-      </c>
-      <c r="AB39">
-        <v>1.75</v>
-      </c>
-      <c r="AC39">
-        <v>3.42</v>
-      </c>
-      <c r="AD39">
-        <v>1.23</v>
-      </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>2.99</v>
+        <v>4.39</v>
       </c>
       <c r="Q72">
-        <v>2.99</v>
+        <v>2.27</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S72">
+        <v>1.44</v>
+      </c>
+      <c r="T72">
+        <v>2.69</v>
+      </c>
+      <c r="U72">
+        <v>2.9</v>
+      </c>
+      <c r="V72">
         <v>1.38</v>
       </c>
-      <c r="T72">
-        <v>2.88</v>
-      </c>
-      <c r="U72">
-        <v>2.67</v>
-      </c>
-      <c r="V72">
-        <v>1.45</v>
-      </c>
       <c r="W72">
+        <v>1.03</v>
+      </c>
+      <c r="X72">
+        <v>1.03</v>
+      </c>
+      <c r="Y72">
+        <v>1.33</v>
+      </c>
+      <c r="Z72">
+        <v>3.1</v>
+      </c>
+      <c r="AA72">
+        <v>2.02</v>
+      </c>
+      <c r="AB72">
+        <v>1.79</v>
+      </c>
+      <c r="AC72">
+        <v>3.43</v>
+      </c>
+      <c r="AD72">
+        <v>1.27</v>
+      </c>
+      <c r="AE72">
         <v>1.05</v>
       </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.27</v>
-      </c>
-      <c r="Z72">
-        <v>3.43</v>
-      </c>
-      <c r="AA72">
-        <v>1.77</v>
-      </c>
-      <c r="AB72">
+      <c r="AF72">
         <v>1.93</v>
       </c>
-      <c r="AC72">
-        <v>3.14</v>
-      </c>
-      <c r="AD72">
-        <v>1.34</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.68</v>
-      </c>
       <c r="AG72">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK72">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O73">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
-        <v>4.39</v>
+        <v>2.99</v>
       </c>
       <c r="Q73">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="R73">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T73">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U73">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V73">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z73">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="AA73">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC73">
-        <v>3.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD73">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="O102">
-        <v>3.66</v>
+        <v>3.02</v>
       </c>
       <c r="P102">
-        <v>3.57</v>
+        <v>3.1</v>
       </c>
       <c r="Q102">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="R102">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S102">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T102">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U102">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X102">
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z102">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB102">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC102">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="AD102">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O103">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="P103">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="Q103">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="R103">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="U103">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE103">
         <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="O104">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="P104">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="Q104">
+        <v>2.77</v>
+      </c>
+      <c r="R104">
+        <v>1.99</v>
+      </c>
+      <c r="S104">
+        <v>1.42</v>
+      </c>
+      <c r="T104">
+        <v>2.74</v>
+      </c>
+      <c r="U104">
+        <v>2.82</v>
+      </c>
+      <c r="V104">
+        <v>1.4</v>
+      </c>
+      <c r="W104">
+        <v>1.04</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>1.32</v>
+      </c>
+      <c r="Z104">
         <v>3.16</v>
       </c>
-      <c r="R104">
-        <v>2.09</v>
-      </c>
-      <c r="S104">
-        <v>1.5</v>
-      </c>
-      <c r="T104">
-        <v>2.39</v>
-      </c>
-      <c r="U104">
-        <v>3.2</v>
-      </c>
-      <c r="V104">
-        <v>1.3</v>
-      </c>
-      <c r="W104">
-        <v>1.01</v>
-      </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
-      <c r="Y104">
-        <v>1.36</v>
-      </c>
-      <c r="Z104">
-        <v>2.7</v>
-      </c>
       <c r="AA104">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="AD104">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE104">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK104">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="O108">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P108">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q108">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="R108">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S108">
+        <v>1.33</v>
+      </c>
+      <c r="T108">
+        <v>3</v>
+      </c>
+      <c r="U108">
+        <v>2.72</v>
+      </c>
+      <c r="V108">
+        <v>1.36</v>
+      </c>
+      <c r="W108">
+        <v>1.06</v>
+      </c>
+      <c r="X108">
+        <v>1.01</v>
+      </c>
+      <c r="Y108">
         <v>1.3</v>
       </c>
-      <c r="T108">
-        <v>2.95</v>
-      </c>
-      <c r="U108">
-        <v>2.55</v>
-      </c>
-      <c r="V108">
-        <v>1.44</v>
-      </c>
-      <c r="W108">
-        <v>1.07</v>
-      </c>
-      <c r="X108">
-        <v>1</v>
-      </c>
-      <c r="Y108">
-        <v>1.26</v>
-      </c>
       <c r="Z108">
-        <v>3.66</v>
+        <v>3.34</v>
       </c>
       <c r="AA108">
+        <v>1.86</v>
+      </c>
+      <c r="AB108">
         <v>1.81</v>
       </c>
-      <c r="AB108">
-        <v>1.86</v>
-      </c>
       <c r="AC108">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD108">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG108">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK108">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="O109">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q109">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R109">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T109">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U109">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V109">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.4</v>
+      </c>
+      <c r="Z109">
+        <v>2.7</v>
+      </c>
+      <c r="AA109">
+        <v>2.2</v>
+      </c>
+      <c r="AB109">
+        <v>1.58</v>
+      </c>
+      <c r="AC109">
+        <v>4.05</v>
+      </c>
+      <c r="AD109">
+        <v>1.17</v>
+      </c>
+      <c r="AE109">
         <v>1.02</v>
       </c>
-      <c r="Y109">
-        <v>1.27</v>
-      </c>
-      <c r="Z109">
-        <v>3.14</v>
-      </c>
-      <c r="AA109">
+      <c r="AF109">
         <v>2</v>
       </c>
-      <c r="AB109">
-        <v>1.8</v>
-      </c>
-      <c r="AC109">
-        <v>3.34</v>
-      </c>
-      <c r="AD109">
+      <c r="AG109">
+        <v>1.67</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.24</v>
       </c>
-      <c r="AE109">
-        <v>1.04</v>
-      </c>
-      <c r="AF109">
-        <v>1.86</v>
-      </c>
-      <c r="AG109">
-        <v>1.83</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.25</v>
-      </c>
       <c r="AK109">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P110">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
         <v>1.33</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U110">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA110">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD110">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
         <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG110">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,28 +18402,28 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P111">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q111">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V111">
         <v>1.44</v>
@@ -18435,47 +18435,47 @@
         <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB111">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC111">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
+        <v>1.88</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.25</v>
+      </c>
+      <c r="AK111">
         <v>2.1</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.3</v>
-      </c>
-      <c r="AK111">
-        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="O112">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P112">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R112">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S112">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T112">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U112">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V112">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W112">
+        <v>1.05</v>
+      </c>
+      <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
+        <v>1.27</v>
+      </c>
+      <c r="Z112">
+        <v>3.14</v>
+      </c>
+      <c r="AA112">
+        <v>2</v>
+      </c>
+      <c r="AB112">
+        <v>1.8</v>
+      </c>
+      <c r="AC112">
+        <v>3.34</v>
+      </c>
+      <c r="AD112">
+        <v>1.24</v>
+      </c>
+      <c r="AE112">
         <v>1.04</v>
       </c>
-      <c r="X112">
-        <v>1.03</v>
-      </c>
-      <c r="Y112">
-        <v>1.4</v>
-      </c>
-      <c r="Z112">
-        <v>2.7</v>
-      </c>
-      <c r="AA112">
-        <v>2.2</v>
-      </c>
-      <c r="AB112">
-        <v>1.58</v>
-      </c>
-      <c r="AC112">
-        <v>4.05</v>
-      </c>
-      <c r="AD112">
-        <v>1.17</v>
-      </c>
-      <c r="AE112">
-        <v>1.02</v>
-      </c>
       <c r="AF112">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG112">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,31 +21173,31 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.55</v>
+        <v>4.13</v>
       </c>
       <c r="O128">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="P128">
-        <v>5.05</v>
+        <v>1.68</v>
       </c>
       <c r="Q128">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="R128">
         <v>2.3</v>
       </c>
       <c r="S128">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T128">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U128">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V128">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W128">
         <v>1.11</v>
@@ -21206,31 +21206,31 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z128">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA128">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB128">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD128">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE128">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF128">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK128">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,43 +21336,43 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.13</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P129">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q129">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="R129">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S129">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T129">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="V129">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y129">
         <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA129">
         <v>1.63</v>
@@ -21381,19 +21381,19 @@
         <v>2.1</v>
       </c>
       <c r="AC129">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AD129">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE129">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF129">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG129">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,80 +21499,80 @@
         </is>
       </c>
       <c r="N130">
+        <v>1.55</v>
+      </c>
+      <c r="O130">
+        <v>3.78</v>
+      </c>
+      <c r="P130">
+        <v>5.05</v>
+      </c>
+      <c r="Q130">
+        <v>2.1</v>
+      </c>
+      <c r="R130">
+        <v>2.3</v>
+      </c>
+      <c r="S130">
+        <v>1.3</v>
+      </c>
+      <c r="T130">
+        <v>3.2</v>
+      </c>
+      <c r="U130">
+        <v>2.63</v>
+      </c>
+      <c r="V130">
+        <v>1.44</v>
+      </c>
+      <c r="W130">
+        <v>1.11</v>
+      </c>
+      <c r="X130">
+        <v>1.01</v>
+      </c>
+      <c r="Y130">
+        <v>1.18</v>
+      </c>
+      <c r="Z130">
+        <v>3.84</v>
+      </c>
+      <c r="AA130">
+        <v>1.8</v>
+      </c>
+      <c r="AB130">
         <v>2</v>
       </c>
-      <c r="O130">
-        <v>3.46</v>
-      </c>
-      <c r="P130">
-        <v>3.15</v>
-      </c>
-      <c r="Q130">
-        <v>2.5</v>
-      </c>
-      <c r="R130">
-        <v>2.27</v>
-      </c>
-      <c r="S130">
-        <v>1.26</v>
-      </c>
-      <c r="T130">
-        <v>3.3</v>
-      </c>
-      <c r="U130">
-        <v>2.34</v>
-      </c>
-      <c r="V130">
-        <v>1.48</v>
-      </c>
-      <c r="W130">
-        <v>1.08</v>
-      </c>
-      <c r="X130">
-        <v>1.03</v>
-      </c>
-      <c r="Y130">
-        <v>1.16</v>
-      </c>
-      <c r="Z130">
-        <v>4.05</v>
-      </c>
-      <c r="AA130">
-        <v>1.63</v>
-      </c>
-      <c r="AB130">
-        <v>2.1</v>
-      </c>
       <c r="AC130">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AD130">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE130">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF130">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG130">
+        <v>1.95</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ130">
+        <v>1.2</v>
+      </c>
+      <c r="AK130">
         <v>2.25</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>1.25</v>
-      </c>
-      <c r="AK130">
-        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
+        <v>2.41</v>
+      </c>
+      <c r="O15">
+        <v>3.57</v>
+      </c>
+      <c r="P15">
         <v>2.8</v>
       </c>
-      <c r="O15">
-        <v>3.51</v>
-      </c>
-      <c r="P15">
-        <v>2.44</v>
-      </c>
       <c r="Q15">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="R15">
         <v>2.02</v>
@@ -2775,10 +2775,10 @@
         <v>2.74</v>
       </c>
       <c r="U15">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
         <v>2</v>
@@ -2799,10 +2799,10 @@
         <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
         <v>1.05</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q16">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="R16">
         <v>2.02</v>
@@ -2938,10 +2938,10 @@
         <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
         <v>1.04</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
         <v>2</v>
@@ -2962,10 +2962,10 @@
         <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
         <v>1.05</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>4.38</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P24">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
         <v>1.55</v>
@@ -4251,34 +4251,34 @@
         <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
         <v>4.38</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.5</v>
+      </c>
+      <c r="O25">
+        <v>4.3</v>
+      </c>
+      <c r="P25">
+        <v>4.83</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="O25">
-        <v>3.62</v>
-      </c>
-      <c r="P25">
-        <v>3.04</v>
-      </c>
-      <c r="Q25">
-        <v>2.52</v>
-      </c>
       <c r="R25">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,29 +5684,29 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>2.59</v>
       </c>
       <c r="Q33">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
         <v>2.88</v>
@@ -5715,37 +5715,37 @@
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
         <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>3.87</v>
       </c>
       <c r="Q34">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.81</v>
+      </c>
+      <c r="AB34">
+        <v>1.95</v>
+      </c>
+      <c r="AC34">
+        <v>2.66</v>
+      </c>
+      <c r="AD34">
+        <v>1.41</v>
+      </c>
+      <c r="AE34">
         <v>1.12</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.25</v>
-      </c>
-      <c r="Z34">
-        <v>3.82</v>
-      </c>
-      <c r="AA34">
-        <v>1.79</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.83</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,84 +6010,84 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>2.86</v>
+      </c>
+      <c r="U35">
+        <v>2.46</v>
+      </c>
+      <c r="V35">
+        <v>1.46</v>
+      </c>
+      <c r="W35">
+        <v>1.12</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.82</v>
+      </c>
+      <c r="AA35">
+        <v>1.79</v>
+      </c>
+      <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.83</v>
+      </c>
+      <c r="AD35">
+        <v>1.33</v>
+      </c>
+      <c r="AE35">
+        <v>1.09</v>
+      </c>
+      <c r="AF35">
+        <v>1.62</v>
+      </c>
+      <c r="AG35">
+        <v>2.15</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.88</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.05</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.42</v>
-      </c>
-      <c r="AD35">
-        <v>1.23</v>
-      </c>
-      <c r="AE35">
-        <v>1.05</v>
-      </c>
-      <c r="AF35">
-        <v>1.75</v>
-      </c>
-      <c r="AG35">
-        <v>1.96</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.29</v>
-      </c>
-      <c r="AK35">
-        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>4.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
+        <v>2.71</v>
+      </c>
+      <c r="U36">
+        <v>2.81</v>
+      </c>
+      <c r="V36">
+        <v>1.36</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.27</v>
+      </c>
+      <c r="Z36">
+        <v>3.42</v>
+      </c>
+      <c r="AA36">
+        <v>1.88</v>
+      </c>
+      <c r="AB36">
+        <v>1.88</v>
+      </c>
+      <c r="AC36">
         <v>3.08</v>
       </c>
-      <c r="U36">
-        <v>2.48</v>
-      </c>
-      <c r="V36">
-        <v>1.46</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.26</v>
-      </c>
-      <c r="Z36">
-        <v>3.58</v>
-      </c>
-      <c r="AA36">
-        <v>1.83</v>
-      </c>
-      <c r="AB36">
-        <v>1.94</v>
-      </c>
-      <c r="AC36">
-        <v>3.11</v>
-      </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="O37">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="P37">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>4.73</v>
       </c>
       <c r="Q39">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.27</v>
+        <v>3.11</v>
       </c>
       <c r="O49">
-        <v>3.16</v>
+        <v>3.56</v>
       </c>
       <c r="P49">
-        <v>3.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="U49">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="V49">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AB49">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AC49">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.11</v>
+        <v>4.03</v>
       </c>
       <c r="O50">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.03</v>
+        <v>2.27</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>3.19</v>
       </c>
       <c r="Q51">
-        <v>4.36</v>
+        <v>2.96</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S51">
+        <v>1.39</v>
+      </c>
+      <c r="T51">
+        <v>2.7</v>
+      </c>
+      <c r="U51">
+        <v>2.88</v>
+      </c>
+      <c r="V51">
+        <v>1.35</v>
+      </c>
+      <c r="W51">
+        <v>1.03</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
         <v>1.3</v>
       </c>
-      <c r="T51">
-        <v>3.1</v>
-      </c>
-      <c r="U51">
-        <v>2.49</v>
-      </c>
-      <c r="V51">
-        <v>1.44</v>
-      </c>
-      <c r="W51">
-        <v>1.08</v>
-      </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.22</v>
-      </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,65 +8785,65 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
         <v>3.5</v>
       </c>
       <c r="P52">
+        <v>2.87</v>
+      </c>
+      <c r="Q52">
+        <v>2.7</v>
+      </c>
+      <c r="R52">
+        <v>2.2</v>
+      </c>
+      <c r="S52">
+        <v>1.33</v>
+      </c>
+      <c r="T52">
         <v>3</v>
       </c>
-      <c r="Q52">
-        <v>2.82</v>
-      </c>
-      <c r="R52">
-        <v>2.37</v>
-      </c>
-      <c r="S52">
-        <v>1.28</v>
-      </c>
-      <c r="T52">
-        <v>3.12</v>
-      </c>
       <c r="U52">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V52">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AA52">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AB52">
+        <v>1.99</v>
+      </c>
+      <c r="AC52">
+        <v>2.93</v>
+      </c>
+      <c r="AD52">
+        <v>1.37</v>
+      </c>
+      <c r="AE52">
+        <v>1.1</v>
+      </c>
+      <c r="AF52">
+        <v>1.64</v>
+      </c>
+      <c r="AG52">
         <v>2.1</v>
       </c>
-      <c r="AC52">
-        <v>2.68</v>
-      </c>
-      <c r="AD52">
-        <v>1.45</v>
-      </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
-      <c r="AF52">
-        <v>1.56</v>
-      </c>
-      <c r="AG52">
-        <v>2.25</v>
-      </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="Q58">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
         <v>1.36</v>
       </c>
       <c r="T58">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="U58">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z58">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA58">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC58">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S62">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T62">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U62">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V62">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z62">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="AA62">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AB62">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC62">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="AD62">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK62">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11067,61 +11067,61 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="O66">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="P66">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="Q66">
+        <v>2.21</v>
+      </c>
+      <c r="R66">
+        <v>2.44</v>
+      </c>
+      <c r="S66">
+        <v>1.29</v>
+      </c>
+      <c r="T66">
+        <v>3.13</v>
+      </c>
+      <c r="U66">
         <v>2.38</v>
       </c>
-      <c r="R66">
-        <v>2.42</v>
-      </c>
-      <c r="S66">
-        <v>1.32</v>
-      </c>
-      <c r="T66">
-        <v>3.16</v>
-      </c>
-      <c r="U66">
-        <v>2.44</v>
-      </c>
       <c r="V66">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W66">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="AA66">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB66">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AC66">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD66">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE66">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG66">
         <v>2.1</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK66">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="O67">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="P67">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="Q67">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R67">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T67">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="U67">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="V67">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Z67">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AA67">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AB67">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AC67">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AD67">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG67">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,61 +11396,61 @@
         <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="Q68">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="R68">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T68">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U68">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V68">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z68">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AA68">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB68">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AC68">
-        <v>3.84</v>
+        <v>4.12</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE68">
         <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N69">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.02</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
         <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="O81">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="P81">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q81">
         <v>3.4</v>
       </c>
       <c r="R81">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S81">
         <v>1.44</v>
       </c>
       <c r="T81">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U81">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V81">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W81">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z81">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA81">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AB81">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC81">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="AD81">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE81">
         <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG81">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N86">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N87">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="O103">
-        <v>3.66</v>
+        <v>3.06</v>
       </c>
       <c r="P103">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="Q103">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="R103">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S103">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="U103">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V103">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z103">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="AA103">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AD103">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE103">
         <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O104">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="P104">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="Q104">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="R104">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S104">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="U104">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="AA104">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB104">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC104">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AD104">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE104">
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG104">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O107">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P107">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q107">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R107">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S107">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U107">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V107">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
         <v>1.06</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC107">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE107">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG107">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK107">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,58 +17913,58 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="O108">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="P108">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q108">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="R108">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T108">
+        <v>2.62</v>
+      </c>
+      <c r="U108">
         <v>3</v>
       </c>
-      <c r="U108">
-        <v>2.72</v>
-      </c>
       <c r="V108">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z108">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AA108">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AB108">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AC108">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD108">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF108">
         <v>2</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
+        <v>1.68</v>
+      </c>
+      <c r="O109">
+        <v>3.8</v>
+      </c>
+      <c r="P109">
+        <v>4.5</v>
+      </c>
+      <c r="Q109">
+        <v>2.2</v>
+      </c>
+      <c r="R109">
+        <v>2.25</v>
+      </c>
+      <c r="S109">
+        <v>1.3</v>
+      </c>
+      <c r="T109">
+        <v>2.95</v>
+      </c>
+      <c r="U109">
+        <v>2.55</v>
+      </c>
+      <c r="V109">
+        <v>1.44</v>
+      </c>
+      <c r="W109">
+        <v>1.07</v>
+      </c>
+      <c r="X109">
+        <v>1</v>
+      </c>
+      <c r="Y109">
+        <v>1.26</v>
+      </c>
+      <c r="Z109">
+        <v>3.66</v>
+      </c>
+      <c r="AA109">
         <v>1.81</v>
       </c>
-      <c r="O109">
-        <v>3.35</v>
-      </c>
-      <c r="P109">
-        <v>4.4</v>
-      </c>
-      <c r="Q109">
-        <v>2.38</v>
-      </c>
-      <c r="R109">
+      <c r="AB109">
+        <v>1.86</v>
+      </c>
+      <c r="AC109">
+        <v>3.04</v>
+      </c>
+      <c r="AD109">
+        <v>1.29</v>
+      </c>
+      <c r="AE109">
+        <v>1.07</v>
+      </c>
+      <c r="AF109">
+        <v>1.78</v>
+      </c>
+      <c r="AG109">
+        <v>1.88</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.25</v>
+      </c>
+      <c r="AK109">
         <v>2.1</v>
-      </c>
-      <c r="S109">
-        <v>1.42</v>
-      </c>
-      <c r="T109">
-        <v>2.62</v>
-      </c>
-      <c r="U109">
-        <v>3</v>
-      </c>
-      <c r="V109">
-        <v>1.29</v>
-      </c>
-      <c r="W109">
-        <v>1.04</v>
-      </c>
-      <c r="X109">
-        <v>1.03</v>
-      </c>
-      <c r="Y109">
-        <v>1.4</v>
-      </c>
-      <c r="Z109">
-        <v>2.7</v>
-      </c>
-      <c r="AA109">
-        <v>2.2</v>
-      </c>
-      <c r="AB109">
-        <v>1.58</v>
-      </c>
-      <c r="AC109">
-        <v>4.05</v>
-      </c>
-      <c r="AD109">
-        <v>1.17</v>
-      </c>
-      <c r="AE109">
-        <v>1.02</v>
-      </c>
-      <c r="AF109">
-        <v>2</v>
-      </c>
-      <c r="AG109">
-        <v>1.67</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.24</v>
-      </c>
-      <c r="AK109">
-        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
         <v>3.55</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.69</v>
+      </c>
+      <c r="U110">
+        <v>2.8</v>
+      </c>
+      <c r="V110">
+        <v>1.35</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.83</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.44</v>
-      </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
       <c r="Z110">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>2.89</v>
+        <v>3.67</v>
       </c>
       <c r="AD110">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P111">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R111">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T111">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="U111">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z111">
-        <v>3.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA111">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB111">
+        <v>1.8</v>
+      </c>
+      <c r="AC111">
+        <v>3.34</v>
+      </c>
+      <c r="AD111">
+        <v>1.24</v>
+      </c>
+      <c r="AE111">
+        <v>1.04</v>
+      </c>
+      <c r="AF111">
         <v>1.86</v>
       </c>
-      <c r="AC111">
-        <v>3.04</v>
-      </c>
-      <c r="AD111">
-        <v>1.29</v>
-      </c>
-      <c r="AE111">
-        <v>1.07</v>
-      </c>
-      <c r="AF111">
-        <v>1.78</v>
-      </c>
       <c r="AG111">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="O112">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q112">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="R112">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
+        <v>2.83</v>
+      </c>
+      <c r="U112">
+        <v>2.5</v>
+      </c>
+      <c r="V112">
+        <v>1.44</v>
+      </c>
+      <c r="W112">
+        <v>1.07</v>
+      </c>
+      <c r="X112">
+        <v>1</v>
+      </c>
+      <c r="Y112">
+        <v>1.23</v>
+      </c>
+      <c r="Z112">
+        <v>3.5</v>
+      </c>
+      <c r="AA112">
+        <v>1.75</v>
+      </c>
+      <c r="AB112">
+        <v>1.93</v>
+      </c>
+      <c r="AC112">
         <v>2.89</v>
       </c>
-      <c r="U112">
-        <v>2.97</v>
-      </c>
-      <c r="V112">
-        <v>1.37</v>
-      </c>
-      <c r="W112">
-        <v>1.05</v>
-      </c>
-      <c r="X112">
-        <v>1.02</v>
-      </c>
-      <c r="Y112">
-        <v>1.27</v>
-      </c>
-      <c r="Z112">
-        <v>3.14</v>
-      </c>
-      <c r="AA112">
-        <v>2</v>
-      </c>
-      <c r="AB112">
-        <v>1.8</v>
-      </c>
-      <c r="AC112">
-        <v>3.34</v>
-      </c>
       <c r="AD112">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N120">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N127">

--- a/jogos_2026-10-03.xlsx
+++ b/jogos_2026-10-03.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O2">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -819,43 +819,43 @@
         <v>2.7</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB3">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC3">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,58 +961,58 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>4.83</v>
+        <v>4.66</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="U4">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>1.66</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AK4">
         <v>1.14</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AD5">
         <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.83</v>
@@ -1287,58 +1287,58 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
         <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
         <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
         <v>1.81</v>
@@ -1360,7 +1360,7 @@
         <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>2.23</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R7">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U7">
         <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="AA7">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC7">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,58 +1613,58 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="O8">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T8">
         <v>2.75</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
         <v>1.03</v>
       </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AA8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC8">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
         <v>1.75</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>1.7</v>
       </c>
       <c r="O11">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
         <v>4.33</v>
@@ -2114,22 +2114,22 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S11">
         <v>1.27</v>
       </c>
       <c r="T11">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2138,25 +2138,25 @@
         <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AC11">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD11">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
         <v>2.15</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="P12">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="R13">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V13">
         <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC13">
-        <v>3.48</v>
+        <v>3.07</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="U14">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="AA14">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB14">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
+        <v>2.2</v>
+      </c>
+      <c r="Q15">
+        <v>3.5</v>
+      </c>
+      <c r="R15">
+        <v>2.14</v>
+      </c>
+      <c r="S15">
+        <v>1.36</v>
+      </c>
+      <c r="T15">
         <v>2.8</v>
       </c>
-      <c r="Q15">
-        <v>2.99</v>
-      </c>
-      <c r="R15">
-        <v>2.02</v>
-      </c>
-      <c r="S15">
-        <v>1.43</v>
-      </c>
-      <c r="T15">
-        <v>2.74</v>
-      </c>
       <c r="U15">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
         <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>2.25</v>
+      </c>
+      <c r="O16">
+        <v>3.3</v>
+      </c>
+      <c r="P16">
         <v>2.8</v>
       </c>
-      <c r="O16">
-        <v>3.51</v>
-      </c>
-      <c r="P16">
-        <v>2.44</v>
-      </c>
       <c r="Q16">
-        <v>3.64</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
         <v>1.04</v>
       </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>3.71</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
         <v>3.6</v>
       </c>
       <c r="P18">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R18">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T18">
         <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.13</v>
@@ -3276,31 +3276,31 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA18">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB18">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AD18">
         <v>1.56</v>
       </c>
       <c r="AE18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="O19">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,25 +3445,25 @@
         <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3738,58 +3738,58 @@
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
         <v>3.3</v>
@@ -3916,43 +3916,43 @@
         <v>3.25</v>
       </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
         <v>4</v>
       </c>
       <c r="AA22">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB22">
         <v>2.08</v>
       </c>
       <c r="AC22">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AD22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.56</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O23">
         <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="Q23">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
+        <v>1.11</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.17</v>
+      </c>
+      <c r="Z23">
+        <v>4.05</v>
+      </c>
+      <c r="AA23">
+        <v>1.62</v>
+      </c>
+      <c r="AB23">
+        <v>2.25</v>
+      </c>
+      <c r="AC23">
+        <v>2.72</v>
+      </c>
+      <c r="AD23">
+        <v>1.33</v>
+      </c>
+      <c r="AE23">
         <v>1.14</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.15</v>
-      </c>
-      <c r="Z23">
-        <v>4.38</v>
-      </c>
-      <c r="AA23">
-        <v>1.79</v>
-      </c>
-      <c r="AB23">
-        <v>1.97</v>
-      </c>
-      <c r="AC23">
-        <v>2.38</v>
-      </c>
-      <c r="AD23">
-        <v>1.46</v>
-      </c>
-      <c r="AE23">
-        <v>1.16</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="Q24">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V24">
+        <v>1.7</v>
+      </c>
+      <c r="W24">
+        <v>1.15</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.17</v>
+      </c>
+      <c r="Z24">
+        <v>5.1</v>
+      </c>
+      <c r="AA24">
+        <v>1.57</v>
+      </c>
+      <c r="AB24">
+        <v>2.35</v>
+      </c>
+      <c r="AC24">
+        <v>2.35</v>
+      </c>
+      <c r="AD24">
         <v>1.55</v>
       </c>
-      <c r="W24">
-        <v>1.14</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.16</v>
-      </c>
-      <c r="Z24">
-        <v>4.38</v>
-      </c>
-      <c r="AA24">
-        <v>1.81</v>
-      </c>
-      <c r="AB24">
-        <v>1.96</v>
-      </c>
-      <c r="AC24">
-        <v>2.49</v>
-      </c>
-      <c r="AD24">
-        <v>1.44</v>
-      </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.83</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="O26">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="P26">
-        <v>5.86</v>
+        <v>4.45</v>
       </c>
       <c r="Q26">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="S26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="U26">
         <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W26">
         <v>1.08</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB26">
+        <v>1.98</v>
+      </c>
+      <c r="AC26">
+        <v>2.95</v>
+      </c>
+      <c r="AD26">
+        <v>1.36</v>
+      </c>
+      <c r="AE26">
+        <v>1.11</v>
+      </c>
+      <c r="AF26">
+        <v>1.75</v>
+      </c>
+      <c r="AG26">
         <v>1.91</v>
-      </c>
-      <c r="AC26">
-        <v>2.89</v>
-      </c>
-      <c r="AD26">
-        <v>1.38</v>
-      </c>
-      <c r="AE26">
-        <v>1.13</v>
-      </c>
-      <c r="AF26">
-        <v>1.76</v>
-      </c>
-      <c r="AG26">
-        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>1.66</v>
+        <v>6.25</v>
       </c>
       <c r="Q27">
-        <v>5</v>
+        <v>2.03</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.19</v>
+        <v>3.38</v>
       </c>
       <c r="AA27">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB27">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>1.1</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>5.3</v>
+      </c>
+      <c r="O28">
+        <v>3.7</v>
+      </c>
+      <c r="P28">
+        <v>1.55</v>
+      </c>
+      <c r="Q28">
+        <v>6</v>
+      </c>
+      <c r="R28">
+        <v>2.15</v>
+      </c>
+      <c r="S28">
         <v>1.42</v>
       </c>
-      <c r="O28">
-        <v>3.94</v>
-      </c>
-      <c r="P28">
-        <v>6.77</v>
-      </c>
-      <c r="Q28">
-        <v>1.94</v>
-      </c>
-      <c r="R28">
-        <v>2.23</v>
-      </c>
-      <c r="S28">
-        <v>1.34</v>
-      </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>1.08</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R30">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
         <v>1.33</v>
@@ -5226,34 +5226,34 @@
         <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC30">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AD30">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
         <v>2.18</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,16 +5371,16 @@
         <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S31">
         <v>1.31</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U31">
         <v>2.57</v>
@@ -5395,31 +5395,31 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB31">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AK31">
         <v>1.44</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O32">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U32">
         <v>2.2</v>
       </c>
       <c r="V32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5573,16 +5573,16 @@
         <v>2.27</v>
       </c>
       <c r="AD32">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AE32">
         <v>1.19</v>
       </c>
       <c r="AF32">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG32">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5684,32 +5684,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="V33">
         <v>1.36</v>
@@ -5718,34 +5718,34 @@
         <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.29</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
+        <v>1.73</v>
+      </c>
+      <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.21</v>
+      </c>
+      <c r="AK34">
         <v>1.7</v>
-      </c>
-      <c r="AG34">
-        <v>2.05</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.2</v>
-      </c>
-      <c r="AK34">
-        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>4.5</v>
       </c>
       <c r="Q35">
-        <v>3.56</v>
+        <v>2.15</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V35">
         <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AA35">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC35">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="AD35">
         <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.31</v>
+        <v>2.95</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="U36">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="O37">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>2.93</v>
+        <v>4.5</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="U38">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
         <v>1.09</v>
@@ -6545,16 +6545,16 @@
         <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AC38">
         <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.6</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK38">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,35 +6662,35 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.73</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
+        <v>3.1</v>
+      </c>
+      <c r="R39">
         <v>2.1</v>
       </c>
-      <c r="R39">
-        <v>2.3</v>
-      </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6699,31 +6699,31 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,61 +6832,61 @@
         <v>5.25</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="O43">
         <v>3.1</v>
@@ -7360,13 +7360,13 @@
         <v>2.28</v>
       </c>
       <c r="AB43">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC43">
-        <v>3.96</v>
+        <v>4.17</v>
       </c>
       <c r="AD43">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
         <v>1.02</v>
@@ -7375,7 +7375,7 @@
         <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
         <v>3.62</v>
       </c>
       <c r="P44">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="Q44">
         <v>2.7</v>
@@ -7538,7 +7538,7 @@
         <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7647,16 +7647,16 @@
         <v>2.43</v>
       </c>
       <c r="O45">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="P45">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
       </c>
       <c r="R45">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
         <v>1.22</v>
@@ -7665,19 +7665,19 @@
         <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z45">
         <v>4.7</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q46">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
         <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z46">
-        <v>3.68</v>
+        <v>4.51</v>
       </c>
       <c r="AA46">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC46">
         <v>2.7</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
         <v>1.33</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="O47">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="P47">
-        <v>3.6</v>
+        <v>3.93</v>
       </c>
       <c r="Q47">
         <v>2.3</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
         <v>1.26</v>
@@ -8000,7 +8000,7 @@
         <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.15</v>
@@ -8009,10 +8009,10 @@
         <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB47">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AC47">
         <v>2.41</v>
@@ -8021,13 +8021,13 @@
         <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O48">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="P48">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V48">
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.04</v>
@@ -8169,28 +8169,28 @@
         <v>1.21</v>
       </c>
       <c r="Z48">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
         <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE48">
         <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
         <v>1.57</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="O49">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="P49">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="Q49">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AB49">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AC49">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.03</v>
+        <v>2.18</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="U50">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
         <v>2</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.27</v>
+        <v>3.52</v>
       </c>
       <c r="O51">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="Q51">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
+        <v>1.29</v>
+      </c>
+      <c r="T51">
+        <v>3.26</v>
+      </c>
+      <c r="U51">
+        <v>2.38</v>
+      </c>
+      <c r="V51">
+        <v>1.5</v>
+      </c>
+      <c r="W51">
+        <v>1.09</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.2</v>
+      </c>
+      <c r="Z51">
+        <v>4.1</v>
+      </c>
+      <c r="AA51">
+        <v>1.66</v>
+      </c>
+      <c r="AB51">
+        <v>2.11</v>
+      </c>
+      <c r="AC51">
+        <v>2.59</v>
+      </c>
+      <c r="AD51">
         <v>1.39</v>
       </c>
-      <c r="T51">
-        <v>2.7</v>
-      </c>
-      <c r="U51">
-        <v>2.88</v>
-      </c>
-      <c r="V51">
-        <v>1.35</v>
-      </c>
-      <c r="W51">
-        <v>1.03</v>
-      </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="Y51">
+      <c r="AE51">
+        <v>1.14</v>
+      </c>
+      <c r="AF51">
+        <v>1.53</v>
+      </c>
+      <c r="AG51">
+        <v>2.45</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.22</v>
+      </c>
+      <c r="AK51">
         <v>1.3</v>
-      </c>
-      <c r="Z51">
-        <v>3.44</v>
-      </c>
-      <c r="AA51">
-        <v>2</v>
-      </c>
-      <c r="AB51">
-        <v>1.83</v>
-      </c>
-      <c r="AC51">
-        <v>3.2</v>
-      </c>
-      <c r="AD51">
-        <v>1.3</v>
-      </c>
-      <c r="AE51">
-        <v>1.06</v>
-      </c>
-      <c r="AF51">
-        <v>1.73</v>
-      </c>
-      <c r="AG51">
-        <v>1.98</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.31</v>
-      </c>
-      <c r="AK51">
-        <v>1.56</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.8</v>
+        <v>1.15</v>
       </c>
       <c r="O53">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="P53">
-        <v>1.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q53">
-        <v>3.98</v>
+        <v>1.38</v>
       </c>
       <c r="R53">
-        <v>2.53</v>
+        <v>3.84</v>
       </c>
       <c r="S53">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="T53">
+        <v>5.8</v>
+      </c>
+      <c r="U53">
+        <v>1.58</v>
+      </c>
+      <c r="V53">
+        <v>2.18</v>
+      </c>
+      <c r="W53">
+        <v>1.36</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1.01</v>
+      </c>
+      <c r="Z53">
+        <v>10</v>
+      </c>
+      <c r="AA53">
+        <v>1.12</v>
+      </c>
+      <c r="AB53">
         <v>5</v>
       </c>
-      <c r="U53">
-        <v>1.87</v>
-      </c>
-      <c r="V53">
-        <v>1.85</v>
-      </c>
-      <c r="W53">
-        <v>1.22</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.07</v>
-      </c>
-      <c r="Z53">
-        <v>7</v>
-      </c>
-      <c r="AA53">
-        <v>1.3</v>
-      </c>
-      <c r="AB53">
-        <v>2.97</v>
-      </c>
       <c r="AC53">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AD53">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="AE53">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AF53">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.92</v>
+        <v>1.06</v>
       </c>
       <c r="AK53">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="O54">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="P54">
-        <v>15.5</v>
+        <v>3.39</v>
       </c>
       <c r="Q54">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="R54">
-        <v>3.74</v>
+        <v>2.7</v>
       </c>
       <c r="S54">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="T54">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="V54">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="W54">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA54">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AB54">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AC54">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AD54">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="AE54">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AG54">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK54">
-        <v>5.5</v>
+        <v>1.88</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.89</v>
+        <v>2.85</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P55">
-        <v>3.33</v>
+        <v>1.71</v>
       </c>
       <c r="Q55">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="R55">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T55">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U55">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="V55">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="W55">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA55">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB55">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AC55">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD55">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE55">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF55">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AG55">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AK55">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P56">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q56">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T56">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U56">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="V56">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AA56">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AB56">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC56">
-        <v>3.92</v>
+        <v>4.03</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG56">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK56">
         <v>1.5</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="O57">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="Q57">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R57">
         <v>2.2</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T57">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="U57">
         <v>2.63</v>
@@ -9627,7 +9627,7 @@
         <v>1.41</v>
       </c>
       <c r="W57">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1</v>
@@ -9636,25 +9636,25 @@
         <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA57">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB57">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC57">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD57">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
         <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG57">
         <v>1.83</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="O59">
-        <v>4.87</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>7.41</v>
+        <v>5.5</v>
       </c>
       <c r="Q59">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U59">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V59">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9962,28 +9962,28 @@
         <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="AA59">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB59">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC59">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AD59">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
         <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG59">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="R60">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="S60">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U60">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="V60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>3.68</v>
+        <v>4.22</v>
       </c>
       <c r="AA60">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB60">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC60">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF60">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="O61">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="P61">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="Q61">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="R61">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S61">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T61">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U61">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W61">
         <v>1.01</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Z61">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC61">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD61">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE61">
         <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG61">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O63">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q63">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T63">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="V63">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W63">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA63">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AC63">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AD63">
+        <v>1.69</v>
+      </c>
+      <c r="AE63">
+        <v>1.29</v>
+      </c>
+      <c r="AF63">
+        <v>1.4</v>
+      </c>
+      <c r="AG63">
+        <v>2.75</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.63</v>
       </c>
-      <c r="AE63">
-        <v>1.22</v>
-      </c>
-      <c r="AF63">
-        <v>1.41</v>
-      </c>
-      <c r="AG63">
-        <v>2.62</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.22</v>
-      </c>
       <c r="AK63">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P64">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q64">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R64">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="S64">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T64">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="V64">
         <v>1.5</v>
@@ -10771,34 +10771,34 @@
         <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB64">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AC64">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AD64">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
         <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -10904,55 +10904,55 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="O65">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="Q65">
-        <v>4.78</v>
+        <v>3.84</v>
       </c>
       <c r="R65">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S65">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U65">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="V65">
         <v>1.3</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z65">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AA65">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AB65">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AC65">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="AD65">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE65">
         <v>1.01</v>
@@ -10961,7 +10961,7 @@
         <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK65">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11556,55 +11556,55 @@
         </is>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P69">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="Q69">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="R69">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T69">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="V69">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W69">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA69">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
         <v>2.97</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
         <v>1.08</v>
@@ -11613,7 +11613,7 @@
         <v>1.81</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O70">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="P70">
-        <v>4.92</v>
+        <v>4.33</v>
       </c>
       <c r="Q70">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R70">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S70">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T70">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="U70">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V70">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z70">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AA70">
+        <v>1.79</v>
+      </c>
+      <c r="AB70">
+        <v>1.96</v>
+      </c>
+      <c r="AC70">
+        <v>2.95</v>
+      </c>
+      <c r="AD70">
+        <v>1.37</v>
+      </c>
+      <c r="AE70">
+        <v>1.1</v>
+      </c>
+      <c r="AF70">
+        <v>1.73</v>
+      </c>
+      <c r="AG70">
         <v>1.95</v>
       </c>
-      <c r="AB70">
-        <v>1.75</v>
-      </c>
-      <c r="AC70">
-        <v>3.14</v>
-      </c>
-      <c r="AD70">
-        <v>1.33</v>
-      </c>
-      <c r="AE70">
-        <v>1.07</v>
-      </c>
-      <c r="AF70">
-        <v>1.88</v>
-      </c>
-      <c r="AG70">
-        <v>1.76</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="O71">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T71">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U71">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z71">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AC71">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="AD71">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE71">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P72">
-        <v>4.39</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="R72">
         <v>2.05</v>
       </c>
       <c r="S72">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T72">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U72">
+        <v>3.12</v>
+      </c>
+      <c r="V72">
+        <v>1.33</v>
+      </c>
+      <c r="W72">
+        <v>1.04</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
+        <v>1.36</v>
+      </c>
+      <c r="Z72">
         <v>2.9</v>
       </c>
-      <c r="V72">
-        <v>1.38</v>
-      </c>
-      <c r="W72">
-        <v>1.03</v>
-      </c>
-      <c r="X72">
-        <v>1.03</v>
-      </c>
-      <c r="Y72">
-        <v>1.33</v>
-      </c>
-      <c r="Z72">
-        <v>3.1</v>
-      </c>
       <c r="AA72">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB72">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC72">
-        <v>3.43</v>
+        <v>4.1</v>
       </c>
       <c r="AD72">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE72">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG72">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK72">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>2.4</v>
+      </c>
+      <c r="O73">
+        <v>3.3</v>
+      </c>
+      <c r="P73">
+        <v>2.6</v>
+      </c>
+      <c r="Q73">
+        <v>3.1</v>
+      </c>
+      <c r="R73">
         <v>2.26</v>
       </c>
-      <c r="O73">
-        <v>3.7</v>
-      </c>
-      <c r="P73">
-        <v>2.99</v>
-      </c>
-      <c r="Q73">
-        <v>2.99</v>
-      </c>
-      <c r="R73">
-        <v>2.25</v>
-      </c>
       <c r="S73">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U73">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V73">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>3.43</v>
+        <v>3.9</v>
       </c>
       <c r="AA73">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC73">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AD73">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE73">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AG73">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O74">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="Q74">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="R74">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="S74">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="T74">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="U74">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="V74">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
         <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z74">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA74">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB74">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC74">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD74">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF74">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AG74">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="O75">
-        <v>5.24</v>
+        <v>6.5</v>
       </c>
       <c r="P75">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="Q75">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="R75">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="S75">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U75">
-        <v>2.76</v>
+        <v>2.27</v>
       </c>
       <c r="V75">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W75">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z75">
-        <v>3.51</v>
+        <v>4.65</v>
       </c>
       <c r="AA75">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AB75">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AC75">
-        <v>2.99</v>
+        <v>2.36</v>
       </c>
       <c r="AD75">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AG75">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK75">
-        <v>3.04</v>
+        <v>4.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O76">
         <v>4.2</v>
       </c>
       <c r="P76">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q76">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="R76">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S76">
         <v>1.25</v>
       </c>
       <c r="T76">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V76">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W76">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z76">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA76">
         <v>1.5</v>
       </c>
       <c r="AB76">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC76">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AD76">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK76">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,61 +13023,61 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U78">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="V78">
         <v>1.36</v>
       </c>
       <c r="W78">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z78">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB78">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC78">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="AD78">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG78">
         <v>1.85</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q79">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
+        <v>1.07</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.34</v>
+      </c>
+      <c r="Z79">
+        <v>2.85</v>
+      </c>
+      <c r="AA79">
+        <v>2.16</v>
+      </c>
+      <c r="AB79">
+        <v>1.69</v>
+      </c>
+      <c r="AC79">
+        <v>3.84</v>
+      </c>
+      <c r="AD79">
+        <v>1.22</v>
+      </c>
+      <c r="AE79">
         <v>1.02</v>
       </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>1.37</v>
-      </c>
-      <c r="Z79">
-        <v>2.95</v>
-      </c>
-      <c r="AA79">
-        <v>2.1</v>
-      </c>
-      <c r="AB79">
-        <v>1.74</v>
-      </c>
-      <c r="AC79">
-        <v>3.65</v>
-      </c>
-      <c r="AD79">
-        <v>1.24</v>
-      </c>
-      <c r="AE79">
-        <v>1.03</v>
-      </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>3.2</v>
+      </c>
+      <c r="O80">
         <v>3.1</v>
       </c>
-      <c r="O80">
-        <v>3.3</v>
-      </c>
       <c r="P80">
+        <v>2.05</v>
+      </c>
+      <c r="Q80">
+        <v>3.6</v>
+      </c>
+      <c r="R80">
+        <v>2.26</v>
+      </c>
+      <c r="S80">
+        <v>1.33</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80">
+        <v>2.52</v>
+      </c>
+      <c r="V80">
+        <v>1.4</v>
+      </c>
+      <c r="W80">
+        <v>1.06</v>
+      </c>
+      <c r="X80">
+        <v>1.03</v>
+      </c>
+      <c r="Y80">
+        <v>1.26</v>
+      </c>
+      <c r="Z80">
+        <v>3.5</v>
+      </c>
+      <c r="AA80">
         <v>1.95</v>
       </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
-      </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O82">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="P82">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="O83">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q83">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="R83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U83">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
         <v>1.04</v>
       </c>
       <c r="X83">
+        <v>1.05</v>
+      </c>
+      <c r="Y83">
+        <v>1.3</v>
+      </c>
+      <c r="Z83">
+        <v>2.97</v>
+      </c>
+      <c r="AA83">
+        <v>2.15</v>
+      </c>
+      <c r="AB83">
+        <v>1.6</v>
+      </c>
+      <c r="AC83">
+        <v>4.4</v>
+      </c>
+      <c r="AD83">
+        <v>1.18</v>
+      </c>
+      <c r="AE83">
         <v>1.04</v>
       </c>
-      <c r="Y83">
-        <v>1.29</v>
-      </c>
-      <c r="Z83">
-        <v>3.04</v>
-      </c>
-      <c r="AA83">
-        <v>2.05</v>
-      </c>
-      <c r="AB83">
-        <v>1.66</v>
-      </c>
-      <c r="AC83">
-        <v>3.9</v>
-      </c>
-      <c r="AD83">
-        <v>1.22</v>
-      </c>
-      <c r="AE83">
-        <v>1.05</v>
-      </c>
       <c r="AF83">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O84">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P84">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q84">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R84">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S84">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T84">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U84">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V84">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W84">
+        <v>1.07</v>
+      </c>
+      <c r="X84">
         <v>1.03</v>
-      </c>
-      <c r="X84">
-        <v>1.02</v>
       </c>
       <c r="Y84">
         <v>1.34</v>
       </c>
       <c r="Z84">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AA84">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB84">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC84">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE84">
         <v>1.04</v>
       </c>
       <c r="AF84">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG84">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AK84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O85">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>3.38</v>
+        <v>3.69</v>
       </c>
       <c r="Q85">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="R85">
+        <v>2.1</v>
+      </c>
+      <c r="S85">
+        <v>1.4</v>
+      </c>
+      <c r="T85">
+        <v>2.6</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>1.35</v>
+      </c>
+      <c r="W85">
+        <v>1.07</v>
+      </c>
+      <c r="X85">
+        <v>1.02</v>
+      </c>
+      <c r="Y85">
+        <v>1.37</v>
+      </c>
+      <c r="Z85">
+        <v>2.79</v>
+      </c>
+      <c r="AA85">
         <v>2.15</v>
       </c>
-      <c r="S85">
-        <v>1.46</v>
-      </c>
-      <c r="T85">
-        <v>2.64</v>
-      </c>
-      <c r="U85">
-        <v>2.96</v>
-      </c>
-      <c r="V85">
-        <v>1.37</v>
-      </c>
-      <c r="W85">
+      <c r="AB85">
+        <v>1.66</v>
+      </c>
+      <c r="AC85">
+        <v>3.95</v>
+      </c>
+      <c r="AD85">
+        <v>1.21</v>
+      </c>
+      <c r="AE85">
         <v>1.02</v>
       </c>
-      <c r="X85">
-        <v>1.01</v>
-      </c>
-      <c r="Y85">
-        <v>1.38</v>
-      </c>
-      <c r="Z85">
-        <v>2.91</v>
-      </c>
-      <c r="AA85">
-        <v>2.12</v>
-      </c>
-      <c r="AB85">
-        <v>1.72</v>
-      </c>
-      <c r="AC85">
-        <v>3.72</v>
-      </c>
-      <c r="AD85">
-        <v>1.24</v>
-      </c>
-      <c r="AE85">
-        <v>1.03</v>
-      </c>
       <c r="AF85">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG85">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK85">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O86">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R86">
         <v>2.1</v>
       </c>
       <c r="S86">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="U86">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="V86">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W86">
         <v>1.08</v>
@@ -14360,28 +14360,28 @@
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z86">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA86">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB86">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC86">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD86">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE86">
         <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
         <v>2</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AK86">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q87">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="R87">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S87">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T87">
         <v>2.4</v>
       </c>
       <c r="U87">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="V87">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
+        <v>1.08</v>
+      </c>
+      <c r="X87">
+        <v>1.03</v>
+      </c>
+      <c r="Y87">
+        <v>1.25</v>
+      </c>
+      <c r="Z87">
+        <v>3.5</v>
+      </c>
+      <c r="AA87">
+        <v>1.95</v>
+      </c>
+      <c r="AB87">
+        <v>1.82</v>
+      </c>
+      <c r="AC87">
+        <v>3.3</v>
+      </c>
+      <c r="AD87">
+        <v>1.3</v>
+      </c>
+      <c r="AE87">
         <v>1.07</v>
       </c>
-      <c r="X87">
-        <v>1.05</v>
-      </c>
-      <c r="Y87">
-        <v>1.33</v>
-      </c>
-      <c r="Z87">
-        <v>2.91</v>
-      </c>
-      <c r="AA87">
-        <v>2.15</v>
-      </c>
-      <c r="AB87">
-        <v>1.62</v>
-      </c>
-      <c r="AC87">
-        <v>3.9</v>
-      </c>
-      <c r="AD87">
-        <v>1.18</v>
-      </c>
-      <c r="AE87">
-        <v>1.04</v>
-      </c>
       <c r="AF87">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG87">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK87">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15957,58 +15957,58 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O96">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P96">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q96">
         <v>2.4</v>
       </c>
       <c r="R96">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S96">
         <v>1.18</v>
       </c>
       <c r="T96">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="U96">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="V96">
         <v>1.77</v>
       </c>
       <c r="W96">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z96">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA96">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB96">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC96">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AD96">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AE96">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF96">
         <v>1.33</v>
@@ -16030,7 +16030,7 @@
         <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,16 +16120,16 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O97">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R97">
         <v>2.5</v>
@@ -16138,13 +16138,13 @@
         <v>1.2</v>
       </c>
       <c r="T97">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U97">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V97">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W97">
         <v>1.18</v>
@@ -16153,16 +16153,16 @@
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA97">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB97">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC97">
         <v>2.06</v>
@@ -16174,10 +16174,10 @@
         <v>1.25</v>
       </c>
       <c r="AF97">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG97">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q98">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R98">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="S98">
         <v>1.15</v>
@@ -16304,10 +16304,10 @@
         <v>4.3</v>
       </c>
       <c r="U98">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V98">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W98">
         <v>1.22</v>
@@ -16322,25 +16322,25 @@
         <v>7</v>
       </c>
       <c r="AA98">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AB98">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AC98">
         <v>1.89</v>
       </c>
       <c r="AD98">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AE98">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF98">
         <v>1.35</v>
       </c>
       <c r="AG98">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16449,22 +16449,22 @@
         <v>2.82</v>
       </c>
       <c r="O99">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q99">
         <v>3.32</v>
       </c>
       <c r="R99">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U99">
         <v>1.99</v>
@@ -16473,10 +16473,10 @@
         <v>1.74</v>
       </c>
       <c r="W99">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
         <v>1.06</v>
@@ -16491,19 +16491,19 @@
         <v>2.9</v>
       </c>
       <c r="AC99">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AD99">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE99">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF99">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AG99">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,55 +16618,55 @@
         <v>2.3</v>
       </c>
       <c r="Q100">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R100">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S100">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T100">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U100">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V100">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
         <v>1.42</v>
       </c>
       <c r="Z100">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="AA100">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB100">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC100">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="AD100">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE100">
         <v>1.01</v>
       </c>
       <c r="AF100">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG100">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="O101">
-        <v>4.07</v>
+        <v>3.75</v>
       </c>
       <c r="P101">
-        <v>5.06</v>
+        <v>5.25</v>
       </c>
       <c r="Q101">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R101">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V101">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
         <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z101">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AA101">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB101">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC101">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="AD101">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG101">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK101">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O102">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
         <v>3.1</v>
       </c>
       <c r="Q102">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="R102">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W102">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
+        <v>1.27</v>
+      </c>
+      <c r="Z102">
+        <v>3.44</v>
+      </c>
+      <c r="AA102">
+        <v>1.85</v>
+      </c>
+      <c r="AB102">
+        <v>1.91</v>
+      </c>
+      <c r="AC102">
+        <v>3.1</v>
+      </c>
+      <c r="AD102">
         <v>1.36</v>
       </c>
-      <c r="Z102">
-        <v>2.7</v>
-      </c>
-      <c r="AA102">
-        <v>2.3</v>
-      </c>
-      <c r="AB102">
-        <v>1.6</v>
-      </c>
-      <c r="AC102">
-        <v>3.99</v>
-      </c>
-      <c r="AD102">
-        <v>1.2</v>
-      </c>
       <c r="AE102">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG102">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O103">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="P103">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="Q103">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="R103">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="U103">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y103">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z103">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC103">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK103">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O104">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="Q104">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R104">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="S104">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T104">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="U104">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V104">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z104">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AA104">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB104">
+        <v>1.81</v>
+      </c>
+      <c r="AC104">
+        <v>3.2</v>
+      </c>
+      <c r="AD104">
+        <v>1.32</v>
+      </c>
+      <c r="AE104">
+        <v>1.07</v>
+      </c>
+      <c r="AF104">
         <v>1.7</v>
       </c>
-      <c r="AC104">
-        <v>3.58</v>
-      </c>
-      <c r="AD104">
-        <v>1.21</v>
-      </c>
-      <c r="AE104">
-        <v>1.04</v>
-      </c>
-      <c r="AF104">
-        <v>1.82</v>
-      </c>
       <c r="AG104">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,25 +17424,25 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="O105">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="Q105">
+        <v>2.31</v>
+      </c>
+      <c r="R105">
         <v>2.25</v>
       </c>
-      <c r="R105">
-        <v>2.3</v>
-      </c>
       <c r="S105">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="U105">
         <v>2.55</v>
@@ -17451,16 +17451,16 @@
         <v>1.45</v>
       </c>
       <c r="W105">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA105">
         <v>1.75</v>
@@ -17469,13 +17469,13 @@
         <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AD105">
         <v>1.35</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
         <v>1.67</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O106">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="Q106">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R106">
         <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U106">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z106">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA106">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AC106">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="AD106">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE106">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AG106">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17753,61 +17753,61 @@
         <v>1.46</v>
       </c>
       <c r="O107">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P107">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="Q107">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R107">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U107">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
         <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA107">
         <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AD107">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG107">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="O108">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q108">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="R108">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S108">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U108">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="V108">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W108">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z108">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AA108">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB108">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AC108">
-        <v>4.05</v>
+        <v>2.98</v>
       </c>
       <c r="AD108">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AG108">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O109">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P109">
+        <v>4.4</v>
+      </c>
+      <c r="Q109">
+        <v>2.4</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>1.44</v>
+      </c>
+      <c r="T109">
+        <v>2.64</v>
+      </c>
+      <c r="U109">
+        <v>3.09</v>
+      </c>
+      <c r="V109">
+        <v>1.29</v>
+      </c>
+      <c r="W109">
+        <v>1.01</v>
+      </c>
+      <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.41</v>
+      </c>
+      <c r="Z109">
+        <v>2.88</v>
+      </c>
+      <c r="AA109">
+        <v>2.2</v>
+      </c>
+      <c r="AB109">
+        <v>1.71</v>
+      </c>
+      <c r="AC109">
         <v>4.5</v>
       </c>
-      <c r="Q109">
-        <v>2.2</v>
-      </c>
-      <c r="R109">
-        <v>2.25</v>
-      </c>
-      <c r="S109">
-        <v>1.3</v>
-      </c>
-      <c r="T109">
-        <v>2.95</v>
-      </c>
-      <c r="U109">
-        <v>2.55</v>
-      </c>
-      <c r="V109">
-        <v>1.44</v>
-      </c>
-      <c r="W109">
-        <v>1.07</v>
-      </c>
-      <c r="X109">
-        <v>1</v>
-      </c>
-      <c r="Y109">
-        <v>1.26</v>
-      </c>
-      <c r="Z109">
-        <v>3.66</v>
-      </c>
-      <c r="AA109">
-        <v>1.81</v>
-      </c>
-      <c r="AB109">
-        <v>1.86</v>
-      </c>
-      <c r="AC109">
-        <v>3.04</v>
-      </c>
       <c r="AD109">
+        <v>1.17</v>
+      </c>
+      <c r="AE109">
+        <v>1.03</v>
+      </c>
+      <c r="AF109">
+        <v>2</v>
+      </c>
+      <c r="AG109">
+        <v>1.69</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.29</v>
       </c>
-      <c r="AE109">
-        <v>1.07</v>
-      </c>
-      <c r="AF109">
-        <v>1.78</v>
-      </c>
-      <c r="AG109">
-        <v>1.88</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.25</v>
-      </c>
       <c r="AK109">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R110">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S110">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z110">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="AA110">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC110">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.69</v>
+        <v>2.47</v>
       </c>
       <c r="O111">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P111">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q111">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R111">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T111">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="U111">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="V111">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z111">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA111">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB111">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC111">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="AD111">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF111">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AG111">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,65 +18565,65 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P112">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="R112">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W112">
         <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA112">
+        <v>2.11</v>
+      </c>
+      <c r="AB112">
+        <v>1.73</v>
+      </c>
+      <c r="AC112">
+        <v>3.8</v>
+      </c